--- a/aggregate_data.xlsx
+++ b/aggregate_data.xlsx
@@ -8,10 +8,10 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="CPU Statistics" sheetId="2" r:id="rId4"/>
-    <sheet name="CPU Charts" sheetId="3" r:id="rId6"/>
-    <sheet name="Memory Statistics" sheetId="4" r:id="rId7"/>
-    <sheet name="Memory Charts" sheetId="5" r:id="rId8"/>
+    <sheet name="CPU_Statistics" sheetId="2" r:id="rId4"/>
+    <sheet name="CPU_Charts" sheetId="3" r:id="rId6"/>
+    <sheet name="Memory_Statistics" sheetId="4" r:id="rId7"/>
+    <sheet name="Memory_Charts" sheetId="5" r:id="rId8"/>
   </sheets>
   <calcPr calcId="122211"/>
 </workbook>
@@ -218,12 +218,12 @@
           <invertIfNegative val="0"/>
           <cat>
             <strRef>
-              <f>CPU Statistics!$D$2:$D$19</f>
+              <f>CPU_Statistics!$D$2:$D$19</f>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>CPU Statistics!$E$2:$E$19</f>
+              <f>CPU_Statistics!$E$2:$E$19</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -711,12 +711,12 @@
           <invertIfNegative val="0"/>
           <cat>
             <strRef>
-              <f>Memory Statistics!$D$2:$D$19</f>
+              <f>Memory_Statistics!$D$2:$D$19</f>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>Memory Statistics!$E$2:$E$19</f>
+              <f>Memory_Statistics!$E$2:$E$19</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -741,12 +741,12 @@
           <invertIfNegative val="0"/>
           <cat>
             <strRef>
-              <f>Memory Statistics!$D$2:$D$19</f>
+              <f>Memory_Statistics!$D$2:$D$19</f>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>Memory Statistics!$F$2:$F$19</f>
+              <f>Memory_Statistics!$F$2:$F$19</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -984,12 +984,12 @@
           <invertIfNegative val="0"/>
           <cat>
             <strRef>
-              <f>Memory Statistics!$D$2:$D$19</f>
+              <f>Memory_Statistics!$D$2:$D$19</f>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>Memory Statistics!$G$2:$G$19</f>
+              <f>Memory_Statistics!$G$2:$G$19</f>
             </numRef>
           </val>
           <smooth val="0"/>

--- a/aggregate_data.xlsx
+++ b/aggregate_data.xlsx
@@ -194,10 +194,9 @@
       <thickness val="0"/>
     </backWall>
     <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <varyColors val="1"/>
+      <scatterChart>
+        <scatterStyle val="smoothMarker"/>
+        <varyColors val="0"/>
         <ser>
           <idx val="0"/>
           <order val="0"/>
@@ -206,26 +205,36 @@
               <f>Average Cycles</f>
             </strRef>
           </tx>
-          <dLbls>
-            <showLegendKey val="0"/>
-            <showVal val="0"/>
-            <showCatName val="0"/>
-            <showSerName val="0"/>
-            <showPercent val="0"/>
-            <showBubbleSize val="0"/>
-            <showLeaderLines val="0"/>
-          </dLbls>
+          <spPr>
+            <a:ln w="25400">
+              <a:noFill> </a:noFill>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="5"/>
+            <spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9252">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+            </spPr>
+          </marker>
           <invertIfNegative val="0"/>
-          <cat>
+          <xVal>
             <strRef>
               <f>CPU_Statistics!$D$2:$D$19</f>
             </strRef>
-          </cat>
-          <val>
+          </xVal>
+          <yVal>
             <numRef>
               <f>CPU_Statistics!$E$2:$E$19</f>
             </numRef>
-          </val>
+          </yVal>
           <smooth val="0"/>
         </ser>
         <dLbls>
@@ -239,7 +248,7 @@
         </dLbls>
         <axId val="754001152"/>
         <axId val="753999904"/>
-      </barChart>
+      </scatterChart>
       <catAx>
         <axId val="754001152"/>
         <scaling>

--- a/aggregate_data.xlsx
+++ b/aggregate_data.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <si>
     <t>Algorithm</t>
   </si>
@@ -32,16 +32,16 @@
     <t>File Size (bytes)</t>
   </si>
   <si>
-    <t>Average Cycles</t>
+    <t>Average Time (ns)</t>
   </si>
   <si>
     <t>Std Dev</t>
   </si>
   <si>
-    <t>Min Cycles</t>
-  </si>
-  <si>
-    <t>Max Cycles</t>
+    <t>Min Time (ns)</t>
+  </si>
+  <si>
+    <t>Max Time (ns)</t>
   </si>
   <si>
     <t>Sample Count</t>
@@ -65,10 +65,58 @@
     <t>04_10K.bin</t>
   </si>
   <si>
-    <t>05_50K.bin</t>
-  </si>
-  <si>
-    <t>06_100K.bin</t>
+    <t>05_15K.bin</t>
+  </si>
+  <si>
+    <t>06_20K.bin</t>
+  </si>
+  <si>
+    <t>07_25K.bin</t>
+  </si>
+  <si>
+    <t>08_30K.bin</t>
+  </si>
+  <si>
+    <t>09_35K.bin</t>
+  </si>
+  <si>
+    <t>10_40K.bin</t>
+  </si>
+  <si>
+    <t>11_45K.bin</t>
+  </si>
+  <si>
+    <t>12_50K.bin</t>
+  </si>
+  <si>
+    <t>13_55K.bin</t>
+  </si>
+  <si>
+    <t>14_60K.bin</t>
+  </si>
+  <si>
+    <t>15_65K.bin</t>
+  </si>
+  <si>
+    <t>16_70K.bin</t>
+  </si>
+  <si>
+    <t>17_75K.bin</t>
+  </si>
+  <si>
+    <t>18_80K.bin</t>
+  </si>
+  <si>
+    <t>19_85K.bin</t>
+  </si>
+  <si>
+    <t>20_90K.bin</t>
+  </si>
+  <si>
+    <t>21_95K.bin</t>
+  </si>
+  <si>
+    <t>22_100K.bin</t>
   </si>
   <si>
     <t>merge-sort</t>
@@ -455,16 +503,16 @@
         <v>100</v>
       </c>
       <c r="E2">
-        <v>470457.8</v>
+        <v>29812.7</v>
       </c>
       <c r="F2">
-        <v>41309.90932403508</v>
+        <v>1038.8427263065378</v>
       </c>
       <c r="G2">
-        <v>426848</v>
+        <v>28679</v>
       </c>
       <c r="H2">
-        <v>577414</v>
+        <v>32377</v>
       </c>
       <c r="I2">
         <v>10</v>
@@ -484,16 +532,16 @@
         <v>1024</v>
       </c>
       <c r="E3">
-        <v>13662388.8</v>
+        <v>2779192.4</v>
       </c>
       <c r="F3">
-        <v>9791293.112908844</v>
+        <v>128546.64200608275</v>
       </c>
       <c r="G3">
-        <v>8872904</v>
+        <v>2590798</v>
       </c>
       <c r="H3">
-        <v>41618002</v>
+        <v>2955012</v>
       </c>
       <c r="I3">
         <v>10</v>
@@ -513,16 +561,16 @@
         <v>5120</v>
       </c>
       <c r="E4">
-        <v>232415567.6</v>
+        <v>71031572.7</v>
       </c>
       <c r="F4">
-        <v>9830667.115144517</v>
+        <v>786363.3055916394</v>
       </c>
       <c r="G4">
-        <v>225277644</v>
+        <v>69792216</v>
       </c>
       <c r="H4">
-        <v>260640886</v>
+        <v>72235488</v>
       </c>
       <c r="I4">
         <v>10</v>
@@ -542,16 +590,16 @@
         <v>10240</v>
       </c>
       <c r="E5">
-        <v>927672148.4</v>
+        <v>285652901.5</v>
       </c>
       <c r="F5">
-        <v>16327839.820732826</v>
+        <v>1754952.7315645427</v>
       </c>
       <c r="G5">
-        <v>904739604</v>
+        <v>282599499</v>
       </c>
       <c r="H5">
-        <v>966794964</v>
+        <v>288668232</v>
       </c>
       <c r="I5">
         <v>10</v>
@@ -568,19 +616,19 @@
         <v>15</v>
       </c>
       <c r="D6">
-        <v>51200</v>
+        <v>15360</v>
       </c>
       <c r="E6">
-        <v>22648774218.4</v>
+        <v>633566838</v>
       </c>
       <c r="F6">
-        <v>262017421.55413854</v>
+        <v>2684262.222956245</v>
       </c>
       <c r="G6">
-        <v>21985413392</v>
+        <v>628642329</v>
       </c>
       <c r="H6">
-        <v>22871080652</v>
+        <v>637129164</v>
       </c>
       <c r="I6">
         <v>10</v>
@@ -597,19 +645,19 @@
         <v>16</v>
       </c>
       <c r="D7">
-        <v>102400</v>
+        <v>20480</v>
       </c>
       <c r="E7">
-        <v>89216235783</v>
+        <v>1115376821.8</v>
       </c>
       <c r="F7">
-        <v>302486583.34774214</v>
+        <v>3215632.094184495</v>
       </c>
       <c r="G7">
-        <v>88562186492</v>
+        <v>1111229591</v>
       </c>
       <c r="H7">
-        <v>89589077290</v>
+        <v>1120011995</v>
       </c>
       <c r="I7">
         <v>10</v>
@@ -617,28 +665,28 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" t="s">
         <v>17</v>
       </c>
-      <c r="B8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" t="s">
-        <v>11</v>
-      </c>
       <c r="D8">
-        <v>100</v>
+        <v>25600</v>
       </c>
       <c r="E8">
-        <v>2393228.8</v>
+        <v>1760931144</v>
       </c>
       <c r="F8">
-        <v>1502997.0857843205</v>
+        <v>2228218.8275928376</v>
       </c>
       <c r="G8">
-        <v>732070</v>
+        <v>1757362474</v>
       </c>
       <c r="H8">
-        <v>4638344</v>
+        <v>1765914102</v>
       </c>
       <c r="I8">
         <v>10</v>
@@ -646,28 +694,28 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B9" t="s">
         <v>10</v>
       </c>
       <c r="C9" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D9">
-        <v>1024</v>
+        <v>30720</v>
       </c>
       <c r="E9">
-        <v>11244731</v>
+        <v>2595987199</v>
       </c>
       <c r="F9">
-        <v>3991629.9543546117</v>
+        <v>3541873.2244408466</v>
       </c>
       <c r="G9">
-        <v>8555176</v>
+        <v>2591252196</v>
       </c>
       <c r="H9">
-        <v>22700552</v>
+        <v>2602386165</v>
       </c>
       <c r="I9">
         <v>10</v>
@@ -675,28 +723,28 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B10" t="s">
         <v>10</v>
       </c>
       <c r="C10" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D10">
-        <v>5120</v>
+        <v>35840</v>
       </c>
       <c r="E10">
-        <v>48288553.6</v>
+        <v>3461565794.5</v>
       </c>
       <c r="F10">
-        <v>2605521.701544441</v>
+        <v>10153650.46859956</v>
       </c>
       <c r="G10">
-        <v>44879654</v>
+        <v>3441633539</v>
       </c>
       <c r="H10">
-        <v>53403892</v>
+        <v>3474835531</v>
       </c>
       <c r="I10">
         <v>10</v>
@@ -704,28 +752,28 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B11" t="s">
         <v>10</v>
       </c>
       <c r="C11" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D11">
-        <v>10240</v>
+        <v>40960</v>
       </c>
       <c r="E11">
-        <v>94121817.4</v>
+        <v>4695119000.9</v>
       </c>
       <c r="F11">
-        <v>2452905.744029974</v>
+        <v>8493014.250649782</v>
       </c>
       <c r="G11">
-        <v>91776446</v>
+        <v>4679850158</v>
       </c>
       <c r="H11">
-        <v>99170956</v>
+        <v>4705989171</v>
       </c>
       <c r="I11">
         <v>10</v>
@@ -733,28 +781,28 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B12" t="s">
         <v>10</v>
       </c>
       <c r="C12" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D12">
-        <v>51200</v>
+        <v>46080</v>
       </c>
       <c r="E12">
-        <v>470071874.8</v>
+        <v>5725006478.3</v>
       </c>
       <c r="F12">
-        <v>21110852.23579941</v>
+        <v>6041809.858051444</v>
       </c>
       <c r="G12">
-        <v>413350856</v>
+        <v>5713921093</v>
       </c>
       <c r="H12">
-        <v>501016270</v>
+        <v>5734367665</v>
       </c>
       <c r="I12">
         <v>10</v>
@@ -762,28 +810,28 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B13" t="s">
         <v>10</v>
       </c>
       <c r="C13" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D13">
-        <v>102400</v>
+        <v>51200</v>
       </c>
       <c r="E13">
-        <v>931505808.8</v>
+        <v>7114505067.9</v>
       </c>
       <c r="F13">
-        <v>45925273.48101086</v>
+        <v>17525201.977596793</v>
       </c>
       <c r="G13">
-        <v>798129736</v>
+        <v>7074168021</v>
       </c>
       <c r="H13">
-        <v>970141574</v>
+        <v>7143276005</v>
       </c>
       <c r="I13">
         <v>10</v>
@@ -791,28 +839,28 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B14" t="s">
         <v>10</v>
       </c>
       <c r="C14" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="D14">
-        <v>100</v>
+        <v>56320</v>
       </c>
       <c r="E14">
-        <v>74024.8</v>
+        <v>8592723655.9</v>
       </c>
       <c r="F14">
-        <v>22261.01608103278</v>
+        <v>30407171.825969722</v>
       </c>
       <c r="G14">
-        <v>59750</v>
+        <v>8525099803</v>
       </c>
       <c r="H14">
-        <v>127726</v>
+        <v>8628046431</v>
       </c>
       <c r="I14">
         <v>10</v>
@@ -820,28 +868,28 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B15" t="s">
         <v>10</v>
       </c>
       <c r="C15" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D15">
-        <v>1024</v>
+        <v>61440</v>
       </c>
       <c r="E15">
-        <v>1012422.8</v>
+        <v>10218618516.7</v>
       </c>
       <c r="F15">
-        <v>67146.74044925785</v>
+        <v>30745343.024566714</v>
       </c>
       <c r="G15">
-        <v>950786</v>
+        <v>10158178293</v>
       </c>
       <c r="H15">
-        <v>1186138</v>
+        <v>10253961752</v>
       </c>
       <c r="I15">
         <v>10</v>
@@ -849,28 +897,28 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B16" t="s">
         <v>10</v>
       </c>
       <c r="C16" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="D16">
-        <v>5120</v>
+        <v>66560</v>
       </c>
       <c r="E16">
-        <v>3375298.4</v>
+        <v>11958599692.9</v>
       </c>
       <c r="F16">
-        <v>2134441.1076395246</v>
+        <v>25171658.779982217</v>
       </c>
       <c r="G16">
-        <v>1047546</v>
+        <v>11892977914</v>
       </c>
       <c r="H16">
-        <v>5590728</v>
+        <v>11989094319</v>
       </c>
       <c r="I16">
         <v>10</v>
@@ -878,28 +926,28 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B17" t="s">
         <v>10</v>
       </c>
       <c r="C17" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D17">
-        <v>10240</v>
+        <v>71680</v>
       </c>
       <c r="E17">
-        <v>3817072.4</v>
+        <v>13956227440.6</v>
       </c>
       <c r="F17">
-        <v>3258654.746327423</v>
+        <v>22040504.045345258</v>
       </c>
       <c r="G17">
-        <v>2154710</v>
+        <v>13930206655</v>
       </c>
       <c r="H17">
-        <v>11295598</v>
+        <v>13989960847</v>
       </c>
       <c r="I17">
         <v>10</v>
@@ -907,28 +955,28 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B18" t="s">
         <v>10</v>
       </c>
       <c r="C18" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="D18">
-        <v>51200</v>
+        <v>76800</v>
       </c>
       <c r="E18">
-        <v>13273580.2</v>
+        <v>15974329050.1</v>
       </c>
       <c r="F18">
-        <v>5586736.032824566</v>
+        <v>27462542.64984223</v>
       </c>
       <c r="G18">
-        <v>11281770</v>
+        <v>15906870743</v>
       </c>
       <c r="H18">
-        <v>30031904</v>
+        <v>16005340097</v>
       </c>
       <c r="I18">
         <v>10</v>
@@ -936,30 +984,1422 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" t="s">
+        <v>28</v>
+      </c>
+      <c r="D19">
+        <v>81920</v>
+      </c>
+      <c r="E19">
+        <v>18222895840.3</v>
+      </c>
+      <c r="F19">
+        <v>27783338.178174943</v>
+      </c>
+      <c r="G19">
+        <v>18161021068</v>
+      </c>
+      <c r="H19">
+        <v>18261769127</v>
+      </c>
+      <c r="I19">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" t="s">
+        <v>29</v>
+      </c>
+      <c r="D20">
+        <v>87040</v>
+      </c>
+      <c r="E20">
+        <v>20559390221.8</v>
+      </c>
+      <c r="F20">
+        <v>59666519.4523001</v>
+      </c>
+      <c r="G20">
+        <v>20417708259</v>
+      </c>
+      <c r="H20">
+        <v>20633684590</v>
+      </c>
+      <c r="I20">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" t="s">
+        <v>30</v>
+      </c>
+      <c r="D21">
+        <v>92160</v>
+      </c>
+      <c r="E21">
+        <v>22971938112.2</v>
+      </c>
+      <c r="F21">
+        <v>43803802.270309515</v>
+      </c>
+      <c r="G21">
+        <v>22914267550</v>
+      </c>
+      <c r="H21">
+        <v>23078429638</v>
+      </c>
+      <c r="I21">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" t="s">
+        <v>31</v>
+      </c>
+      <c r="D22">
+        <v>97280</v>
+      </c>
+      <c r="E22">
+        <v>25709704095.3</v>
+      </c>
+      <c r="F22">
+        <v>38325958.63675712</v>
+      </c>
+      <c r="G22">
+        <v>25660233364</v>
+      </c>
+      <c r="H22">
+        <v>25788692513</v>
+      </c>
+      <c r="I22">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" t="s">
+        <v>32</v>
+      </c>
+      <c r="D23">
+        <v>102400</v>
+      </c>
+      <c r="E23">
+        <v>28444096006</v>
+      </c>
+      <c r="F23">
+        <v>60268869.57973121</v>
+      </c>
+      <c r="G23">
+        <v>28366775205</v>
+      </c>
+      <c r="H23">
+        <v>28561291857</v>
+      </c>
+      <c r="I23">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>33</v>
+      </c>
+      <c r="B24" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" t="s">
+        <v>11</v>
+      </c>
+      <c r="D24">
+        <v>100</v>
+      </c>
+      <c r="E24">
+        <v>228556.6</v>
+      </c>
+      <c r="F24">
+        <v>4849.292571087045</v>
+      </c>
+      <c r="G24">
+        <v>222687</v>
+      </c>
+      <c r="H24">
+        <v>236437</v>
+      </c>
+      <c r="I24">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>33</v>
+      </c>
+      <c r="B25" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" t="s">
+        <v>12</v>
+      </c>
+      <c r="D25">
+        <v>1024</v>
+      </c>
+      <c r="E25">
+        <v>2433976.4</v>
+      </c>
+      <c r="F25">
+        <v>273136.75681577536</v>
+      </c>
+      <c r="G25">
+        <v>2203836</v>
+      </c>
+      <c r="H25">
+        <v>2975520</v>
+      </c>
+      <c r="I25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" t="s">
+        <v>13</v>
+      </c>
+      <c r="D26">
+        <v>5120</v>
+      </c>
+      <c r="E26">
+        <v>12705733.4</v>
+      </c>
+      <c r="F26">
+        <v>933828.7338184877</v>
+      </c>
+      <c r="G26">
+        <v>11861835</v>
+      </c>
+      <c r="H26">
+        <v>14966122</v>
+      </c>
+      <c r="I26">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>33</v>
+      </c>
+      <c r="B27" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" t="s">
+        <v>14</v>
+      </c>
+      <c r="D27">
+        <v>10240</v>
+      </c>
+      <c r="E27">
+        <v>25389107.5</v>
+      </c>
+      <c r="F27">
+        <v>347554.1741289406</v>
+      </c>
+      <c r="G27">
+        <v>24993520</v>
+      </c>
+      <c r="H27">
+        <v>25980352</v>
+      </c>
+      <c r="I27">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>33</v>
+      </c>
+      <c r="B28" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" t="s">
+        <v>15</v>
+      </c>
+      <c r="D28">
+        <v>15360</v>
+      </c>
+      <c r="E28">
+        <v>36383113.1</v>
+      </c>
+      <c r="F28">
+        <v>770059.4185668337</v>
+      </c>
+      <c r="G28">
+        <v>35528992</v>
+      </c>
+      <c r="H28">
+        <v>38213982</v>
+      </c>
+      <c r="I28">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>33</v>
+      </c>
+      <c r="B29" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" t="s">
+        <v>16</v>
+      </c>
+      <c r="D29">
+        <v>20480</v>
+      </c>
+      <c r="E29">
+        <v>48623879.4</v>
+      </c>
+      <c r="F29">
+        <v>520103.9238371885</v>
+      </c>
+      <c r="G29">
+        <v>47696952</v>
+      </c>
+      <c r="H29">
+        <v>49691603</v>
+      </c>
+      <c r="I29">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>33</v>
+      </c>
+      <c r="B30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" t="s">
+        <v>17</v>
+      </c>
+      <c r="D30">
+        <v>25600</v>
+      </c>
+      <c r="E30">
+        <v>60985352.4</v>
+      </c>
+      <c r="F30">
+        <v>602557.1784213013</v>
+      </c>
+      <c r="G30">
+        <v>59853310</v>
+      </c>
+      <c r="H30">
+        <v>61736222</v>
+      </c>
+      <c r="I30">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>33</v>
+      </c>
+      <c r="B31" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" t="s">
         <v>18</v>
       </c>
-      <c r="B19" t="s">
-        <v>10</v>
-      </c>
-      <c r="C19" t="s">
+      <c r="D31">
+        <v>30720</v>
+      </c>
+      <c r="E31">
+        <v>72569335</v>
+      </c>
+      <c r="F31">
+        <v>693353.8234383654</v>
+      </c>
+      <c r="G31">
+        <v>71757064</v>
+      </c>
+      <c r="H31">
+        <v>74374983</v>
+      </c>
+      <c r="I31">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>33</v>
+      </c>
+      <c r="B32" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" t="s">
+        <v>19</v>
+      </c>
+      <c r="D32">
+        <v>35840</v>
+      </c>
+      <c r="E32">
+        <v>85059505.7</v>
+      </c>
+      <c r="F32">
+        <v>557854.350569582</v>
+      </c>
+      <c r="G32">
+        <v>84024787</v>
+      </c>
+      <c r="H32">
+        <v>85910135</v>
+      </c>
+      <c r="I32">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>33</v>
+      </c>
+      <c r="B33" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" t="s">
+        <v>20</v>
+      </c>
+      <c r="D33">
+        <v>40960</v>
+      </c>
+      <c r="E33">
+        <v>96687521.5</v>
+      </c>
+      <c r="F33">
+        <v>889042.0545714641</v>
+      </c>
+      <c r="G33">
+        <v>94611532</v>
+      </c>
+      <c r="H33">
+        <v>98245339</v>
+      </c>
+      <c r="I33">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" t="s">
+        <v>21</v>
+      </c>
+      <c r="D34">
+        <v>46080</v>
+      </c>
+      <c r="E34">
+        <v>114396494.4</v>
+      </c>
+      <c r="F34">
+        <v>945327.5546362965</v>
+      </c>
+      <c r="G34">
+        <v>112742319</v>
+      </c>
+      <c r="H34">
+        <v>116153523</v>
+      </c>
+      <c r="I34">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>33</v>
+      </c>
+      <c r="B35" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" t="s">
+        <v>22</v>
+      </c>
+      <c r="D35">
+        <v>51200</v>
+      </c>
+      <c r="E35">
+        <v>128073697.4</v>
+      </c>
+      <c r="F35">
+        <v>1515159.2357099764</v>
+      </c>
+      <c r="G35">
+        <v>126838798</v>
+      </c>
+      <c r="H35">
+        <v>132419870</v>
+      </c>
+      <c r="I35">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>33</v>
+      </c>
+      <c r="B36" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" t="s">
+        <v>23</v>
+      </c>
+      <c r="D36">
+        <v>56320</v>
+      </c>
+      <c r="E36">
+        <v>133712954.7</v>
+      </c>
+      <c r="F36">
+        <v>550642.0552932821</v>
+      </c>
+      <c r="G36">
+        <v>132938260</v>
+      </c>
+      <c r="H36">
+        <v>134996673</v>
+      </c>
+      <c r="I36">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>33</v>
+      </c>
+      <c r="B37" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" t="s">
+        <v>24</v>
+      </c>
+      <c r="D37">
+        <v>61440</v>
+      </c>
+      <c r="E37">
+        <v>146554587.8</v>
+      </c>
+      <c r="F37">
+        <v>677399.5802601002</v>
+      </c>
+      <c r="G37">
+        <v>145660508</v>
+      </c>
+      <c r="H37">
+        <v>147777458</v>
+      </c>
+      <c r="I37">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>33</v>
+      </c>
+      <c r="B38" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" t="s">
+        <v>25</v>
+      </c>
+      <c r="D38">
+        <v>66560</v>
+      </c>
+      <c r="E38">
+        <v>158203280.2</v>
+      </c>
+      <c r="F38">
+        <v>500543.7591325657</v>
+      </c>
+      <c r="G38">
+        <v>157138681</v>
+      </c>
+      <c r="H38">
+        <v>158868899</v>
+      </c>
+      <c r="I38">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>33</v>
+      </c>
+      <c r="B39" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" t="s">
+        <v>26</v>
+      </c>
+      <c r="D39">
+        <v>71680</v>
+      </c>
+      <c r="E39">
+        <v>170926709.3</v>
+      </c>
+      <c r="F39">
+        <v>760964.6698459857</v>
+      </c>
+      <c r="G39">
+        <v>169419623</v>
+      </c>
+      <c r="H39">
+        <v>171838531</v>
+      </c>
+      <c r="I39">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>33</v>
+      </c>
+      <c r="B40" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" t="s">
+        <v>27</v>
+      </c>
+      <c r="D40">
+        <v>76800</v>
+      </c>
+      <c r="E40">
+        <v>180511694.5</v>
+      </c>
+      <c r="F40">
+        <v>1006279.7828077687</v>
+      </c>
+      <c r="G40">
+        <v>179017786</v>
+      </c>
+      <c r="H40">
+        <v>181953815</v>
+      </c>
+      <c r="I40">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>33</v>
+      </c>
+      <c r="B41" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" t="s">
+        <v>28</v>
+      </c>
+      <c r="D41">
+        <v>81920</v>
+      </c>
+      <c r="E41">
+        <v>193626605.6</v>
+      </c>
+      <c r="F41">
+        <v>1032261.8028109148</v>
+      </c>
+      <c r="G41">
+        <v>191606156</v>
+      </c>
+      <c r="H41">
+        <v>195508923</v>
+      </c>
+      <c r="I41">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>33</v>
+      </c>
+      <c r="B42" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" t="s">
+        <v>29</v>
+      </c>
+      <c r="D42">
+        <v>87040</v>
+      </c>
+      <c r="E42">
+        <v>208244752.5</v>
+      </c>
+      <c r="F42">
+        <v>1673011.7109844899</v>
+      </c>
+      <c r="G42">
+        <v>206615841</v>
+      </c>
+      <c r="H42">
+        <v>212408433</v>
+      </c>
+      <c r="I42">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>33</v>
+      </c>
+      <c r="B43" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" t="s">
+        <v>30</v>
+      </c>
+      <c r="D43">
+        <v>92160</v>
+      </c>
+      <c r="E43">
+        <v>213587381.4</v>
+      </c>
+      <c r="F43">
+        <v>2453882.5531198187</v>
+      </c>
+      <c r="G43">
+        <v>211265945</v>
+      </c>
+      <c r="H43">
+        <v>220015535</v>
+      </c>
+      <c r="I43">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>33</v>
+      </c>
+      <c r="B44" t="s">
+        <v>10</v>
+      </c>
+      <c r="C44" t="s">
+        <v>31</v>
+      </c>
+      <c r="D44">
+        <v>97280</v>
+      </c>
+      <c r="E44">
+        <v>230312851.5</v>
+      </c>
+      <c r="F44">
+        <v>2113959.2718966585</v>
+      </c>
+      <c r="G44">
+        <v>228374205</v>
+      </c>
+      <c r="H44">
+        <v>233779256</v>
+      </c>
+      <c r="I44">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>33</v>
+      </c>
+      <c r="B45" t="s">
+        <v>10</v>
+      </c>
+      <c r="C45" t="s">
+        <v>32</v>
+      </c>
+      <c r="D45">
+        <v>102400</v>
+      </c>
+      <c r="E45">
+        <v>243367823.3</v>
+      </c>
+      <c r="F45">
+        <v>1448726.7810353371</v>
+      </c>
+      <c r="G45">
+        <v>241387010</v>
+      </c>
+      <c r="H45">
+        <v>246930802</v>
+      </c>
+      <c r="I45">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>34</v>
+      </c>
+      <c r="B46" t="s">
+        <v>10</v>
+      </c>
+      <c r="C46" t="s">
+        <v>11</v>
+      </c>
+      <c r="D46">
+        <v>100</v>
+      </c>
+      <c r="E46">
+        <v>4534.7</v>
+      </c>
+      <c r="F46">
+        <v>939.31337156457</v>
+      </c>
+      <c r="G46">
+        <v>4001</v>
+      </c>
+      <c r="H46">
+        <v>7049</v>
+      </c>
+      <c r="I46">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>34</v>
+      </c>
+      <c r="B47" t="s">
+        <v>10</v>
+      </c>
+      <c r="C47" t="s">
+        <v>12</v>
+      </c>
+      <c r="D47">
+        <v>1024</v>
+      </c>
+      <c r="E47">
+        <v>71213.6</v>
+      </c>
+      <c r="F47">
+        <v>3165.8121927871844</v>
+      </c>
+      <c r="G47">
+        <v>67369</v>
+      </c>
+      <c r="H47">
+        <v>77745</v>
+      </c>
+      <c r="I47">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>34</v>
+      </c>
+      <c r="B48" t="s">
+        <v>10</v>
+      </c>
+      <c r="C48" t="s">
+        <v>13</v>
+      </c>
+      <c r="D48">
+        <v>5120</v>
+      </c>
+      <c r="E48">
+        <v>383914.5</v>
+      </c>
+      <c r="F48">
+        <v>16404.526382983448</v>
+      </c>
+      <c r="G48">
+        <v>369094</v>
+      </c>
+      <c r="H48">
+        <v>430934</v>
+      </c>
+      <c r="I48">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>34</v>
+      </c>
+      <c r="B49" t="s">
+        <v>10</v>
+      </c>
+      <c r="C49" t="s">
+        <v>14</v>
+      </c>
+      <c r="D49">
+        <v>10240</v>
+      </c>
+      <c r="E49">
+        <v>780722.2</v>
+      </c>
+      <c r="F49">
+        <v>15861.735817999237</v>
+      </c>
+      <c r="G49">
+        <v>766377</v>
+      </c>
+      <c r="H49">
+        <v>819666</v>
+      </c>
+      <c r="I49">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>34</v>
+      </c>
+      <c r="B50" t="s">
+        <v>10</v>
+      </c>
+      <c r="C50" t="s">
+        <v>15</v>
+      </c>
+      <c r="D50">
+        <v>15360</v>
+      </c>
+      <c r="E50">
+        <v>1197383.1</v>
+      </c>
+      <c r="F50">
+        <v>28647.41145182231</v>
+      </c>
+      <c r="G50">
+        <v>1163265</v>
+      </c>
+      <c r="H50">
+        <v>1266258</v>
+      </c>
+      <c r="I50">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>34</v>
+      </c>
+      <c r="B51" t="s">
+        <v>10</v>
+      </c>
+      <c r="C51" t="s">
         <v>16</v>
       </c>
-      <c r="D19">
+      <c r="D51">
+        <v>20480</v>
+      </c>
+      <c r="E51">
+        <v>1617710.5</v>
+      </c>
+      <c r="F51">
+        <v>32210.236249521673</v>
+      </c>
+      <c r="G51">
+        <v>1577250</v>
+      </c>
+      <c r="H51">
+        <v>1689270</v>
+      </c>
+      <c r="I51">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>34</v>
+      </c>
+      <c r="B52" t="s">
+        <v>10</v>
+      </c>
+      <c r="C52" t="s">
+        <v>17</v>
+      </c>
+      <c r="D52">
+        <v>25600</v>
+      </c>
+      <c r="E52">
+        <v>2003608</v>
+      </c>
+      <c r="F52">
+        <v>29623.824091430193</v>
+      </c>
+      <c r="G52">
+        <v>1973822</v>
+      </c>
+      <c r="H52">
+        <v>2076675</v>
+      </c>
+      <c r="I52">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>34</v>
+      </c>
+      <c r="B53" t="s">
+        <v>10</v>
+      </c>
+      <c r="C53" t="s">
+        <v>18</v>
+      </c>
+      <c r="D53">
+        <v>30720</v>
+      </c>
+      <c r="E53">
+        <v>2446195.5</v>
+      </c>
+      <c r="F53">
+        <v>32816.35155909322</v>
+      </c>
+      <c r="G53">
+        <v>2412819</v>
+      </c>
+      <c r="H53">
+        <v>2513114</v>
+      </c>
+      <c r="I53">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>34</v>
+      </c>
+      <c r="B54" t="s">
+        <v>10</v>
+      </c>
+      <c r="C54" t="s">
+        <v>19</v>
+      </c>
+      <c r="D54">
+        <v>35840</v>
+      </c>
+      <c r="E54">
+        <v>2859693.4</v>
+      </c>
+      <c r="F54">
+        <v>26447.14919306049</v>
+      </c>
+      <c r="G54">
+        <v>2811834</v>
+      </c>
+      <c r="H54">
+        <v>2899011</v>
+      </c>
+      <c r="I54">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>34</v>
+      </c>
+      <c r="B55" t="s">
+        <v>10</v>
+      </c>
+      <c r="C55" t="s">
+        <v>20</v>
+      </c>
+      <c r="D55">
+        <v>40960</v>
+      </c>
+      <c r="E55">
+        <v>3316331.1</v>
+      </c>
+      <c r="F55">
+        <v>41823.75758214463</v>
+      </c>
+      <c r="G55">
+        <v>3241486</v>
+      </c>
+      <c r="H55">
+        <v>3375923</v>
+      </c>
+      <c r="I55">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>34</v>
+      </c>
+      <c r="B56" t="s">
+        <v>10</v>
+      </c>
+      <c r="C56" t="s">
+        <v>21</v>
+      </c>
+      <c r="D56">
+        <v>46080</v>
+      </c>
+      <c r="E56">
+        <v>3721145.5</v>
+      </c>
+      <c r="F56">
+        <v>39265.9371930685</v>
+      </c>
+      <c r="G56">
+        <v>3664271</v>
+      </c>
+      <c r="H56">
+        <v>3796694</v>
+      </c>
+      <c r="I56">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>34</v>
+      </c>
+      <c r="B57" t="s">
+        <v>10</v>
+      </c>
+      <c r="C57" t="s">
+        <v>22</v>
+      </c>
+      <c r="D57">
+        <v>51200</v>
+      </c>
+      <c r="E57">
+        <v>4190075.6</v>
+      </c>
+      <c r="F57">
+        <v>81707.70218186289</v>
+      </c>
+      <c r="G57">
+        <v>4073204</v>
+      </c>
+      <c r="H57">
+        <v>4334729</v>
+      </c>
+      <c r="I57">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>34</v>
+      </c>
+      <c r="B58" t="s">
+        <v>10</v>
+      </c>
+      <c r="C58" t="s">
+        <v>23</v>
+      </c>
+      <c r="D58">
+        <v>56320</v>
+      </c>
+      <c r="E58">
+        <v>4569048</v>
+      </c>
+      <c r="F58">
+        <v>37896.64476441153</v>
+      </c>
+      <c r="G58">
+        <v>4519449</v>
+      </c>
+      <c r="H58">
+        <v>4635083</v>
+      </c>
+      <c r="I58">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>34</v>
+      </c>
+      <c r="B59" t="s">
+        <v>10</v>
+      </c>
+      <c r="C59" t="s">
+        <v>24</v>
+      </c>
+      <c r="D59">
+        <v>61440</v>
+      </c>
+      <c r="E59">
+        <v>5005579.9</v>
+      </c>
+      <c r="F59">
+        <v>42001.91094569389</v>
+      </c>
+      <c r="G59">
+        <v>4951043</v>
+      </c>
+      <c r="H59">
+        <v>5088751</v>
+      </c>
+      <c r="I59">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>34</v>
+      </c>
+      <c r="B60" t="s">
+        <v>10</v>
+      </c>
+      <c r="C60" t="s">
+        <v>25</v>
+      </c>
+      <c r="D60">
+        <v>66560</v>
+      </c>
+      <c r="E60">
+        <v>5410891.7</v>
+      </c>
+      <c r="F60">
+        <v>25549.463920207796</v>
+      </c>
+      <c r="G60">
+        <v>5363804</v>
+      </c>
+      <c r="H60">
+        <v>5441963</v>
+      </c>
+      <c r="I60">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>34</v>
+      </c>
+      <c r="B61" t="s">
+        <v>10</v>
+      </c>
+      <c r="C61" t="s">
+        <v>26</v>
+      </c>
+      <c r="D61">
+        <v>71680</v>
+      </c>
+      <c r="E61">
+        <v>5874645.8</v>
+      </c>
+      <c r="F61">
+        <v>31047.71521320047</v>
+      </c>
+      <c r="G61">
+        <v>5825408</v>
+      </c>
+      <c r="H61">
+        <v>5913905</v>
+      </c>
+      <c r="I61">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>34</v>
+      </c>
+      <c r="B62" t="s">
+        <v>10</v>
+      </c>
+      <c r="C62" t="s">
+        <v>27</v>
+      </c>
+      <c r="D62">
+        <v>76800</v>
+      </c>
+      <c r="E62">
+        <v>6301448.9</v>
+      </c>
+      <c r="F62">
+        <v>64832.65532808294</v>
+      </c>
+      <c r="G62">
+        <v>6195366</v>
+      </c>
+      <c r="H62">
+        <v>6403857</v>
+      </c>
+      <c r="I62">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>34</v>
+      </c>
+      <c r="B63" t="s">
+        <v>10</v>
+      </c>
+      <c r="C63" t="s">
+        <v>28</v>
+      </c>
+      <c r="D63">
+        <v>81920</v>
+      </c>
+      <c r="E63">
+        <v>6677578.1</v>
+      </c>
+      <c r="F63">
+        <v>66910.3650467549</v>
+      </c>
+      <c r="G63">
+        <v>6579023</v>
+      </c>
+      <c r="H63">
+        <v>6812683</v>
+      </c>
+      <c r="I63">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>34</v>
+      </c>
+      <c r="B64" t="s">
+        <v>10</v>
+      </c>
+      <c r="C64" t="s">
+        <v>29</v>
+      </c>
+      <c r="D64">
+        <v>87040</v>
+      </c>
+      <c r="E64">
+        <v>7194367</v>
+      </c>
+      <c r="F64">
+        <v>80967.88520765501</v>
+      </c>
+      <c r="G64">
+        <v>7081896</v>
+      </c>
+      <c r="H64">
+        <v>7329831</v>
+      </c>
+      <c r="I64">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>34</v>
+      </c>
+      <c r="B65" t="s">
+        <v>10</v>
+      </c>
+      <c r="C65" t="s">
+        <v>30</v>
+      </c>
+      <c r="D65">
+        <v>92160</v>
+      </c>
+      <c r="E65">
+        <v>7653507.4</v>
+      </c>
+      <c r="F65">
+        <v>120579.58204704478</v>
+      </c>
+      <c r="G65">
+        <v>7563230</v>
+      </c>
+      <c r="H65">
+        <v>7997624</v>
+      </c>
+      <c r="I65">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>34</v>
+      </c>
+      <c r="B66" t="s">
+        <v>10</v>
+      </c>
+      <c r="C66" t="s">
+        <v>31</v>
+      </c>
+      <c r="D66">
+        <v>97280</v>
+      </c>
+      <c r="E66">
+        <v>8008970.7</v>
+      </c>
+      <c r="F66">
+        <v>71971.43140864992</v>
+      </c>
+      <c r="G66">
+        <v>7887500</v>
+      </c>
+      <c r="H66">
+        <v>8117298</v>
+      </c>
+      <c r="I66">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>34</v>
+      </c>
+      <c r="B67" t="s">
+        <v>10</v>
+      </c>
+      <c r="C67" t="s">
+        <v>32</v>
+      </c>
+      <c r="D67">
         <v>102400</v>
       </c>
-      <c r="E19">
-        <v>25621712</v>
-      </c>
-      <c r="F19">
-        <v>7078062.584491493</v>
-      </c>
-      <c r="G19">
-        <v>23020458</v>
-      </c>
-      <c r="H19">
-        <v>46852110</v>
-      </c>
-      <c r="I19">
+      <c r="E67">
+        <v>8492545.1</v>
+      </c>
+      <c r="F67">
+        <v>102272.17173156147</v>
+      </c>
+      <c r="G67">
+        <v>8385884</v>
+      </c>
+      <c r="H67">
+        <v>8732149</v>
+      </c>
+      <c r="I67">
         <v>10</v>
       </c>
     </row>
@@ -977,7 +2417,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2">
@@ -988,10 +2428,10 @@
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3">
@@ -999,13 +2439,13 @@
         <v>100</v>
       </c>
       <c r="B3">
-        <v>470457.8</v>
+        <v>29812.7</v>
       </c>
       <c r="C3">
-        <v>2393228.8</v>
+        <v>228556.6</v>
       </c>
       <c r="D3">
-        <v>74024.8</v>
+        <v>4534.7</v>
       </c>
     </row>
     <row r="4">
@@ -1013,13 +2453,13 @@
         <v>1024</v>
       </c>
       <c r="B4">
-        <v>13662388.8</v>
+        <v>2779192.4</v>
       </c>
       <c r="C4">
-        <v>11244731</v>
+        <v>2433976.4</v>
       </c>
       <c r="D4">
-        <v>1012422.8</v>
+        <v>71213.6</v>
       </c>
     </row>
     <row r="5">
@@ -1027,13 +2467,13 @@
         <v>5120</v>
       </c>
       <c r="B5">
-        <v>232415567.6</v>
+        <v>71031572.7</v>
       </c>
       <c r="C5">
-        <v>48288553.6</v>
+        <v>12705733.4</v>
       </c>
       <c r="D5">
-        <v>3375298.4</v>
+        <v>383914.5</v>
       </c>
     </row>
     <row r="6">
@@ -1041,41 +2481,265 @@
         <v>10240</v>
       </c>
       <c r="B6">
-        <v>927672148.4</v>
+        <v>285652901.5</v>
       </c>
       <c r="C6">
-        <v>94121817.4</v>
+        <v>25389107.5</v>
       </c>
       <c r="D6">
-        <v>3817072.4</v>
+        <v>780722.2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>51200</v>
+        <v>15360</v>
       </c>
       <c r="B7">
-        <v>22648774218.4</v>
+        <v>633566838</v>
       </c>
       <c r="C7">
-        <v>470071874.8</v>
+        <v>36383113.1</v>
       </c>
       <c r="D7">
-        <v>13273580.2</v>
+        <v>1197383.1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
+        <v>20480</v>
+      </c>
+      <c r="B8">
+        <v>1115376821.8</v>
+      </c>
+      <c r="C8">
+        <v>48623879.4</v>
+      </c>
+      <c r="D8">
+        <v>1617710.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>25600</v>
+      </c>
+      <c r="B9">
+        <v>1760931144</v>
+      </c>
+      <c r="C9">
+        <v>60985352.4</v>
+      </c>
+      <c r="D9">
+        <v>2003608</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>30720</v>
+      </c>
+      <c r="B10">
+        <v>2595987199</v>
+      </c>
+      <c r="C10">
+        <v>72569335</v>
+      </c>
+      <c r="D10">
+        <v>2446195.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>35840</v>
+      </c>
+      <c r="B11">
+        <v>3461565794.5</v>
+      </c>
+      <c r="C11">
+        <v>85059505.7</v>
+      </c>
+      <c r="D11">
+        <v>2859693.4</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>40960</v>
+      </c>
+      <c r="B12">
+        <v>4695119000.9</v>
+      </c>
+      <c r="C12">
+        <v>96687521.5</v>
+      </c>
+      <c r="D12">
+        <v>3316331.1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>46080</v>
+      </c>
+      <c r="B13">
+        <v>5725006478.3</v>
+      </c>
+      <c r="C13">
+        <v>114396494.4</v>
+      </c>
+      <c r="D13">
+        <v>3721145.5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>51200</v>
+      </c>
+      <c r="B14">
+        <v>7114505067.9</v>
+      </c>
+      <c r="C14">
+        <v>128073697.4</v>
+      </c>
+      <c r="D14">
+        <v>4190075.6</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>56320</v>
+      </c>
+      <c r="B15">
+        <v>8592723655.9</v>
+      </c>
+      <c r="C15">
+        <v>133712954.7</v>
+      </c>
+      <c r="D15">
+        <v>4569048</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>61440</v>
+      </c>
+      <c r="B16">
+        <v>10218618516.7</v>
+      </c>
+      <c r="C16">
+        <v>146554587.8</v>
+      </c>
+      <c r="D16">
+        <v>5005579.9</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>66560</v>
+      </c>
+      <c r="B17">
+        <v>11958599692.9</v>
+      </c>
+      <c r="C17">
+        <v>158203280.2</v>
+      </c>
+      <c r="D17">
+        <v>5410891.7</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>71680</v>
+      </c>
+      <c r="B18">
+        <v>13956227440.6</v>
+      </c>
+      <c r="C18">
+        <v>170926709.3</v>
+      </c>
+      <c r="D18">
+        <v>5874645.8</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>76800</v>
+      </c>
+      <c r="B19">
+        <v>15974329050.1</v>
+      </c>
+      <c r="C19">
+        <v>180511694.5</v>
+      </c>
+      <c r="D19">
+        <v>6301448.9</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>81920</v>
+      </c>
+      <c r="B20">
+        <v>18222895840.3</v>
+      </c>
+      <c r="C20">
+        <v>193626605.6</v>
+      </c>
+      <c r="D20">
+        <v>6677578.1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>87040</v>
+      </c>
+      <c r="B21">
+        <v>20559390221.8</v>
+      </c>
+      <c r="C21">
+        <v>208244752.5</v>
+      </c>
+      <c r="D21">
+        <v>7194367</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>92160</v>
+      </c>
+      <c r="B22">
+        <v>22971938112.2</v>
+      </c>
+      <c r="C22">
+        <v>213587381.4</v>
+      </c>
+      <c r="D22">
+        <v>7653507.4</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>97280</v>
+      </c>
+      <c r="B23">
+        <v>25709704095.3</v>
+      </c>
+      <c r="C23">
+        <v>230312851.5</v>
+      </c>
+      <c r="D23">
+        <v>8008970.7</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
         <v>102400</v>
       </c>
-      <c r="B8">
-        <v>89216235783</v>
-      </c>
-      <c r="C8">
-        <v>931505808.8</v>
-      </c>
-      <c r="D8">
-        <v>25621712</v>
+      <c r="B24">
+        <v>28444096006</v>
+      </c>
+      <c r="C24">
+        <v>243367823.3</v>
+      </c>
+      <c r="D24">
+        <v>8492545.1</v>
       </c>
     </row>
   </sheetData>
@@ -1103,24 +2767,24 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="F1" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="G1" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="H1" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="I1" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="B2" t="s">
         <v>10</v>
@@ -1149,7 +2813,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="B3" t="s">
         <v>10</v>
@@ -1178,7 +2842,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="B4" t="s">
         <v>10</v>
@@ -1207,7 +2871,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="B5" t="s">
         <v>10</v>
@@ -1236,7 +2900,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="B6" t="s">
         <v>10</v>
@@ -1245,27 +2909,27 @@
         <v>15</v>
       </c>
       <c r="D6">
-        <v>51200</v>
+        <v>15360</v>
       </c>
       <c r="E6">
-        <v>804864</v>
+        <v>214016</v>
       </c>
       <c r="F6">
-        <v>804864</v>
+        <v>214016</v>
       </c>
       <c r="G6">
-        <v>7.86015351862341</v>
+        <v>6.967120255224949</v>
       </c>
       <c r="H6">
-        <v>51199</v>
+        <v>15359</v>
       </c>
       <c r="I6">
-        <v>51199</v>
+        <v>15359</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="B7" t="s">
         <v>10</v>
@@ -1274,21 +2938,485 @@
         <v>16</v>
       </c>
       <c r="D7">
+        <v>20480</v>
+      </c>
+      <c r="E7">
+        <v>294912</v>
+      </c>
+      <c r="F7">
+        <v>294912</v>
+      </c>
+      <c r="G7">
+        <v>7.200351579666976</v>
+      </c>
+      <c r="H7">
+        <v>20479</v>
+      </c>
+      <c r="I7">
+        <v>20479</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8">
+        <v>25600</v>
+      </c>
+      <c r="E8">
+        <v>376832</v>
+      </c>
+      <c r="F8">
+        <v>376832</v>
+      </c>
+      <c r="G8">
+        <v>7.360287511230908</v>
+      </c>
+      <c r="H8">
+        <v>25599</v>
+      </c>
+      <c r="I8">
+        <v>25599</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9">
+        <v>30720</v>
+      </c>
+      <c r="E9">
+        <v>458752</v>
+      </c>
+      <c r="F9">
+        <v>458752</v>
+      </c>
+      <c r="G9">
+        <v>7.466909730134445</v>
+      </c>
+      <c r="H9">
+        <v>30719</v>
+      </c>
+      <c r="I9">
+        <v>30719</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10">
+        <v>35840</v>
+      </c>
+      <c r="E10">
+        <v>543744</v>
+      </c>
+      <c r="F10">
+        <v>543744</v>
+      </c>
+      <c r="G10">
+        <v>7.585925946594492</v>
+      </c>
+      <c r="H10">
+        <v>35839</v>
+      </c>
+      <c r="I10">
+        <v>35839</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11">
+        <v>40960</v>
+      </c>
+      <c r="E11">
+        <v>630784</v>
+      </c>
+      <c r="F11">
+        <v>630784</v>
+      </c>
+      <c r="G11">
+        <v>7.700187992870919</v>
+      </c>
+      <c r="H11">
+        <v>40959</v>
+      </c>
+      <c r="I11">
+        <v>40959</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D12">
+        <v>46080</v>
+      </c>
+      <c r="E12">
+        <v>717824</v>
+      </c>
+      <c r="F12">
+        <v>717824</v>
+      </c>
+      <c r="G12">
+        <v>7.789057922263938</v>
+      </c>
+      <c r="H12">
+        <v>46079</v>
+      </c>
+      <c r="I12">
+        <v>46079</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13">
+        <v>51200</v>
+      </c>
+      <c r="E13">
+        <v>804864</v>
+      </c>
+      <c r="F13">
+        <v>804864</v>
+      </c>
+      <c r="G13">
+        <v>7.86015351862341</v>
+      </c>
+      <c r="H13">
+        <v>51199</v>
+      </c>
+      <c r="I13">
+        <v>51199</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14">
+        <v>56320</v>
+      </c>
+      <c r="E14">
+        <v>891904</v>
+      </c>
+      <c r="F14">
+        <v>891904</v>
+      </c>
+      <c r="G14">
+        <v>7.918322413395124</v>
+      </c>
+      <c r="H14">
+        <v>56319</v>
+      </c>
+      <c r="I14">
+        <v>56319</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" t="s">
+        <v>24</v>
+      </c>
+      <c r="D15">
+        <v>61440</v>
+      </c>
+      <c r="E15">
+        <v>978944</v>
+      </c>
+      <c r="F15">
+        <v>978944</v>
+      </c>
+      <c r="G15">
+        <v>7.966796334575758</v>
+      </c>
+      <c r="H15">
+        <v>61439</v>
+      </c>
+      <c r="I15">
+        <v>61439</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" t="s">
+        <v>25</v>
+      </c>
+      <c r="D16">
+        <v>66560</v>
+      </c>
+      <c r="E16">
+        <v>1067008</v>
+      </c>
+      <c r="F16">
+        <v>1067008</v>
+      </c>
+      <c r="G16">
+        <v>8.015505040640635</v>
+      </c>
+      <c r="H16">
+        <v>66559</v>
+      </c>
+      <c r="I16">
+        <v>66559</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" t="s">
+        <v>26</v>
+      </c>
+      <c r="D17">
+        <v>71680</v>
+      </c>
+      <c r="E17">
+        <v>1159168</v>
+      </c>
+      <c r="F17">
+        <v>1159168</v>
+      </c>
+      <c r="G17">
+        <v>8.085827090221683</v>
+      </c>
+      <c r="H17">
+        <v>71679</v>
+      </c>
+      <c r="I17">
+        <v>71679</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" t="s">
+        <v>27</v>
+      </c>
+      <c r="D18">
+        <v>76800</v>
+      </c>
+      <c r="E18">
+        <v>1251328</v>
+      </c>
+      <c r="F18">
+        <v>1251328</v>
+      </c>
+      <c r="G18">
+        <v>8.146772744436776</v>
+      </c>
+      <c r="H18">
+        <v>76799</v>
+      </c>
+      <c r="I18">
+        <v>76799</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>33</v>
+      </c>
+      <c r="B19" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" t="s">
+        <v>28</v>
+      </c>
+      <c r="D19">
+        <v>81920</v>
+      </c>
+      <c r="E19">
+        <v>1343488</v>
+      </c>
+      <c r="F19">
+        <v>1343488</v>
+      </c>
+      <c r="G19">
+        <v>8.20010009887816</v>
+      </c>
+      <c r="H19">
+        <v>81919</v>
+      </c>
+      <c r="I19">
+        <v>81919</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>33</v>
+      </c>
+      <c r="B20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" t="s">
+        <v>29</v>
+      </c>
+      <c r="D20">
+        <v>87040</v>
+      </c>
+      <c r="E20">
+        <v>1435648</v>
+      </c>
+      <c r="F20">
+        <v>1435648</v>
+      </c>
+      <c r="G20">
+        <v>8.24715357483427</v>
+      </c>
+      <c r="H20">
+        <v>87039</v>
+      </c>
+      <c r="I20">
+        <v>87039</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>33</v>
+      </c>
+      <c r="B21" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" t="s">
+        <v>30</v>
+      </c>
+      <c r="D21">
+        <v>92160</v>
+      </c>
+      <c r="E21">
+        <v>1527808</v>
+      </c>
+      <c r="F21">
+        <v>1527808</v>
+      </c>
+      <c r="G21">
+        <v>8.28897883006543</v>
+      </c>
+      <c r="H21">
+        <v>92159</v>
+      </c>
+      <c r="I21">
+        <v>92159</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>33</v>
+      </c>
+      <c r="B22" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" t="s">
+        <v>31</v>
+      </c>
+      <c r="D22">
+        <v>97280</v>
+      </c>
+      <c r="E22">
+        <v>1619968</v>
+      </c>
+      <c r="F22">
+        <v>1619968</v>
+      </c>
+      <c r="G22">
+        <v>8.326401381593149</v>
+      </c>
+      <c r="H22">
+        <v>97279</v>
+      </c>
+      <c r="I22">
+        <v>97279</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>33</v>
+      </c>
+      <c r="B23" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" t="s">
+        <v>32</v>
+      </c>
+      <c r="D23">
         <v>102400</v>
       </c>
-      <c r="E7">
+      <c r="E23">
         <v>1712128</v>
       </c>
-      <c r="F7">
+      <c r="F23">
         <v>1712128</v>
       </c>
-      <c r="G7">
+      <c r="G23">
         <v>8.36008164142228</v>
       </c>
-      <c r="H7">
+      <c r="H23">
         <v>102399</v>
       </c>
-      <c r="I7">
+      <c r="I23">
         <v>102399</v>
       </c>
     </row>
@@ -1306,7 +3434,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2">
@@ -1314,7 +3442,7 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3">
@@ -1351,17 +3479,145 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>51200</v>
+        <v>15360</v>
       </c>
       <c r="B7">
-        <v>51200</v>
+        <v>15360</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
+        <v>20480</v>
+      </c>
+      <c r="B8">
+        <v>20480</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>25600</v>
+      </c>
+      <c r="B9">
+        <v>25600</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>30720</v>
+      </c>
+      <c r="B10">
+        <v>30720</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>35840</v>
+      </c>
+      <c r="B11">
+        <v>35840</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>40960</v>
+      </c>
+      <c r="B12">
+        <v>40960</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>46080</v>
+      </c>
+      <c r="B13">
+        <v>46080</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>51200</v>
+      </c>
+      <c r="B14">
+        <v>51200</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>56320</v>
+      </c>
+      <c r="B15">
+        <v>56320</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>61440</v>
+      </c>
+      <c r="B16">
+        <v>61440</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>66560</v>
+      </c>
+      <c r="B17">
+        <v>66560</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>71680</v>
+      </c>
+      <c r="B18">
+        <v>71680</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>76800</v>
+      </c>
+      <c r="B19">
+        <v>76800</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>81920</v>
+      </c>
+      <c r="B20">
+        <v>81920</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>87040</v>
+      </c>
+      <c r="B21">
+        <v>87040</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>92160</v>
+      </c>
+      <c r="B22">
+        <v>92160</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>97280</v>
+      </c>
+      <c r="B23">
+        <v>97280</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
         <v>102400</v>
       </c>
-      <c r="B8">
+      <c r="B24">
         <v>102400</v>
       </c>
     </row>

--- a/aggregate_data.xlsx
+++ b/aggregate_data.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
   <si>
     <t>Algorithm</t>
   </si>
@@ -50,7 +50,7 @@
     <t>bubble-sort</t>
   </si>
   <si>
-    <t>i9</t>
+    <t>deck</t>
   </si>
   <si>
     <t>01_100.bin</t>
@@ -119,13 +119,25 @@
     <t>22_100K.bin</t>
   </si>
   <si>
+    <t>i9</t>
+  </si>
+  <si>
+    <t>rpi3</t>
+  </si>
+  <si>
     <t>merge-sort</t>
   </si>
   <si>
     <t>quick-sort</t>
   </si>
   <si>
+    <t>CPU Performance - deck</t>
+  </si>
+  <si>
     <t>CPU Performance - i9</t>
+  </si>
+  <si>
+    <t>CPU Performance - rpi3</t>
   </si>
   <si>
     <t>Total Allocated (bytes)</t>
@@ -143,7 +155,13 @@
     <t>Free Count</t>
   </si>
   <si>
+    <t>Memory Usage - deck</t>
+  </si>
+  <si>
     <t>Memory Usage - i9</t>
+  </si>
+  <si>
+    <t>Memory Usage - rpi3</t>
   </si>
 </sst>
 </file>
@@ -503,16 +521,16 @@
         <v>100</v>
       </c>
       <c r="E2">
-        <v>29812.7</v>
+        <v>82963.4</v>
       </c>
       <c r="F2">
-        <v>1038.8427263065378</v>
+        <v>4089.738700699594</v>
       </c>
       <c r="G2">
-        <v>28679</v>
+        <v>77781</v>
       </c>
       <c r="H2">
-        <v>32377</v>
+        <v>91802</v>
       </c>
       <c r="I2">
         <v>10</v>
@@ -532,16 +550,16 @@
         <v>1024</v>
       </c>
       <c r="E3">
-        <v>2779192.4</v>
+        <v>9827302</v>
       </c>
       <c r="F3">
-        <v>128546.64200608275</v>
+        <v>2061274.261417243</v>
       </c>
       <c r="G3">
-        <v>2590798</v>
+        <v>6928708</v>
       </c>
       <c r="H3">
-        <v>2955012</v>
+        <v>11744995</v>
       </c>
       <c r="I3">
         <v>10</v>
@@ -561,16 +579,16 @@
         <v>5120</v>
       </c>
       <c r="E4">
-        <v>71031572.7</v>
+        <v>179148840.3</v>
       </c>
       <c r="F4">
-        <v>786363.3055916394</v>
+        <v>284517.10500778334</v>
       </c>
       <c r="G4">
-        <v>69792216</v>
+        <v>178840651</v>
       </c>
       <c r="H4">
-        <v>72235488</v>
+        <v>179753087</v>
       </c>
       <c r="I4">
         <v>10</v>
@@ -590,16 +608,16 @@
         <v>10240</v>
       </c>
       <c r="E5">
-        <v>285652901.5</v>
+        <v>713713868.4</v>
       </c>
       <c r="F5">
-        <v>1754952.7315645427</v>
+        <v>834617.7062593627</v>
       </c>
       <c r="G5">
-        <v>282599499</v>
+        <v>712633828</v>
       </c>
       <c r="H5">
-        <v>288668232</v>
+        <v>715199375</v>
       </c>
       <c r="I5">
         <v>10</v>
@@ -619,16 +637,16 @@
         <v>15360</v>
       </c>
       <c r="E6">
-        <v>633566838</v>
+        <v>1610808023.7</v>
       </c>
       <c r="F6">
-        <v>2684262.222956245</v>
+        <v>1657340.6867823557</v>
       </c>
       <c r="G6">
-        <v>628642329</v>
+        <v>1607993449</v>
       </c>
       <c r="H6">
-        <v>637129164</v>
+        <v>1613432589</v>
       </c>
       <c r="I6">
         <v>10</v>
@@ -648,16 +666,16 @@
         <v>20480</v>
       </c>
       <c r="E7">
-        <v>1115376821.8</v>
+        <v>2846276388.7</v>
       </c>
       <c r="F7">
-        <v>3215632.094184495</v>
+        <v>21283699.731431656</v>
       </c>
       <c r="G7">
-        <v>1111229591</v>
+        <v>2834114037</v>
       </c>
       <c r="H7">
-        <v>1120011995</v>
+        <v>2909501239</v>
       </c>
       <c r="I7">
         <v>10</v>
@@ -677,16 +695,16 @@
         <v>25600</v>
       </c>
       <c r="E8">
-        <v>1760931144</v>
+        <v>4433773216.4</v>
       </c>
       <c r="F8">
-        <v>2228218.8275928376</v>
+        <v>5287960.699927226</v>
       </c>
       <c r="G8">
-        <v>1757362474</v>
+        <v>4425246373</v>
       </c>
       <c r="H8">
-        <v>1765914102</v>
+        <v>4444416622</v>
       </c>
       <c r="I8">
         <v>10</v>
@@ -706,16 +724,16 @@
         <v>30720</v>
       </c>
       <c r="E9">
-        <v>2595987199</v>
+        <v>6518896175</v>
       </c>
       <c r="F9">
-        <v>3541873.2244408466</v>
+        <v>12042703.848710064</v>
       </c>
       <c r="G9">
-        <v>2591252196</v>
+        <v>6504239468</v>
       </c>
       <c r="H9">
-        <v>2602386165</v>
+        <v>6542536931</v>
       </c>
       <c r="I9">
         <v>10</v>
@@ -735,16 +753,16 @@
         <v>35840</v>
       </c>
       <c r="E10">
-        <v>3461565794.5</v>
+        <v>8815969638.3</v>
       </c>
       <c r="F10">
-        <v>10153650.46859956</v>
+        <v>18147002.001699448</v>
       </c>
       <c r="G10">
-        <v>3441633539</v>
+        <v>8794981928</v>
       </c>
       <c r="H10">
-        <v>3474835531</v>
+        <v>8855848713</v>
       </c>
       <c r="I10">
         <v>10</v>
@@ -764,16 +782,16 @@
         <v>40960</v>
       </c>
       <c r="E11">
-        <v>4695119000.9</v>
+        <v>11585239740.2</v>
       </c>
       <c r="F11">
-        <v>8493014.250649782</v>
+        <v>11937238.296264147</v>
       </c>
       <c r="G11">
-        <v>4679850158</v>
+        <v>11572192805</v>
       </c>
       <c r="H11">
-        <v>4705989171</v>
+        <v>11616431365</v>
       </c>
       <c r="I11">
         <v>10</v>
@@ -793,16 +811,16 @@
         <v>46080</v>
       </c>
       <c r="E12">
-        <v>5725006478.3</v>
+        <v>14567175307.8</v>
       </c>
       <c r="F12">
-        <v>6041809.858051444</v>
+        <v>69059238.11696501</v>
       </c>
       <c r="G12">
-        <v>5713921093</v>
+        <v>14506497452</v>
       </c>
       <c r="H12">
-        <v>5734367665</v>
+        <v>14700638214</v>
       </c>
       <c r="I12">
         <v>10</v>
@@ -822,16 +840,16 @@
         <v>51200</v>
       </c>
       <c r="E13">
-        <v>7114505067.9</v>
+        <v>18091568600.6</v>
       </c>
       <c r="F13">
-        <v>17525201.977596793</v>
+        <v>23981846.203662902</v>
       </c>
       <c r="G13">
-        <v>7074168021</v>
+        <v>18071762360</v>
       </c>
       <c r="H13">
-        <v>7143276005</v>
+        <v>18159310302</v>
       </c>
       <c r="I13">
         <v>10</v>
@@ -851,16 +869,16 @@
         <v>56320</v>
       </c>
       <c r="E14">
-        <v>8592723655.9</v>
+        <v>21710078733.8</v>
       </c>
       <c r="F14">
-        <v>30407171.825969722</v>
+        <v>42846955.34210898</v>
       </c>
       <c r="G14">
-        <v>8525099803</v>
+        <v>21642457665</v>
       </c>
       <c r="H14">
-        <v>8628046431</v>
+        <v>21810656153</v>
       </c>
       <c r="I14">
         <v>10</v>
@@ -880,16 +898,16 @@
         <v>61440</v>
       </c>
       <c r="E15">
-        <v>10218618516.7</v>
+        <v>26149479114.6</v>
       </c>
       <c r="F15">
-        <v>30745343.024566714</v>
+        <v>53274079.76542069</v>
       </c>
       <c r="G15">
-        <v>10158178293</v>
+        <v>26080532209</v>
       </c>
       <c r="H15">
-        <v>10253961752</v>
+        <v>26258847316</v>
       </c>
       <c r="I15">
         <v>10</v>
@@ -909,16 +927,16 @@
         <v>66560</v>
       </c>
       <c r="E16">
-        <v>11958599692.9</v>
+        <v>30474127218.4</v>
       </c>
       <c r="F16">
-        <v>25171658.779982217</v>
+        <v>60846524.88695662</v>
       </c>
       <c r="G16">
-        <v>11892977914</v>
+        <v>30388867119</v>
       </c>
       <c r="H16">
-        <v>11989094319</v>
+        <v>30575301463</v>
       </c>
       <c r="I16">
         <v>10</v>
@@ -938,16 +956,16 @@
         <v>71680</v>
       </c>
       <c r="E17">
-        <v>13956227440.6</v>
+        <v>35765170742.2</v>
       </c>
       <c r="F17">
-        <v>22040504.045345258</v>
+        <v>39000473.511962675</v>
       </c>
       <c r="G17">
-        <v>13930206655</v>
+        <v>35698707329</v>
       </c>
       <c r="H17">
-        <v>13989960847</v>
+        <v>35848928825</v>
       </c>
       <c r="I17">
         <v>10</v>
@@ -967,16 +985,16 @@
         <v>76800</v>
       </c>
       <c r="E18">
-        <v>15974329050.1</v>
+        <v>40081367236.2</v>
       </c>
       <c r="F18">
-        <v>27462542.64984223</v>
+        <v>47603630.26636414</v>
       </c>
       <c r="G18">
-        <v>15906870743</v>
+        <v>40016859722</v>
       </c>
       <c r="H18">
-        <v>16005340097</v>
+        <v>40155849258</v>
       </c>
       <c r="I18">
         <v>10</v>
@@ -996,16 +1014,16 @@
         <v>81920</v>
       </c>
       <c r="E19">
-        <v>18222895840.3</v>
+        <v>46179802809.9</v>
       </c>
       <c r="F19">
-        <v>27783338.178174943</v>
+        <v>51431168.953458846</v>
       </c>
       <c r="G19">
-        <v>18161021068</v>
+        <v>46106170428</v>
       </c>
       <c r="H19">
-        <v>18261769127</v>
+        <v>46282603515</v>
       </c>
       <c r="I19">
         <v>10</v>
@@ -1025,16 +1043,16 @@
         <v>87040</v>
       </c>
       <c r="E20">
-        <v>20559390221.8</v>
+        <v>51951214409</v>
       </c>
       <c r="F20">
-        <v>59666519.4523001</v>
+        <v>55534843.65785769</v>
       </c>
       <c r="G20">
-        <v>20417708259</v>
+        <v>51840292439</v>
       </c>
       <c r="H20">
-        <v>20633684590</v>
+        <v>52043922185</v>
       </c>
       <c r="I20">
         <v>10</v>
@@ -1054,16 +1072,16 @@
         <v>92160</v>
       </c>
       <c r="E21">
-        <v>22971938112.2</v>
+        <v>58742794034.3</v>
       </c>
       <c r="F21">
-        <v>43803802.270309515</v>
+        <v>61714435.93323697</v>
       </c>
       <c r="G21">
-        <v>22914267550</v>
+        <v>58658945497</v>
       </c>
       <c r="H21">
-        <v>23078429638</v>
+        <v>58858551229</v>
       </c>
       <c r="I21">
         <v>10</v>
@@ -1083,16 +1101,16 @@
         <v>97280</v>
       </c>
       <c r="E22">
-        <v>25709704095.3</v>
+        <v>65638213779.5</v>
       </c>
       <c r="F22">
-        <v>38325958.63675712</v>
+        <v>69292695.21668938</v>
       </c>
       <c r="G22">
-        <v>25660233364</v>
+        <v>65537968200</v>
       </c>
       <c r="H22">
-        <v>25788692513</v>
+        <v>65781016153</v>
       </c>
       <c r="I22">
         <v>10</v>
@@ -1112,16 +1130,16 @@
         <v>102400</v>
       </c>
       <c r="E23">
-        <v>28444096006</v>
+        <v>71617023099.5</v>
       </c>
       <c r="F23">
-        <v>60268869.57973121</v>
+        <v>101499522.71723272</v>
       </c>
       <c r="G23">
-        <v>28366775205</v>
+        <v>71444662375</v>
       </c>
       <c r="H23">
-        <v>28561291857</v>
+        <v>71754877680</v>
       </c>
       <c r="I23">
         <v>10</v>
@@ -1129,10 +1147,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" t="s">
         <v>33</v>
-      </c>
-      <c r="B24" t="s">
-        <v>10</v>
       </c>
       <c r="C24" t="s">
         <v>11</v>
@@ -1141,16 +1159,16 @@
         <v>100</v>
       </c>
       <c r="E24">
-        <v>228556.6</v>
+        <v>29812.7</v>
       </c>
       <c r="F24">
-        <v>4849.292571087045</v>
+        <v>1038.8427263065378</v>
       </c>
       <c r="G24">
-        <v>222687</v>
+        <v>28679</v>
       </c>
       <c r="H24">
-        <v>236437</v>
+        <v>32377</v>
       </c>
       <c r="I24">
         <v>10</v>
@@ -1158,10 +1176,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
+        <v>9</v>
+      </c>
+      <c r="B25" t="s">
         <v>33</v>
-      </c>
-      <c r="B25" t="s">
-        <v>10</v>
       </c>
       <c r="C25" t="s">
         <v>12</v>
@@ -1170,16 +1188,16 @@
         <v>1024</v>
       </c>
       <c r="E25">
-        <v>2433976.4</v>
+        <v>2779192.4</v>
       </c>
       <c r="F25">
-        <v>273136.75681577536</v>
+        <v>128546.64200608275</v>
       </c>
       <c r="G25">
-        <v>2203836</v>
+        <v>2590798</v>
       </c>
       <c r="H25">
-        <v>2975520</v>
+        <v>2955012</v>
       </c>
       <c r="I25">
         <v>10</v>
@@ -1187,10 +1205,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
+        <v>9</v>
+      </c>
+      <c r="B26" t="s">
         <v>33</v>
-      </c>
-      <c r="B26" t="s">
-        <v>10</v>
       </c>
       <c r="C26" t="s">
         <v>13</v>
@@ -1199,16 +1217,16 @@
         <v>5120</v>
       </c>
       <c r="E26">
-        <v>12705733.4</v>
+        <v>71031572.7</v>
       </c>
       <c r="F26">
-        <v>933828.7338184877</v>
+        <v>786363.3055916394</v>
       </c>
       <c r="G26">
-        <v>11861835</v>
+        <v>69792216</v>
       </c>
       <c r="H26">
-        <v>14966122</v>
+        <v>72235488</v>
       </c>
       <c r="I26">
         <v>10</v>
@@ -1216,10 +1234,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
+        <v>9</v>
+      </c>
+      <c r="B27" t="s">
         <v>33</v>
-      </c>
-      <c r="B27" t="s">
-        <v>10</v>
       </c>
       <c r="C27" t="s">
         <v>14</v>
@@ -1228,16 +1246,16 @@
         <v>10240</v>
       </c>
       <c r="E27">
-        <v>25389107.5</v>
+        <v>285652901.5</v>
       </c>
       <c r="F27">
-        <v>347554.1741289406</v>
+        <v>1754952.7315645427</v>
       </c>
       <c r="G27">
-        <v>24993520</v>
+        <v>282599499</v>
       </c>
       <c r="H27">
-        <v>25980352</v>
+        <v>288668232</v>
       </c>
       <c r="I27">
         <v>10</v>
@@ -1245,10 +1263,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
+        <v>9</v>
+      </c>
+      <c r="B28" t="s">
         <v>33</v>
-      </c>
-      <c r="B28" t="s">
-        <v>10</v>
       </c>
       <c r="C28" t="s">
         <v>15</v>
@@ -1257,16 +1275,16 @@
         <v>15360</v>
       </c>
       <c r="E28">
-        <v>36383113.1</v>
+        <v>633566838</v>
       </c>
       <c r="F28">
-        <v>770059.4185668337</v>
+        <v>2684262.222956245</v>
       </c>
       <c r="G28">
-        <v>35528992</v>
+        <v>628642329</v>
       </c>
       <c r="H28">
-        <v>38213982</v>
+        <v>637129164</v>
       </c>
       <c r="I28">
         <v>10</v>
@@ -1274,10 +1292,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
+        <v>9</v>
+      </c>
+      <c r="B29" t="s">
         <v>33</v>
-      </c>
-      <c r="B29" t="s">
-        <v>10</v>
       </c>
       <c r="C29" t="s">
         <v>16</v>
@@ -1286,16 +1304,16 @@
         <v>20480</v>
       </c>
       <c r="E29">
-        <v>48623879.4</v>
+        <v>1115376821.8</v>
       </c>
       <c r="F29">
-        <v>520103.9238371885</v>
+        <v>3215632.094184495</v>
       </c>
       <c r="G29">
-        <v>47696952</v>
+        <v>1111229591</v>
       </c>
       <c r="H29">
-        <v>49691603</v>
+        <v>1120011995</v>
       </c>
       <c r="I29">
         <v>10</v>
@@ -1303,10 +1321,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
+        <v>9</v>
+      </c>
+      <c r="B30" t="s">
         <v>33</v>
-      </c>
-      <c r="B30" t="s">
-        <v>10</v>
       </c>
       <c r="C30" t="s">
         <v>17</v>
@@ -1315,16 +1333,16 @@
         <v>25600</v>
       </c>
       <c r="E30">
-        <v>60985352.4</v>
+        <v>1760931144</v>
       </c>
       <c r="F30">
-        <v>602557.1784213013</v>
+        <v>2228218.8275928376</v>
       </c>
       <c r="G30">
-        <v>59853310</v>
+        <v>1757362474</v>
       </c>
       <c r="H30">
-        <v>61736222</v>
+        <v>1765914102</v>
       </c>
       <c r="I30">
         <v>10</v>
@@ -1332,10 +1350,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
+        <v>9</v>
+      </c>
+      <c r="B31" t="s">
         <v>33</v>
-      </c>
-      <c r="B31" t="s">
-        <v>10</v>
       </c>
       <c r="C31" t="s">
         <v>18</v>
@@ -1344,16 +1362,16 @@
         <v>30720</v>
       </c>
       <c r="E31">
-        <v>72569335</v>
+        <v>2595987199</v>
       </c>
       <c r="F31">
-        <v>693353.8234383654</v>
+        <v>3541873.2244408466</v>
       </c>
       <c r="G31">
-        <v>71757064</v>
+        <v>2591252196</v>
       </c>
       <c r="H31">
-        <v>74374983</v>
+        <v>2602386165</v>
       </c>
       <c r="I31">
         <v>10</v>
@@ -1361,10 +1379,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
+        <v>9</v>
+      </c>
+      <c r="B32" t="s">
         <v>33</v>
-      </c>
-      <c r="B32" t="s">
-        <v>10</v>
       </c>
       <c r="C32" t="s">
         <v>19</v>
@@ -1373,16 +1391,16 @@
         <v>35840</v>
       </c>
       <c r="E32">
-        <v>85059505.7</v>
+        <v>3461565794.5</v>
       </c>
       <c r="F32">
-        <v>557854.350569582</v>
+        <v>10153650.46859956</v>
       </c>
       <c r="G32">
-        <v>84024787</v>
+        <v>3441633539</v>
       </c>
       <c r="H32">
-        <v>85910135</v>
+        <v>3474835531</v>
       </c>
       <c r="I32">
         <v>10</v>
@@ -1390,10 +1408,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
+        <v>9</v>
+      </c>
+      <c r="B33" t="s">
         <v>33</v>
-      </c>
-      <c r="B33" t="s">
-        <v>10</v>
       </c>
       <c r="C33" t="s">
         <v>20</v>
@@ -1402,16 +1420,16 @@
         <v>40960</v>
       </c>
       <c r="E33">
-        <v>96687521.5</v>
+        <v>4695119000.9</v>
       </c>
       <c r="F33">
-        <v>889042.0545714641</v>
+        <v>8493014.250649782</v>
       </c>
       <c r="G33">
-        <v>94611532</v>
+        <v>4679850158</v>
       </c>
       <c r="H33">
-        <v>98245339</v>
+        <v>4705989171</v>
       </c>
       <c r="I33">
         <v>10</v>
@@ -1419,10 +1437,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
+        <v>9</v>
+      </c>
+      <c r="B34" t="s">
         <v>33</v>
-      </c>
-      <c r="B34" t="s">
-        <v>10</v>
       </c>
       <c r="C34" t="s">
         <v>21</v>
@@ -1431,16 +1449,16 @@
         <v>46080</v>
       </c>
       <c r="E34">
-        <v>114396494.4</v>
+        <v>5725006478.3</v>
       </c>
       <c r="F34">
-        <v>945327.5546362965</v>
+        <v>6041809.858051444</v>
       </c>
       <c r="G34">
-        <v>112742319</v>
+        <v>5713921093</v>
       </c>
       <c r="H34">
-        <v>116153523</v>
+        <v>5734367665</v>
       </c>
       <c r="I34">
         <v>10</v>
@@ -1448,10 +1466,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
+        <v>9</v>
+      </c>
+      <c r="B35" t="s">
         <v>33</v>
-      </c>
-      <c r="B35" t="s">
-        <v>10</v>
       </c>
       <c r="C35" t="s">
         <v>22</v>
@@ -1460,16 +1478,16 @@
         <v>51200</v>
       </c>
       <c r="E35">
-        <v>128073697.4</v>
+        <v>7114505067.9</v>
       </c>
       <c r="F35">
-        <v>1515159.2357099764</v>
+        <v>17525201.977596793</v>
       </c>
       <c r="G35">
-        <v>126838798</v>
+        <v>7074168021</v>
       </c>
       <c r="H35">
-        <v>132419870</v>
+        <v>7143276005</v>
       </c>
       <c r="I35">
         <v>10</v>
@@ -1477,10 +1495,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
+        <v>9</v>
+      </c>
+      <c r="B36" t="s">
         <v>33</v>
-      </c>
-      <c r="B36" t="s">
-        <v>10</v>
       </c>
       <c r="C36" t="s">
         <v>23</v>
@@ -1489,16 +1507,16 @@
         <v>56320</v>
       </c>
       <c r="E36">
-        <v>133712954.7</v>
+        <v>8592723655.9</v>
       </c>
       <c r="F36">
-        <v>550642.0552932821</v>
+        <v>30407171.825969722</v>
       </c>
       <c r="G36">
-        <v>132938260</v>
+        <v>8525099803</v>
       </c>
       <c r="H36">
-        <v>134996673</v>
+        <v>8628046431</v>
       </c>
       <c r="I36">
         <v>10</v>
@@ -1506,10 +1524,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
+        <v>9</v>
+      </c>
+      <c r="B37" t="s">
         <v>33</v>
-      </c>
-      <c r="B37" t="s">
-        <v>10</v>
       </c>
       <c r="C37" t="s">
         <v>24</v>
@@ -1518,16 +1536,16 @@
         <v>61440</v>
       </c>
       <c r="E37">
-        <v>146554587.8</v>
+        <v>10218618516.7</v>
       </c>
       <c r="F37">
-        <v>677399.5802601002</v>
+        <v>30745343.024566714</v>
       </c>
       <c r="G37">
-        <v>145660508</v>
+        <v>10158178293</v>
       </c>
       <c r="H37">
-        <v>147777458</v>
+        <v>10253961752</v>
       </c>
       <c r="I37">
         <v>10</v>
@@ -1535,10 +1553,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
+        <v>9</v>
+      </c>
+      <c r="B38" t="s">
         <v>33</v>
-      </c>
-      <c r="B38" t="s">
-        <v>10</v>
       </c>
       <c r="C38" t="s">
         <v>25</v>
@@ -1547,16 +1565,16 @@
         <v>66560</v>
       </c>
       <c r="E38">
-        <v>158203280.2</v>
+        <v>11958599692.9</v>
       </c>
       <c r="F38">
-        <v>500543.7591325657</v>
+        <v>25171658.779982217</v>
       </c>
       <c r="G38">
-        <v>157138681</v>
+        <v>11892977914</v>
       </c>
       <c r="H38">
-        <v>158868899</v>
+        <v>11989094319</v>
       </c>
       <c r="I38">
         <v>10</v>
@@ -1564,10 +1582,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
+        <v>9</v>
+      </c>
+      <c r="B39" t="s">
         <v>33</v>
-      </c>
-      <c r="B39" t="s">
-        <v>10</v>
       </c>
       <c r="C39" t="s">
         <v>26</v>
@@ -1576,16 +1594,16 @@
         <v>71680</v>
       </c>
       <c r="E39">
-        <v>170926709.3</v>
+        <v>13956227440.6</v>
       </c>
       <c r="F39">
-        <v>760964.6698459857</v>
+        <v>22040504.045345258</v>
       </c>
       <c r="G39">
-        <v>169419623</v>
+        <v>13930206655</v>
       </c>
       <c r="H39">
-        <v>171838531</v>
+        <v>13989960847</v>
       </c>
       <c r="I39">
         <v>10</v>
@@ -1593,10 +1611,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
+        <v>9</v>
+      </c>
+      <c r="B40" t="s">
         <v>33</v>
-      </c>
-      <c r="B40" t="s">
-        <v>10</v>
       </c>
       <c r="C40" t="s">
         <v>27</v>
@@ -1605,16 +1623,16 @@
         <v>76800</v>
       </c>
       <c r="E40">
-        <v>180511694.5</v>
+        <v>15974329050.1</v>
       </c>
       <c r="F40">
-        <v>1006279.7828077687</v>
+        <v>27462542.64984223</v>
       </c>
       <c r="G40">
-        <v>179017786</v>
+        <v>15906870743</v>
       </c>
       <c r="H40">
-        <v>181953815</v>
+        <v>16005340097</v>
       </c>
       <c r="I40">
         <v>10</v>
@@ -1622,10 +1640,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
+        <v>9</v>
+      </c>
+      <c r="B41" t="s">
         <v>33</v>
-      </c>
-      <c r="B41" t="s">
-        <v>10</v>
       </c>
       <c r="C41" t="s">
         <v>28</v>
@@ -1634,16 +1652,16 @@
         <v>81920</v>
       </c>
       <c r="E41">
-        <v>193626605.6</v>
+        <v>18222895840.3</v>
       </c>
       <c r="F41">
-        <v>1032261.8028109148</v>
+        <v>27783338.178174943</v>
       </c>
       <c r="G41">
-        <v>191606156</v>
+        <v>18161021068</v>
       </c>
       <c r="H41">
-        <v>195508923</v>
+        <v>18261769127</v>
       </c>
       <c r="I41">
         <v>10</v>
@@ -1651,10 +1669,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
+        <v>9</v>
+      </c>
+      <c r="B42" t="s">
         <v>33</v>
-      </c>
-      <c r="B42" t="s">
-        <v>10</v>
       </c>
       <c r="C42" t="s">
         <v>29</v>
@@ -1663,16 +1681,16 @@
         <v>87040</v>
       </c>
       <c r="E42">
-        <v>208244752.5</v>
+        <v>20559390221.8</v>
       </c>
       <c r="F42">
-        <v>1673011.7109844899</v>
+        <v>59666519.4523001</v>
       </c>
       <c r="G42">
-        <v>206615841</v>
+        <v>20417708259</v>
       </c>
       <c r="H42">
-        <v>212408433</v>
+        <v>20633684590</v>
       </c>
       <c r="I42">
         <v>10</v>
@@ -1680,10 +1698,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
+        <v>9</v>
+      </c>
+      <c r="B43" t="s">
         <v>33</v>
-      </c>
-      <c r="B43" t="s">
-        <v>10</v>
       </c>
       <c r="C43" t="s">
         <v>30</v>
@@ -1692,16 +1710,16 @@
         <v>92160</v>
       </c>
       <c r="E43">
-        <v>213587381.4</v>
+        <v>22971938112.2</v>
       </c>
       <c r="F43">
-        <v>2453882.5531198187</v>
+        <v>43803802.270309515</v>
       </c>
       <c r="G43">
-        <v>211265945</v>
+        <v>22914267550</v>
       </c>
       <c r="H43">
-        <v>220015535</v>
+        <v>23078429638</v>
       </c>
       <c r="I43">
         <v>10</v>
@@ -1709,10 +1727,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
+        <v>9</v>
+      </c>
+      <c r="B44" t="s">
         <v>33</v>
-      </c>
-      <c r="B44" t="s">
-        <v>10</v>
       </c>
       <c r="C44" t="s">
         <v>31</v>
@@ -1721,16 +1739,16 @@
         <v>97280</v>
       </c>
       <c r="E44">
-        <v>230312851.5</v>
+        <v>25709704095.3</v>
       </c>
       <c r="F44">
-        <v>2113959.2718966585</v>
+        <v>38325958.63675712</v>
       </c>
       <c r="G44">
-        <v>228374205</v>
+        <v>25660233364</v>
       </c>
       <c r="H44">
-        <v>233779256</v>
+        <v>25788692513</v>
       </c>
       <c r="I44">
         <v>10</v>
@@ -1738,10 +1756,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
+        <v>9</v>
+      </c>
+      <c r="B45" t="s">
         <v>33</v>
-      </c>
-      <c r="B45" t="s">
-        <v>10</v>
       </c>
       <c r="C45" t="s">
         <v>32</v>
@@ -1750,16 +1768,16 @@
         <v>102400</v>
       </c>
       <c r="E45">
-        <v>243367823.3</v>
+        <v>28444096006</v>
       </c>
       <c r="F45">
-        <v>1448726.7810353371</v>
+        <v>60268869.57973121</v>
       </c>
       <c r="G45">
-        <v>241387010</v>
+        <v>28366775205</v>
       </c>
       <c r="H45">
-        <v>246930802</v>
+        <v>28561291857</v>
       </c>
       <c r="I45">
         <v>10</v>
@@ -1767,10 +1785,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
+        <v>9</v>
+      </c>
+      <c r="B46" t="s">
         <v>34</v>
-      </c>
-      <c r="B46" t="s">
-        <v>10</v>
       </c>
       <c r="C46" t="s">
         <v>11</v>
@@ -1779,16 +1797,16 @@
         <v>100</v>
       </c>
       <c r="E46">
-        <v>4534.7</v>
+        <v>557762.8</v>
       </c>
       <c r="F46">
-        <v>939.31337156457</v>
+        <v>49378.27960510573</v>
       </c>
       <c r="G46">
-        <v>4001</v>
+        <v>522862</v>
       </c>
       <c r="H46">
-        <v>7049</v>
+        <v>673330</v>
       </c>
       <c r="I46">
         <v>10</v>
@@ -1796,10 +1814,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
+        <v>9</v>
+      </c>
+      <c r="B47" t="s">
         <v>34</v>
-      </c>
-      <c r="B47" t="s">
-        <v>10</v>
       </c>
       <c r="C47" t="s">
         <v>12</v>
@@ -1808,16 +1826,16 @@
         <v>1024</v>
       </c>
       <c r="E47">
-        <v>71213.6</v>
+        <v>56498903.5</v>
       </c>
       <c r="F47">
-        <v>3165.8121927871844</v>
+        <v>86660.02979372902</v>
       </c>
       <c r="G47">
-        <v>67369</v>
+        <v>56349414</v>
       </c>
       <c r="H47">
-        <v>77745</v>
+        <v>56637331</v>
       </c>
       <c r="I47">
         <v>10</v>
@@ -1825,10 +1843,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
+        <v>9</v>
+      </c>
+      <c r="B48" t="s">
         <v>34</v>
-      </c>
-      <c r="B48" t="s">
-        <v>10</v>
       </c>
       <c r="C48" t="s">
         <v>13</v>
@@ -1837,16 +1855,16 @@
         <v>5120</v>
       </c>
       <c r="E48">
-        <v>383914.5</v>
+        <v>1406698940.4</v>
       </c>
       <c r="F48">
-        <v>16404.526382983448</v>
+        <v>277608.86882633995</v>
       </c>
       <c r="G48">
-        <v>369094</v>
+        <v>1406412740</v>
       </c>
       <c r="H48">
-        <v>430934</v>
+        <v>1407315713</v>
       </c>
       <c r="I48">
         <v>10</v>
@@ -1854,10 +1872,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
+        <v>9</v>
+      </c>
+      <c r="B49" t="s">
         <v>34</v>
-      </c>
-      <c r="B49" t="s">
-        <v>10</v>
       </c>
       <c r="C49" t="s">
         <v>14</v>
@@ -1866,16 +1884,16 @@
         <v>10240</v>
       </c>
       <c r="E49">
-        <v>780722.2</v>
+        <v>5578436295.1</v>
       </c>
       <c r="F49">
-        <v>15861.735817999237</v>
+        <v>819106.3273941241</v>
       </c>
       <c r="G49">
-        <v>766377</v>
+        <v>5577624331</v>
       </c>
       <c r="H49">
-        <v>819666</v>
+        <v>5579872579</v>
       </c>
       <c r="I49">
         <v>10</v>
@@ -1883,10 +1901,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
+        <v>9</v>
+      </c>
+      <c r="B50" t="s">
         <v>34</v>
-      </c>
-      <c r="B50" t="s">
-        <v>10</v>
       </c>
       <c r="C50" t="s">
         <v>15</v>
@@ -1895,16 +1913,16 @@
         <v>15360</v>
       </c>
       <c r="E50">
-        <v>1197383.1</v>
+        <v>12684706235</v>
       </c>
       <c r="F50">
-        <v>28647.41145182231</v>
+        <v>786593.0910386895</v>
       </c>
       <c r="G50">
-        <v>1163265</v>
+        <v>12683145101</v>
       </c>
       <c r="H50">
-        <v>1266258</v>
+        <v>12685513412</v>
       </c>
       <c r="I50">
         <v>10</v>
@@ -1912,10 +1930,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
+        <v>9</v>
+      </c>
+      <c r="B51" t="s">
         <v>34</v>
-      </c>
-      <c r="B51" t="s">
-        <v>10</v>
       </c>
       <c r="C51" t="s">
         <v>16</v>
@@ -1924,16 +1942,16 @@
         <v>20480</v>
       </c>
       <c r="E51">
-        <v>1617710.5</v>
+        <v>22322146682.4</v>
       </c>
       <c r="F51">
-        <v>32210.236249521673</v>
+        <v>1508084.435970493</v>
       </c>
       <c r="G51">
-        <v>1577250</v>
+        <v>22320886867</v>
       </c>
       <c r="H51">
-        <v>1689270</v>
+        <v>22326251003</v>
       </c>
       <c r="I51">
         <v>10</v>
@@ -1941,10 +1959,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
+        <v>9</v>
+      </c>
+      <c r="B52" t="s">
         <v>34</v>
-      </c>
-      <c r="B52" t="s">
-        <v>10</v>
       </c>
       <c r="C52" t="s">
         <v>17</v>
@@ -1953,16 +1971,16 @@
         <v>25600</v>
       </c>
       <c r="E52">
-        <v>2003608</v>
+        <v>35129432253.3</v>
       </c>
       <c r="F52">
-        <v>29623.824091430193</v>
+        <v>13663869.868057922</v>
       </c>
       <c r="G52">
-        <v>1973822</v>
+        <v>35120849330</v>
       </c>
       <c r="H52">
-        <v>2076675</v>
+        <v>35164606138</v>
       </c>
       <c r="I52">
         <v>10</v>
@@ -1970,10 +1988,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
+        <v>9</v>
+      </c>
+      <c r="B53" t="s">
         <v>34</v>
-      </c>
-      <c r="B53" t="s">
-        <v>10</v>
       </c>
       <c r="C53" t="s">
         <v>18</v>
@@ -1982,16 +2000,16 @@
         <v>30720</v>
       </c>
       <c r="E53">
-        <v>2446195.5</v>
+        <v>50811537498.2</v>
       </c>
       <c r="F53">
-        <v>32816.35155909322</v>
+        <v>2750914.6207847237</v>
       </c>
       <c r="G53">
-        <v>2412819</v>
+        <v>50808710891</v>
       </c>
       <c r="H53">
-        <v>2513114</v>
+        <v>50815717848</v>
       </c>
       <c r="I53">
         <v>10</v>
@@ -1999,10 +2017,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
+        <v>9</v>
+      </c>
+      <c r="B54" t="s">
         <v>34</v>
-      </c>
-      <c r="B54" t="s">
-        <v>10</v>
       </c>
       <c r="C54" t="s">
         <v>19</v>
@@ -2011,16 +2029,16 @@
         <v>35840</v>
       </c>
       <c r="E54">
-        <v>2859693.4</v>
+        <v>69105582394.1</v>
       </c>
       <c r="F54">
-        <v>26447.14919306049</v>
+        <v>2514229.228712985</v>
       </c>
       <c r="G54">
-        <v>2811834</v>
+        <v>69101874012</v>
       </c>
       <c r="H54">
-        <v>2899011</v>
+        <v>69109777277</v>
       </c>
       <c r="I54">
         <v>10</v>
@@ -2028,10 +2046,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
+        <v>9</v>
+      </c>
+      <c r="B55" t="s">
         <v>34</v>
-      </c>
-      <c r="B55" t="s">
-        <v>10</v>
       </c>
       <c r="C55" t="s">
         <v>20</v>
@@ -2040,16 +2058,16 @@
         <v>40960</v>
       </c>
       <c r="E55">
-        <v>3316331.1</v>
+        <v>90692851024.3</v>
       </c>
       <c r="F55">
-        <v>41823.75758214463</v>
+        <v>2109611.070176304</v>
       </c>
       <c r="G55">
-        <v>3241486</v>
+        <v>90689505103</v>
       </c>
       <c r="H55">
-        <v>3375923</v>
+        <v>90697338797</v>
       </c>
       <c r="I55">
         <v>10</v>
@@ -2057,10 +2075,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
+        <v>9</v>
+      </c>
+      <c r="B56" t="s">
         <v>34</v>
-      </c>
-      <c r="B56" t="s">
-        <v>10</v>
       </c>
       <c r="C56" t="s">
         <v>21</v>
@@ -2069,16 +2087,16 @@
         <v>46080</v>
       </c>
       <c r="E56">
-        <v>3721145.5</v>
+        <v>114442607094.5</v>
       </c>
       <c r="F56">
-        <v>39265.9371930685</v>
+        <v>4613690.178731906</v>
       </c>
       <c r="G56">
-        <v>3664271</v>
+        <v>114435965442</v>
       </c>
       <c r="H56">
-        <v>3796694</v>
+        <v>114453047312</v>
       </c>
       <c r="I56">
         <v>10</v>
@@ -2086,10 +2104,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
+        <v>9</v>
+      </c>
+      <c r="B57" t="s">
         <v>34</v>
-      </c>
-      <c r="B57" t="s">
-        <v>10</v>
       </c>
       <c r="C57" t="s">
         <v>22</v>
@@ -2098,16 +2116,16 @@
         <v>51200</v>
       </c>
       <c r="E57">
-        <v>4190075.6</v>
+        <v>141530964374.9</v>
       </c>
       <c r="F57">
-        <v>81707.70218186289</v>
+        <v>5680083.992185212</v>
       </c>
       <c r="G57">
-        <v>4073204</v>
+        <v>141525015167</v>
       </c>
       <c r="H57">
-        <v>4334729</v>
+        <v>141542970873</v>
       </c>
       <c r="I57">
         <v>10</v>
@@ -2115,10 +2133,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
+        <v>9</v>
+      </c>
+      <c r="B58" t="s">
         <v>34</v>
-      </c>
-      <c r="B58" t="s">
-        <v>10</v>
       </c>
       <c r="C58" t="s">
         <v>23</v>
@@ -2127,16 +2145,16 @@
         <v>56320</v>
       </c>
       <c r="E58">
-        <v>4569048</v>
+        <v>170701367450.8</v>
       </c>
       <c r="F58">
-        <v>37896.64476441153</v>
+        <v>6489901.998310649</v>
       </c>
       <c r="G58">
-        <v>4519449</v>
+        <v>170692680172</v>
       </c>
       <c r="H58">
-        <v>4635083</v>
+        <v>170714312546</v>
       </c>
       <c r="I58">
         <v>10</v>
@@ -2144,10 +2162,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
+        <v>9</v>
+      </c>
+      <c r="B59" t="s">
         <v>34</v>
-      </c>
-      <c r="B59" t="s">
-        <v>10</v>
       </c>
       <c r="C59" t="s">
         <v>24</v>
@@ -2156,16 +2174,16 @@
         <v>61440</v>
       </c>
       <c r="E59">
-        <v>5005579.9</v>
+        <v>203820136377.7</v>
       </c>
       <c r="F59">
-        <v>42001.91094569389</v>
+        <v>6501354.223700845</v>
       </c>
       <c r="G59">
-        <v>4951043</v>
+        <v>203808169055</v>
       </c>
       <c r="H59">
-        <v>5088751</v>
+        <v>203830521490</v>
       </c>
       <c r="I59">
         <v>10</v>
@@ -2173,10 +2191,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
+        <v>9</v>
+      </c>
+      <c r="B60" t="s">
         <v>34</v>
-      </c>
-      <c r="B60" t="s">
-        <v>10</v>
       </c>
       <c r="C60" t="s">
         <v>25</v>
@@ -2185,16 +2203,16 @@
         <v>66560</v>
       </c>
       <c r="E60">
-        <v>5410891.7</v>
+        <v>239084713971.6</v>
       </c>
       <c r="F60">
-        <v>25549.463920207796</v>
+        <v>35338724.83126185</v>
       </c>
       <c r="G60">
-        <v>5363804</v>
+        <v>239019559105</v>
       </c>
       <c r="H60">
-        <v>5441963</v>
+        <v>239121298540</v>
       </c>
       <c r="I60">
         <v>10</v>
@@ -2202,10 +2220,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
+        <v>9</v>
+      </c>
+      <c r="B61" t="s">
         <v>34</v>
-      </c>
-      <c r="B61" t="s">
-        <v>10</v>
       </c>
       <c r="C61" t="s">
         <v>26</v>
@@ -2214,16 +2232,16 @@
         <v>71680</v>
       </c>
       <c r="E61">
-        <v>5874645.8</v>
+        <v>277618517241</v>
       </c>
       <c r="F61">
-        <v>31047.71521320047</v>
+        <v>28148848.283475317</v>
       </c>
       <c r="G61">
-        <v>5825408</v>
+        <v>277588582604</v>
       </c>
       <c r="H61">
-        <v>5913905</v>
+        <v>277673143662</v>
       </c>
       <c r="I61">
         <v>10</v>
@@ -2231,10 +2249,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
+        <v>9</v>
+      </c>
+      <c r="B62" t="s">
         <v>34</v>
-      </c>
-      <c r="B62" t="s">
-        <v>10</v>
       </c>
       <c r="C62" t="s">
         <v>27</v>
@@ -2243,16 +2261,16 @@
         <v>76800</v>
       </c>
       <c r="E62">
-        <v>6301448.9</v>
+        <v>317605707827.7</v>
       </c>
       <c r="F62">
-        <v>64832.65532808294</v>
+        <v>25935068.476712953</v>
       </c>
       <c r="G62">
-        <v>6195366</v>
+        <v>317542017033</v>
       </c>
       <c r="H62">
-        <v>6403857</v>
+        <v>317641236144</v>
       </c>
       <c r="I62">
         <v>10</v>
@@ -2260,10 +2278,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
+        <v>9</v>
+      </c>
+      <c r="B63" t="s">
         <v>34</v>
-      </c>
-      <c r="B63" t="s">
-        <v>10</v>
       </c>
       <c r="C63" t="s">
         <v>28</v>
@@ -2272,16 +2290,16 @@
         <v>81920</v>
       </c>
       <c r="E63">
-        <v>6677578.1</v>
+        <v>361211297263.7</v>
       </c>
       <c r="F63">
-        <v>66910.3650467549</v>
+        <v>16448616.409208236</v>
       </c>
       <c r="G63">
-        <v>6579023</v>
+        <v>361183964017</v>
       </c>
       <c r="H63">
-        <v>6812683</v>
+        <v>361231010546</v>
       </c>
       <c r="I63">
         <v>10</v>
@@ -2289,10 +2307,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
+        <v>9</v>
+      </c>
+      <c r="B64" t="s">
         <v>34</v>
-      </c>
-      <c r="B64" t="s">
-        <v>10</v>
       </c>
       <c r="C64" t="s">
         <v>29</v>
@@ -2301,16 +2319,16 @@
         <v>87040</v>
       </c>
       <c r="E64">
-        <v>7194367</v>
+        <v>408896660387.3</v>
       </c>
       <c r="F64">
-        <v>80967.88520765501</v>
+        <v>30422156.248221766</v>
       </c>
       <c r="G64">
-        <v>7081896</v>
+        <v>408842913035</v>
       </c>
       <c r="H64">
-        <v>7329831</v>
+        <v>408940684567</v>
       </c>
       <c r="I64">
         <v>10</v>
@@ -2318,10 +2336,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
+        <v>9</v>
+      </c>
+      <c r="B65" t="s">
         <v>34</v>
-      </c>
-      <c r="B65" t="s">
-        <v>10</v>
       </c>
       <c r="C65" t="s">
         <v>30</v>
@@ -2330,16 +2348,16 @@
         <v>92160</v>
       </c>
       <c r="E65">
-        <v>7653507.4</v>
+        <v>457546233055.2</v>
       </c>
       <c r="F65">
-        <v>120579.58204704478</v>
+        <v>65248901.709299654</v>
       </c>
       <c r="G65">
-        <v>7563230</v>
+        <v>457421548516</v>
       </c>
       <c r="H65">
-        <v>7997624</v>
+        <v>457649413151</v>
       </c>
       <c r="I65">
         <v>10</v>
@@ -2347,10 +2365,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
+        <v>9</v>
+      </c>
+      <c r="B66" t="s">
         <v>34</v>
-      </c>
-      <c r="B66" t="s">
-        <v>10</v>
       </c>
       <c r="C66" t="s">
         <v>31</v>
@@ -2359,16 +2377,16 @@
         <v>97280</v>
       </c>
       <c r="E66">
-        <v>8008970.7</v>
+        <v>511226726172.7</v>
       </c>
       <c r="F66">
-        <v>71971.43140864992</v>
+        <v>12171957.239852449</v>
       </c>
       <c r="G66">
-        <v>7887500</v>
+        <v>511206986852</v>
       </c>
       <c r="H66">
-        <v>8117298</v>
+        <v>511252613488</v>
       </c>
       <c r="I66">
         <v>10</v>
@@ -2376,10 +2394,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
+        <v>9</v>
+      </c>
+      <c r="B67" t="s">
         <v>34</v>
-      </c>
-      <c r="B67" t="s">
-        <v>10</v>
       </c>
       <c r="C67" t="s">
         <v>32</v>
@@ -2388,18 +2406,3846 @@
         <v>102400</v>
       </c>
       <c r="E67">
+        <v>566110304268.6</v>
+      </c>
+      <c r="F67">
+        <v>19571071.039531726</v>
+      </c>
+      <c r="G67">
+        <v>566084558500</v>
+      </c>
+      <c r="H67">
+        <v>566155959828</v>
+      </c>
+      <c r="I67">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>35</v>
+      </c>
+      <c r="B68" t="s">
+        <v>10</v>
+      </c>
+      <c r="C68" t="s">
+        <v>11</v>
+      </c>
+      <c r="D68">
+        <v>100</v>
+      </c>
+      <c r="E68">
+        <v>928269.2</v>
+      </c>
+      <c r="F68">
+        <v>25960.25534851304</v>
+      </c>
+      <c r="G68">
+        <v>906987</v>
+      </c>
+      <c r="H68">
+        <v>990179</v>
+      </c>
+      <c r="I68">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>35</v>
+      </c>
+      <c r="B69" t="s">
+        <v>10</v>
+      </c>
+      <c r="C69" t="s">
+        <v>12</v>
+      </c>
+      <c r="D69">
+        <v>1024</v>
+      </c>
+      <c r="E69">
+        <v>10278739.1</v>
+      </c>
+      <c r="F69">
+        <v>506185.6066253662</v>
+      </c>
+      <c r="G69">
+        <v>9708150</v>
+      </c>
+      <c r="H69">
+        <v>11201087</v>
+      </c>
+      <c r="I69">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>35</v>
+      </c>
+      <c r="B70" t="s">
+        <v>10</v>
+      </c>
+      <c r="C70" t="s">
+        <v>13</v>
+      </c>
+      <c r="D70">
+        <v>5120</v>
+      </c>
+      <c r="E70">
+        <v>51183088.8</v>
+      </c>
+      <c r="F70">
+        <v>325929.0182661863</v>
+      </c>
+      <c r="G70">
+        <v>50766749</v>
+      </c>
+      <c r="H70">
+        <v>51825819</v>
+      </c>
+      <c r="I70">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>35</v>
+      </c>
+      <c r="B71" t="s">
+        <v>10</v>
+      </c>
+      <c r="C71" t="s">
+        <v>14</v>
+      </c>
+      <c r="D71">
+        <v>10240</v>
+      </c>
+      <c r="E71">
+        <v>101877702.7</v>
+      </c>
+      <c r="F71">
+        <v>475124.46097944694</v>
+      </c>
+      <c r="G71">
+        <v>100830375</v>
+      </c>
+      <c r="H71">
+        <v>102599568</v>
+      </c>
+      <c r="I71">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>35</v>
+      </c>
+      <c r="B72" t="s">
+        <v>10</v>
+      </c>
+      <c r="C72" t="s">
+        <v>15</v>
+      </c>
+      <c r="D72">
+        <v>15360</v>
+      </c>
+      <c r="E72">
+        <v>152962324.1</v>
+      </c>
+      <c r="F72">
+        <v>910198.7173682953</v>
+      </c>
+      <c r="G72">
+        <v>151956961</v>
+      </c>
+      <c r="H72">
+        <v>154887555</v>
+      </c>
+      <c r="I72">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>35</v>
+      </c>
+      <c r="B73" t="s">
+        <v>10</v>
+      </c>
+      <c r="C73" t="s">
+        <v>16</v>
+      </c>
+      <c r="D73">
+        <v>20480</v>
+      </c>
+      <c r="E73">
+        <v>204053053.6</v>
+      </c>
+      <c r="F73">
+        <v>832890.3157591881</v>
+      </c>
+      <c r="G73">
+        <v>203189888</v>
+      </c>
+      <c r="H73">
+        <v>206203293</v>
+      </c>
+      <c r="I73">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>35</v>
+      </c>
+      <c r="B74" t="s">
+        <v>10</v>
+      </c>
+      <c r="C74" t="s">
+        <v>17</v>
+      </c>
+      <c r="D74">
+        <v>25600</v>
+      </c>
+      <c r="E74">
+        <v>254840481.7</v>
+      </c>
+      <c r="F74">
+        <v>1112704.362623788</v>
+      </c>
+      <c r="G74">
+        <v>253766202</v>
+      </c>
+      <c r="H74">
+        <v>257837617</v>
+      </c>
+      <c r="I74">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>35</v>
+      </c>
+      <c r="B75" t="s">
+        <v>10</v>
+      </c>
+      <c r="C75" t="s">
+        <v>18</v>
+      </c>
+      <c r="D75">
+        <v>30720</v>
+      </c>
+      <c r="E75">
+        <v>306111723.1</v>
+      </c>
+      <c r="F75">
+        <v>1425920.4702321552</v>
+      </c>
+      <c r="G75">
+        <v>304543429</v>
+      </c>
+      <c r="H75">
+        <v>308753267</v>
+      </c>
+      <c r="I75">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>35</v>
+      </c>
+      <c r="B76" t="s">
+        <v>10</v>
+      </c>
+      <c r="C76" t="s">
+        <v>19</v>
+      </c>
+      <c r="D76">
+        <v>35840</v>
+      </c>
+      <c r="E76">
+        <v>357054966</v>
+      </c>
+      <c r="F76">
+        <v>1168862.3880232438</v>
+      </c>
+      <c r="G76">
+        <v>355134742</v>
+      </c>
+      <c r="H76">
+        <v>358629628</v>
+      </c>
+      <c r="I76">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>35</v>
+      </c>
+      <c r="B77" t="s">
+        <v>10</v>
+      </c>
+      <c r="C77" t="s">
+        <v>20</v>
+      </c>
+      <c r="D77">
+        <v>40960</v>
+      </c>
+      <c r="E77">
+        <v>407498526.5</v>
+      </c>
+      <c r="F77">
+        <v>1997074.998634165</v>
+      </c>
+      <c r="G77">
+        <v>405344357</v>
+      </c>
+      <c r="H77">
+        <v>411715125</v>
+      </c>
+      <c r="I77">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>35</v>
+      </c>
+      <c r="B78" t="s">
+        <v>10</v>
+      </c>
+      <c r="C78" t="s">
+        <v>21</v>
+      </c>
+      <c r="D78">
+        <v>46080</v>
+      </c>
+      <c r="E78">
+        <v>461330246.7</v>
+      </c>
+      <c r="F78">
+        <v>2638334.184774781</v>
+      </c>
+      <c r="G78">
+        <v>458951216</v>
+      </c>
+      <c r="H78">
+        <v>466810011</v>
+      </c>
+      <c r="I78">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>35</v>
+      </c>
+      <c r="B79" t="s">
+        <v>10</v>
+      </c>
+      <c r="C79" t="s">
+        <v>22</v>
+      </c>
+      <c r="D79">
+        <v>51200</v>
+      </c>
+      <c r="E79">
+        <v>506856371.5</v>
+      </c>
+      <c r="F79">
+        <v>1707803.4000637338</v>
+      </c>
+      <c r="G79">
+        <v>503607934</v>
+      </c>
+      <c r="H79">
+        <v>509297890</v>
+      </c>
+      <c r="I79">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>35</v>
+      </c>
+      <c r="B80" t="s">
+        <v>10</v>
+      </c>
+      <c r="C80" t="s">
+        <v>23</v>
+      </c>
+      <c r="D80">
+        <v>56320</v>
+      </c>
+      <c r="E80">
+        <v>563467551.2</v>
+      </c>
+      <c r="F80">
+        <v>1643005.0325011665</v>
+      </c>
+      <c r="G80">
+        <v>561863435</v>
+      </c>
+      <c r="H80">
+        <v>567655685</v>
+      </c>
+      <c r="I80">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>35</v>
+      </c>
+      <c r="B81" t="s">
+        <v>10</v>
+      </c>
+      <c r="C81" t="s">
+        <v>24</v>
+      </c>
+      <c r="D81">
+        <v>61440</v>
+      </c>
+      <c r="E81">
+        <v>613243337.9</v>
+      </c>
+      <c r="F81">
+        <v>8303035.412570399</v>
+      </c>
+      <c r="G81">
+        <v>608897558</v>
+      </c>
+      <c r="H81">
+        <v>637910175</v>
+      </c>
+      <c r="I81">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>35</v>
+      </c>
+      <c r="B82" t="s">
+        <v>10</v>
+      </c>
+      <c r="C82" t="s">
+        <v>25</v>
+      </c>
+      <c r="D82">
+        <v>66560</v>
+      </c>
+      <c r="E82">
+        <v>661409185.9</v>
+      </c>
+      <c r="F82">
+        <v>1072844.0102610863</v>
+      </c>
+      <c r="G82">
+        <v>659240191</v>
+      </c>
+      <c r="H82">
+        <v>663137541</v>
+      </c>
+      <c r="I82">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>35</v>
+      </c>
+      <c r="B83" t="s">
+        <v>10</v>
+      </c>
+      <c r="C83" t="s">
+        <v>26</v>
+      </c>
+      <c r="D83">
+        <v>71680</v>
+      </c>
+      <c r="E83">
+        <v>713264838.8</v>
+      </c>
+      <c r="F83">
+        <v>2620358.296302275</v>
+      </c>
+      <c r="G83">
+        <v>708280786</v>
+      </c>
+      <c r="H83">
+        <v>716349847</v>
+      </c>
+      <c r="I83">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>35</v>
+      </c>
+      <c r="B84" t="s">
+        <v>10</v>
+      </c>
+      <c r="C84" t="s">
+        <v>27</v>
+      </c>
+      <c r="D84">
+        <v>76800</v>
+      </c>
+      <c r="E84">
+        <v>762123602</v>
+      </c>
+      <c r="F84">
+        <v>2953730.26626488</v>
+      </c>
+      <c r="G84">
+        <v>758133946</v>
+      </c>
+      <c r="H84">
+        <v>767229819</v>
+      </c>
+      <c r="I84">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>35</v>
+      </c>
+      <c r="B85" t="s">
+        <v>10</v>
+      </c>
+      <c r="C85" t="s">
+        <v>28</v>
+      </c>
+      <c r="D85">
+        <v>81920</v>
+      </c>
+      <c r="E85">
+        <v>819105618.2</v>
+      </c>
+      <c r="F85">
+        <v>12274702.698276253</v>
+      </c>
+      <c r="G85">
+        <v>809668989</v>
+      </c>
+      <c r="H85">
+        <v>842288308</v>
+      </c>
+      <c r="I85">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s">
+        <v>35</v>
+      </c>
+      <c r="B86" t="s">
+        <v>10</v>
+      </c>
+      <c r="C86" t="s">
+        <v>29</v>
+      </c>
+      <c r="D86">
+        <v>87040</v>
+      </c>
+      <c r="E86">
+        <v>864279368.6</v>
+      </c>
+      <c r="F86">
+        <v>4324960.844515294</v>
+      </c>
+      <c r="G86">
+        <v>859716189</v>
+      </c>
+      <c r="H86">
+        <v>872839288</v>
+      </c>
+      <c r="I86">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s">
+        <v>35</v>
+      </c>
+      <c r="B87" t="s">
+        <v>10</v>
+      </c>
+      <c r="C87" t="s">
+        <v>30</v>
+      </c>
+      <c r="D87">
+        <v>92160</v>
+      </c>
+      <c r="E87">
+        <v>918100522.6</v>
+      </c>
+      <c r="F87">
+        <v>2508676.4800159945</v>
+      </c>
+      <c r="G87">
+        <v>914308081</v>
+      </c>
+      <c r="H87">
+        <v>922515336</v>
+      </c>
+      <c r="I87">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s">
+        <v>35</v>
+      </c>
+      <c r="B88" t="s">
+        <v>10</v>
+      </c>
+      <c r="C88" t="s">
+        <v>31</v>
+      </c>
+      <c r="D88">
+        <v>97280</v>
+      </c>
+      <c r="E88">
+        <v>971643274.9</v>
+      </c>
+      <c r="F88">
+        <v>3617193.901653945</v>
+      </c>
+      <c r="G88">
+        <v>965541383</v>
+      </c>
+      <c r="H88">
+        <v>976187667</v>
+      </c>
+      <c r="I88">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s">
+        <v>35</v>
+      </c>
+      <c r="B89" t="s">
+        <v>10</v>
+      </c>
+      <c r="C89" t="s">
+        <v>32</v>
+      </c>
+      <c r="D89">
+        <v>102400</v>
+      </c>
+      <c r="E89">
+        <v>1025923888.2</v>
+      </c>
+      <c r="F89">
+        <v>2426049.1676918175</v>
+      </c>
+      <c r="G89">
+        <v>1019419762</v>
+      </c>
+      <c r="H89">
+        <v>1028538926</v>
+      </c>
+      <c r="I89">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s">
+        <v>35</v>
+      </c>
+      <c r="B90" t="s">
+        <v>33</v>
+      </c>
+      <c r="C90" t="s">
+        <v>11</v>
+      </c>
+      <c r="D90">
+        <v>100</v>
+      </c>
+      <c r="E90">
+        <v>228556.6</v>
+      </c>
+      <c r="F90">
+        <v>4849.292571087045</v>
+      </c>
+      <c r="G90">
+        <v>222687</v>
+      </c>
+      <c r="H90">
+        <v>236437</v>
+      </c>
+      <c r="I90">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s">
+        <v>35</v>
+      </c>
+      <c r="B91" t="s">
+        <v>33</v>
+      </c>
+      <c r="C91" t="s">
+        <v>12</v>
+      </c>
+      <c r="D91">
+        <v>1024</v>
+      </c>
+      <c r="E91">
+        <v>2433976.4</v>
+      </c>
+      <c r="F91">
+        <v>273136.75681577536</v>
+      </c>
+      <c r="G91">
+        <v>2203836</v>
+      </c>
+      <c r="H91">
+        <v>2975520</v>
+      </c>
+      <c r="I91">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s">
+        <v>35</v>
+      </c>
+      <c r="B92" t="s">
+        <v>33</v>
+      </c>
+      <c r="C92" t="s">
+        <v>13</v>
+      </c>
+      <c r="D92">
+        <v>5120</v>
+      </c>
+      <c r="E92">
+        <v>12705733.4</v>
+      </c>
+      <c r="F92">
+        <v>933828.7338184877</v>
+      </c>
+      <c r="G92">
+        <v>11861835</v>
+      </c>
+      <c r="H92">
+        <v>14966122</v>
+      </c>
+      <c r="I92">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s">
+        <v>35</v>
+      </c>
+      <c r="B93" t="s">
+        <v>33</v>
+      </c>
+      <c r="C93" t="s">
+        <v>14</v>
+      </c>
+      <c r="D93">
+        <v>10240</v>
+      </c>
+      <c r="E93">
+        <v>25389107.5</v>
+      </c>
+      <c r="F93">
+        <v>347554.1741289406</v>
+      </c>
+      <c r="G93">
+        <v>24993520</v>
+      </c>
+      <c r="H93">
+        <v>25980352</v>
+      </c>
+      <c r="I93">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s">
+        <v>35</v>
+      </c>
+      <c r="B94" t="s">
+        <v>33</v>
+      </c>
+      <c r="C94" t="s">
+        <v>15</v>
+      </c>
+      <c r="D94">
+        <v>15360</v>
+      </c>
+      <c r="E94">
+        <v>36383113.1</v>
+      </c>
+      <c r="F94">
+        <v>770059.4185668337</v>
+      </c>
+      <c r="G94">
+        <v>35528992</v>
+      </c>
+      <c r="H94">
+        <v>38213982</v>
+      </c>
+      <c r="I94">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s">
+        <v>35</v>
+      </c>
+      <c r="B95" t="s">
+        <v>33</v>
+      </c>
+      <c r="C95" t="s">
+        <v>16</v>
+      </c>
+      <c r="D95">
+        <v>20480</v>
+      </c>
+      <c r="E95">
+        <v>48623879.4</v>
+      </c>
+      <c r="F95">
+        <v>520103.9238371885</v>
+      </c>
+      <c r="G95">
+        <v>47696952</v>
+      </c>
+      <c r="H95">
+        <v>49691603</v>
+      </c>
+      <c r="I95">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s">
+        <v>35</v>
+      </c>
+      <c r="B96" t="s">
+        <v>33</v>
+      </c>
+      <c r="C96" t="s">
+        <v>17</v>
+      </c>
+      <c r="D96">
+        <v>25600</v>
+      </c>
+      <c r="E96">
+        <v>60985352.4</v>
+      </c>
+      <c r="F96">
+        <v>602557.1784213013</v>
+      </c>
+      <c r="G96">
+        <v>59853310</v>
+      </c>
+      <c r="H96">
+        <v>61736222</v>
+      </c>
+      <c r="I96">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s">
+        <v>35</v>
+      </c>
+      <c r="B97" t="s">
+        <v>33</v>
+      </c>
+      <c r="C97" t="s">
+        <v>18</v>
+      </c>
+      <c r="D97">
+        <v>30720</v>
+      </c>
+      <c r="E97">
+        <v>72569335</v>
+      </c>
+      <c r="F97">
+        <v>693353.8234383654</v>
+      </c>
+      <c r="G97">
+        <v>71757064</v>
+      </c>
+      <c r="H97">
+        <v>74374983</v>
+      </c>
+      <c r="I97">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s">
+        <v>35</v>
+      </c>
+      <c r="B98" t="s">
+        <v>33</v>
+      </c>
+      <c r="C98" t="s">
+        <v>19</v>
+      </c>
+      <c r="D98">
+        <v>35840</v>
+      </c>
+      <c r="E98">
+        <v>85059505.7</v>
+      </c>
+      <c r="F98">
+        <v>557854.350569582</v>
+      </c>
+      <c r="G98">
+        <v>84024787</v>
+      </c>
+      <c r="H98">
+        <v>85910135</v>
+      </c>
+      <c r="I98">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s">
+        <v>35</v>
+      </c>
+      <c r="B99" t="s">
+        <v>33</v>
+      </c>
+      <c r="C99" t="s">
+        <v>20</v>
+      </c>
+      <c r="D99">
+        <v>40960</v>
+      </c>
+      <c r="E99">
+        <v>96687521.5</v>
+      </c>
+      <c r="F99">
+        <v>889042.0545714641</v>
+      </c>
+      <c r="G99">
+        <v>94611532</v>
+      </c>
+      <c r="H99">
+        <v>98245339</v>
+      </c>
+      <c r="I99">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s">
+        <v>35</v>
+      </c>
+      <c r="B100" t="s">
+        <v>33</v>
+      </c>
+      <c r="C100" t="s">
+        <v>21</v>
+      </c>
+      <c r="D100">
+        <v>46080</v>
+      </c>
+      <c r="E100">
+        <v>114396494.4</v>
+      </c>
+      <c r="F100">
+        <v>945327.5546362965</v>
+      </c>
+      <c r="G100">
+        <v>112742319</v>
+      </c>
+      <c r="H100">
+        <v>116153523</v>
+      </c>
+      <c r="I100">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s">
+        <v>35</v>
+      </c>
+      <c r="B101" t="s">
+        <v>33</v>
+      </c>
+      <c r="C101" t="s">
+        <v>22</v>
+      </c>
+      <c r="D101">
+        <v>51200</v>
+      </c>
+      <c r="E101">
+        <v>128073697.4</v>
+      </c>
+      <c r="F101">
+        <v>1515159.2357099764</v>
+      </c>
+      <c r="G101">
+        <v>126838798</v>
+      </c>
+      <c r="H101">
+        <v>132419870</v>
+      </c>
+      <c r="I101">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s">
+        <v>35</v>
+      </c>
+      <c r="B102" t="s">
+        <v>33</v>
+      </c>
+      <c r="C102" t="s">
+        <v>23</v>
+      </c>
+      <c r="D102">
+        <v>56320</v>
+      </c>
+      <c r="E102">
+        <v>133712954.7</v>
+      </c>
+      <c r="F102">
+        <v>550642.0552932821</v>
+      </c>
+      <c r="G102">
+        <v>132938260</v>
+      </c>
+      <c r="H102">
+        <v>134996673</v>
+      </c>
+      <c r="I102">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s">
+        <v>35</v>
+      </c>
+      <c r="B103" t="s">
+        <v>33</v>
+      </c>
+      <c r="C103" t="s">
+        <v>24</v>
+      </c>
+      <c r="D103">
+        <v>61440</v>
+      </c>
+      <c r="E103">
+        <v>146554587.8</v>
+      </c>
+      <c r="F103">
+        <v>677399.5802601002</v>
+      </c>
+      <c r="G103">
+        <v>145660508</v>
+      </c>
+      <c r="H103">
+        <v>147777458</v>
+      </c>
+      <c r="I103">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s">
+        <v>35</v>
+      </c>
+      <c r="B104" t="s">
+        <v>33</v>
+      </c>
+      <c r="C104" t="s">
+        <v>25</v>
+      </c>
+      <c r="D104">
+        <v>66560</v>
+      </c>
+      <c r="E104">
+        <v>158203280.2</v>
+      </c>
+      <c r="F104">
+        <v>500543.7591325657</v>
+      </c>
+      <c r="G104">
+        <v>157138681</v>
+      </c>
+      <c r="H104">
+        <v>158868899</v>
+      </c>
+      <c r="I104">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s">
+        <v>35</v>
+      </c>
+      <c r="B105" t="s">
+        <v>33</v>
+      </c>
+      <c r="C105" t="s">
+        <v>26</v>
+      </c>
+      <c r="D105">
+        <v>71680</v>
+      </c>
+      <c r="E105">
+        <v>170926709.3</v>
+      </c>
+      <c r="F105">
+        <v>760964.6698459857</v>
+      </c>
+      <c r="G105">
+        <v>169419623</v>
+      </c>
+      <c r="H105">
+        <v>171838531</v>
+      </c>
+      <c r="I105">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s">
+        <v>35</v>
+      </c>
+      <c r="B106" t="s">
+        <v>33</v>
+      </c>
+      <c r="C106" t="s">
+        <v>27</v>
+      </c>
+      <c r="D106">
+        <v>76800</v>
+      </c>
+      <c r="E106">
+        <v>180511694.5</v>
+      </c>
+      <c r="F106">
+        <v>1006279.7828077687</v>
+      </c>
+      <c r="G106">
+        <v>179017786</v>
+      </c>
+      <c r="H106">
+        <v>181953815</v>
+      </c>
+      <c r="I106">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s">
+        <v>35</v>
+      </c>
+      <c r="B107" t="s">
+        <v>33</v>
+      </c>
+      <c r="C107" t="s">
+        <v>28</v>
+      </c>
+      <c r="D107">
+        <v>81920</v>
+      </c>
+      <c r="E107">
+        <v>193626605.6</v>
+      </c>
+      <c r="F107">
+        <v>1032261.8028109148</v>
+      </c>
+      <c r="G107">
+        <v>191606156</v>
+      </c>
+      <c r="H107">
+        <v>195508923</v>
+      </c>
+      <c r="I107">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s">
+        <v>35</v>
+      </c>
+      <c r="B108" t="s">
+        <v>33</v>
+      </c>
+      <c r="C108" t="s">
+        <v>29</v>
+      </c>
+      <c r="D108">
+        <v>87040</v>
+      </c>
+      <c r="E108">
+        <v>208244752.5</v>
+      </c>
+      <c r="F108">
+        <v>1673011.7109844899</v>
+      </c>
+      <c r="G108">
+        <v>206615841</v>
+      </c>
+      <c r="H108">
+        <v>212408433</v>
+      </c>
+      <c r="I108">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s">
+        <v>35</v>
+      </c>
+      <c r="B109" t="s">
+        <v>33</v>
+      </c>
+      <c r="C109" t="s">
+        <v>30</v>
+      </c>
+      <c r="D109">
+        <v>92160</v>
+      </c>
+      <c r="E109">
+        <v>213587381.4</v>
+      </c>
+      <c r="F109">
+        <v>2453882.5531198187</v>
+      </c>
+      <c r="G109">
+        <v>211265945</v>
+      </c>
+      <c r="H109">
+        <v>220015535</v>
+      </c>
+      <c r="I109">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s">
+        <v>35</v>
+      </c>
+      <c r="B110" t="s">
+        <v>33</v>
+      </c>
+      <c r="C110" t="s">
+        <v>31</v>
+      </c>
+      <c r="D110">
+        <v>97280</v>
+      </c>
+      <c r="E110">
+        <v>230312851.5</v>
+      </c>
+      <c r="F110">
+        <v>2113959.2718966585</v>
+      </c>
+      <c r="G110">
+        <v>228374205</v>
+      </c>
+      <c r="H110">
+        <v>233779256</v>
+      </c>
+      <c r="I110">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s">
+        <v>35</v>
+      </c>
+      <c r="B111" t="s">
+        <v>33</v>
+      </c>
+      <c r="C111" t="s">
+        <v>32</v>
+      </c>
+      <c r="D111">
+        <v>102400</v>
+      </c>
+      <c r="E111">
+        <v>243367823.3</v>
+      </c>
+      <c r="F111">
+        <v>1448726.7810353371</v>
+      </c>
+      <c r="G111">
+        <v>241387010</v>
+      </c>
+      <c r="H111">
+        <v>246930802</v>
+      </c>
+      <c r="I111">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s">
+        <v>35</v>
+      </c>
+      <c r="B112" t="s">
+        <v>34</v>
+      </c>
+      <c r="C112" t="s">
+        <v>11</v>
+      </c>
+      <c r="D112">
+        <v>100</v>
+      </c>
+      <c r="E112">
+        <v>3288990.9</v>
+      </c>
+      <c r="F112">
+        <v>164217.49508529837</v>
+      </c>
+      <c r="G112">
+        <v>3143967</v>
+      </c>
+      <c r="H112">
+        <v>3679272</v>
+      </c>
+      <c r="I112">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s">
+        <v>35</v>
+      </c>
+      <c r="B113" t="s">
+        <v>34</v>
+      </c>
+      <c r="C113" t="s">
+        <v>12</v>
+      </c>
+      <c r="D113">
+        <v>1024</v>
+      </c>
+      <c r="E113">
+        <v>33342812.4</v>
+      </c>
+      <c r="F113">
+        <v>310863.28306578763</v>
+      </c>
+      <c r="G113">
+        <v>32816262</v>
+      </c>
+      <c r="H113">
+        <v>33837498</v>
+      </c>
+      <c r="I113">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s">
+        <v>35</v>
+      </c>
+      <c r="B114" t="s">
+        <v>34</v>
+      </c>
+      <c r="C114" t="s">
+        <v>13</v>
+      </c>
+      <c r="D114">
+        <v>5120</v>
+      </c>
+      <c r="E114">
+        <v>165331042.4</v>
+      </c>
+      <c r="F114">
+        <v>724403.8031875867</v>
+      </c>
+      <c r="G114">
+        <v>164162247</v>
+      </c>
+      <c r="H114">
+        <v>166435807</v>
+      </c>
+      <c r="I114">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s">
+        <v>35</v>
+      </c>
+      <c r="B115" t="s">
+        <v>34</v>
+      </c>
+      <c r="C115" t="s">
+        <v>14</v>
+      </c>
+      <c r="D115">
+        <v>10240</v>
+      </c>
+      <c r="E115">
+        <v>330034105.4</v>
+      </c>
+      <c r="F115">
+        <v>821614.592814076</v>
+      </c>
+      <c r="G115">
+        <v>328401604</v>
+      </c>
+      <c r="H115">
+        <v>331079702</v>
+      </c>
+      <c r="I115">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s">
+        <v>35</v>
+      </c>
+      <c r="B116" t="s">
+        <v>34</v>
+      </c>
+      <c r="C116" t="s">
+        <v>15</v>
+      </c>
+      <c r="D116">
+        <v>15360</v>
+      </c>
+      <c r="E116">
+        <v>490022168.3</v>
+      </c>
+      <c r="F116">
+        <v>1115301.2706879743</v>
+      </c>
+      <c r="G116">
+        <v>488715626</v>
+      </c>
+      <c r="H116">
+        <v>492167779</v>
+      </c>
+      <c r="I116">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s">
+        <v>35</v>
+      </c>
+      <c r="B117" t="s">
+        <v>34</v>
+      </c>
+      <c r="C117" t="s">
+        <v>16</v>
+      </c>
+      <c r="D117">
+        <v>20480</v>
+      </c>
+      <c r="E117">
+        <v>661321424.9</v>
+      </c>
+      <c r="F117">
+        <v>2675608.078471974</v>
+      </c>
+      <c r="G117">
+        <v>657536959</v>
+      </c>
+      <c r="H117">
+        <v>665896180</v>
+      </c>
+      <c r="I117">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s">
+        <v>35</v>
+      </c>
+      <c r="B118" t="s">
+        <v>34</v>
+      </c>
+      <c r="C118" t="s">
+        <v>17</v>
+      </c>
+      <c r="D118">
+        <v>25600</v>
+      </c>
+      <c r="E118">
+        <v>830303817</v>
+      </c>
+      <c r="F118">
+        <v>1759438.501212816</v>
+      </c>
+      <c r="G118">
+        <v>827154219</v>
+      </c>
+      <c r="H118">
+        <v>832925015</v>
+      </c>
+      <c r="I118">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s">
+        <v>35</v>
+      </c>
+      <c r="B119" t="s">
+        <v>34</v>
+      </c>
+      <c r="C119" t="s">
+        <v>18</v>
+      </c>
+      <c r="D119">
+        <v>30720</v>
+      </c>
+      <c r="E119">
+        <v>992089360.5</v>
+      </c>
+      <c r="F119">
+        <v>1246302.8622103257</v>
+      </c>
+      <c r="G119">
+        <v>990980820</v>
+      </c>
+      <c r="H119">
+        <v>994557163</v>
+      </c>
+      <c r="I119">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s">
+        <v>35</v>
+      </c>
+      <c r="B120" t="s">
+        <v>34</v>
+      </c>
+      <c r="C120" t="s">
+        <v>19</v>
+      </c>
+      <c r="D120">
+        <v>35840</v>
+      </c>
+      <c r="E120">
+        <v>1166714536.8</v>
+      </c>
+      <c r="F120">
+        <v>2979007.821605536</v>
+      </c>
+      <c r="G120">
+        <v>1161982258</v>
+      </c>
+      <c r="H120">
+        <v>1171425127</v>
+      </c>
+      <c r="I120">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s">
+        <v>35</v>
+      </c>
+      <c r="B121" t="s">
+        <v>34</v>
+      </c>
+      <c r="C121" t="s">
+        <v>20</v>
+      </c>
+      <c r="D121">
+        <v>40960</v>
+      </c>
+      <c r="E121">
+        <v>1333042823.5</v>
+      </c>
+      <c r="F121">
+        <v>2930781.8093097704</v>
+      </c>
+      <c r="G121">
+        <v>1330012735</v>
+      </c>
+      <c r="H121">
+        <v>1340629897</v>
+      </c>
+      <c r="I121">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s">
+        <v>35</v>
+      </c>
+      <c r="B122" t="s">
+        <v>34</v>
+      </c>
+      <c r="C122" t="s">
+        <v>21</v>
+      </c>
+      <c r="D122">
+        <v>46080</v>
+      </c>
+      <c r="E122">
+        <v>1490738197.6</v>
+      </c>
+      <c r="F122">
+        <v>2806297.732629102</v>
+      </c>
+      <c r="G122">
+        <v>1487854442</v>
+      </c>
+      <c r="H122">
+        <v>1495503674</v>
+      </c>
+      <c r="I122">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s">
+        <v>35</v>
+      </c>
+      <c r="B123" t="s">
+        <v>34</v>
+      </c>
+      <c r="C123" t="s">
+        <v>22</v>
+      </c>
+      <c r="D123">
+        <v>51200</v>
+      </c>
+      <c r="E123">
+        <v>1684184290.5</v>
+      </c>
+      <c r="F123">
+        <v>2658359.2138217986</v>
+      </c>
+      <c r="G123">
+        <v>1679298171</v>
+      </c>
+      <c r="H123">
+        <v>1688598311</v>
+      </c>
+      <c r="I123">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s">
+        <v>35</v>
+      </c>
+      <c r="B124" t="s">
+        <v>34</v>
+      </c>
+      <c r="C124" t="s">
+        <v>23</v>
+      </c>
+      <c r="D124">
+        <v>56320</v>
+      </c>
+      <c r="E124">
+        <v>1823900667</v>
+      </c>
+      <c r="F124">
+        <v>3257296.987629897</v>
+      </c>
+      <c r="G124">
+        <v>1820656999</v>
+      </c>
+      <c r="H124">
+        <v>1829923659</v>
+      </c>
+      <c r="I124">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s">
+        <v>35</v>
+      </c>
+      <c r="B125" t="s">
+        <v>34</v>
+      </c>
+      <c r="C125" t="s">
+        <v>24</v>
+      </c>
+      <c r="D125">
+        <v>61440</v>
+      </c>
+      <c r="E125">
+        <v>1985824590.8</v>
+      </c>
+      <c r="F125">
+        <v>4372567.708163976</v>
+      </c>
+      <c r="G125">
+        <v>1975746721</v>
+      </c>
+      <c r="H125">
+        <v>1991202161</v>
+      </c>
+      <c r="I125">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s">
+        <v>35</v>
+      </c>
+      <c r="B126" t="s">
+        <v>34</v>
+      </c>
+      <c r="C126" t="s">
+        <v>25</v>
+      </c>
+      <c r="D126">
+        <v>66560</v>
+      </c>
+      <c r="E126">
+        <v>2201072592.7</v>
+      </c>
+      <c r="F126">
+        <v>5015208.29647623</v>
+      </c>
+      <c r="G126">
+        <v>2186559599</v>
+      </c>
+      <c r="H126">
+        <v>2204861579</v>
+      </c>
+      <c r="I126">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s">
+        <v>35</v>
+      </c>
+      <c r="B127" t="s">
+        <v>34</v>
+      </c>
+      <c r="C127" t="s">
+        <v>26</v>
+      </c>
+      <c r="D127">
+        <v>71680</v>
+      </c>
+      <c r="E127">
+        <v>2360389873.2</v>
+      </c>
+      <c r="F127">
+        <v>3219659.0039353794</v>
+      </c>
+      <c r="G127">
+        <v>2355624459</v>
+      </c>
+      <c r="H127">
+        <v>2368247943</v>
+      </c>
+      <c r="I127">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s">
+        <v>35</v>
+      </c>
+      <c r="B128" t="s">
+        <v>34</v>
+      </c>
+      <c r="C128" t="s">
+        <v>27</v>
+      </c>
+      <c r="D128">
+        <v>76800</v>
+      </c>
+      <c r="E128">
+        <v>2518559857.4</v>
+      </c>
+      <c r="F128">
+        <v>7940726.301028819</v>
+      </c>
+      <c r="G128">
+        <v>2497317002</v>
+      </c>
+      <c r="H128">
+        <v>2526192243</v>
+      </c>
+      <c r="I128">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s">
+        <v>35</v>
+      </c>
+      <c r="B129" t="s">
+        <v>34</v>
+      </c>
+      <c r="C129" t="s">
+        <v>28</v>
+      </c>
+      <c r="D129">
+        <v>81920</v>
+      </c>
+      <c r="E129">
+        <v>2676024061.2</v>
+      </c>
+      <c r="F129">
+        <v>5351232.397860474</v>
+      </c>
+      <c r="G129">
+        <v>2661376557</v>
+      </c>
+      <c r="H129">
+        <v>2682808174</v>
+      </c>
+      <c r="I129">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s">
+        <v>35</v>
+      </c>
+      <c r="B130" t="s">
+        <v>34</v>
+      </c>
+      <c r="C130" t="s">
+        <v>29</v>
+      </c>
+      <c r="D130">
+        <v>87040</v>
+      </c>
+      <c r="E130">
+        <v>2842473626</v>
+      </c>
+      <c r="F130">
+        <v>5303739.535610775</v>
+      </c>
+      <c r="G130">
+        <v>2828356036</v>
+      </c>
+      <c r="H130">
+        <v>2849921699</v>
+      </c>
+      <c r="I130">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s">
+        <v>35</v>
+      </c>
+      <c r="B131" t="s">
+        <v>34</v>
+      </c>
+      <c r="C131" t="s">
+        <v>30</v>
+      </c>
+      <c r="D131">
+        <v>92160</v>
+      </c>
+      <c r="E131">
+        <v>3008711128.9</v>
+      </c>
+      <c r="F131">
+        <v>5454208.221043645</v>
+      </c>
+      <c r="G131">
+        <v>2993429067</v>
+      </c>
+      <c r="H131">
+        <v>3013083962</v>
+      </c>
+      <c r="I131">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s">
+        <v>35</v>
+      </c>
+      <c r="B132" t="s">
+        <v>34</v>
+      </c>
+      <c r="C132" t="s">
+        <v>31</v>
+      </c>
+      <c r="D132">
+        <v>97280</v>
+      </c>
+      <c r="E132">
+        <v>3163661340.3</v>
+      </c>
+      <c r="F132">
+        <v>7387866.970561584</v>
+      </c>
+      <c r="G132">
+        <v>3142594134</v>
+      </c>
+      <c r="H132">
+        <v>3169764730</v>
+      </c>
+      <c r="I132">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s">
+        <v>35</v>
+      </c>
+      <c r="B133" t="s">
+        <v>34</v>
+      </c>
+      <c r="C133" t="s">
+        <v>32</v>
+      </c>
+      <c r="D133">
+        <v>102400</v>
+      </c>
+      <c r="E133">
+        <v>3336970656.1</v>
+      </c>
+      <c r="F133">
+        <v>2338561.367507017</v>
+      </c>
+      <c r="G133">
+        <v>3332361932</v>
+      </c>
+      <c r="H133">
+        <v>3340034980</v>
+      </c>
+      <c r="I133">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s">
+        <v>36</v>
+      </c>
+      <c r="B134" t="s">
+        <v>10</v>
+      </c>
+      <c r="C134" t="s">
+        <v>11</v>
+      </c>
+      <c r="D134">
+        <v>100</v>
+      </c>
+      <c r="E134">
+        <v>10055.1</v>
+      </c>
+      <c r="F134">
+        <v>1058.9684084050855</v>
+      </c>
+      <c r="G134">
+        <v>8510</v>
+      </c>
+      <c r="H134">
+        <v>12490</v>
+      </c>
+      <c r="I134">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s">
+        <v>36</v>
+      </c>
+      <c r="B135" t="s">
+        <v>10</v>
+      </c>
+      <c r="C135" t="s">
+        <v>12</v>
+      </c>
+      <c r="D135">
+        <v>1024</v>
+      </c>
+      <c r="E135">
+        <v>123599.4</v>
+      </c>
+      <c r="F135">
+        <v>12298.382968504437</v>
+      </c>
+      <c r="G135">
+        <v>117722</v>
+      </c>
+      <c r="H135">
+        <v>159933</v>
+      </c>
+      <c r="I135">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s">
+        <v>36</v>
+      </c>
+      <c r="B136" t="s">
+        <v>10</v>
+      </c>
+      <c r="C136" t="s">
+        <v>13</v>
+      </c>
+      <c r="D136">
+        <v>5120</v>
+      </c>
+      <c r="E136">
+        <v>685812.9</v>
+      </c>
+      <c r="F136">
+        <v>24012.127571083744</v>
+      </c>
+      <c r="G136">
+        <v>664063</v>
+      </c>
+      <c r="H136">
+        <v>741524</v>
+      </c>
+      <c r="I136">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s">
+        <v>36</v>
+      </c>
+      <c r="B137" t="s">
+        <v>10</v>
+      </c>
+      <c r="C137" t="s">
+        <v>14</v>
+      </c>
+      <c r="D137">
+        <v>10240</v>
+      </c>
+      <c r="E137">
+        <v>1437986.3</v>
+      </c>
+      <c r="F137">
+        <v>32812.23187181878</v>
+      </c>
+      <c r="G137">
+        <v>1406206</v>
+      </c>
+      <c r="H137">
+        <v>1517898</v>
+      </c>
+      <c r="I137">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s">
+        <v>36</v>
+      </c>
+      <c r="B138" t="s">
+        <v>10</v>
+      </c>
+      <c r="C138" t="s">
+        <v>15</v>
+      </c>
+      <c r="D138">
+        <v>15360</v>
+      </c>
+      <c r="E138">
+        <v>2230143.3</v>
+      </c>
+      <c r="F138">
+        <v>43504.3645374806</v>
+      </c>
+      <c r="G138">
+        <v>2188440</v>
+      </c>
+      <c r="H138">
+        <v>2328783</v>
+      </c>
+      <c r="I138">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s">
+        <v>36</v>
+      </c>
+      <c r="B139" t="s">
+        <v>10</v>
+      </c>
+      <c r="C139" t="s">
+        <v>16</v>
+      </c>
+      <c r="D139">
+        <v>20480</v>
+      </c>
+      <c r="E139">
+        <v>2994569.5</v>
+      </c>
+      <c r="F139">
+        <v>47805.34868244347</v>
+      </c>
+      <c r="G139">
+        <v>2940065</v>
+      </c>
+      <c r="H139">
+        <v>3076417</v>
+      </c>
+      <c r="I139">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s">
+        <v>36</v>
+      </c>
+      <c r="B140" t="s">
+        <v>10</v>
+      </c>
+      <c r="C140" t="s">
+        <v>17</v>
+      </c>
+      <c r="D140">
+        <v>25600</v>
+      </c>
+      <c r="E140">
+        <v>3790005.1</v>
+      </c>
+      <c r="F140">
+        <v>58045.87008297835</v>
+      </c>
+      <c r="G140">
+        <v>3740609</v>
+      </c>
+      <c r="H140">
+        <v>3946843</v>
+      </c>
+      <c r="I140">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s">
+        <v>36</v>
+      </c>
+      <c r="B141" t="s">
+        <v>10</v>
+      </c>
+      <c r="C141" t="s">
+        <v>18</v>
+      </c>
+      <c r="D141">
+        <v>30720</v>
+      </c>
+      <c r="E141">
+        <v>4622930.7</v>
+      </c>
+      <c r="F141">
+        <v>27560.527143180698</v>
+      </c>
+      <c r="G141">
+        <v>4591575</v>
+      </c>
+      <c r="H141">
+        <v>4684767</v>
+      </c>
+      <c r="I141">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s">
+        <v>36</v>
+      </c>
+      <c r="B142" t="s">
+        <v>10</v>
+      </c>
+      <c r="C142" t="s">
+        <v>19</v>
+      </c>
+      <c r="D142">
+        <v>35840</v>
+      </c>
+      <c r="E142">
+        <v>5436622.9</v>
+      </c>
+      <c r="F142">
+        <v>77997.62263229565</v>
+      </c>
+      <c r="G142">
+        <v>5348310</v>
+      </c>
+      <c r="H142">
+        <v>5628754</v>
+      </c>
+      <c r="I142">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s">
+        <v>36</v>
+      </c>
+      <c r="B143" t="s">
+        <v>10</v>
+      </c>
+      <c r="C143" t="s">
+        <v>20</v>
+      </c>
+      <c r="D143">
+        <v>40960</v>
+      </c>
+      <c r="E143">
+        <v>6394459.4</v>
+      </c>
+      <c r="F143">
+        <v>90065.01371587082</v>
+      </c>
+      <c r="G143">
+        <v>6296576</v>
+      </c>
+      <c r="H143">
+        <v>6570102</v>
+      </c>
+      <c r="I143">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s">
+        <v>36</v>
+      </c>
+      <c r="B144" t="s">
+        <v>10</v>
+      </c>
+      <c r="C144" t="s">
+        <v>21</v>
+      </c>
+      <c r="D144">
+        <v>46080</v>
+      </c>
+      <c r="E144">
+        <v>7079063</v>
+      </c>
+      <c r="F144">
+        <v>94182.44946379341</v>
+      </c>
+      <c r="G144">
+        <v>7020750</v>
+      </c>
+      <c r="H144">
+        <v>7358366</v>
+      </c>
+      <c r="I144">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s">
+        <v>36</v>
+      </c>
+      <c r="B145" t="s">
+        <v>10</v>
+      </c>
+      <c r="C145" t="s">
+        <v>22</v>
+      </c>
+      <c r="D145">
+        <v>51200</v>
+      </c>
+      <c r="E145">
+        <v>7912422.3</v>
+      </c>
+      <c r="F145">
+        <v>47330.80277166235</v>
+      </c>
+      <c r="G145">
+        <v>7853786</v>
+      </c>
+      <c r="H145">
+        <v>8026358</v>
+      </c>
+      <c r="I145">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s">
+        <v>36</v>
+      </c>
+      <c r="B146" t="s">
+        <v>10</v>
+      </c>
+      <c r="C146" t="s">
+        <v>23</v>
+      </c>
+      <c r="D146">
+        <v>56320</v>
+      </c>
+      <c r="E146">
+        <v>8786584.6</v>
+      </c>
+      <c r="F146">
+        <v>42062.439613507915</v>
+      </c>
+      <c r="G146">
+        <v>8744972</v>
+      </c>
+      <c r="H146">
+        <v>8866054</v>
+      </c>
+      <c r="I146">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s">
+        <v>36</v>
+      </c>
+      <c r="B147" t="s">
+        <v>10</v>
+      </c>
+      <c r="C147" t="s">
+        <v>24</v>
+      </c>
+      <c r="D147">
+        <v>61440</v>
+      </c>
+      <c r="E147">
+        <v>9717019</v>
+      </c>
+      <c r="F147">
+        <v>96277.8778640244</v>
+      </c>
+      <c r="G147">
+        <v>9581318</v>
+      </c>
+      <c r="H147">
+        <v>9861412</v>
+      </c>
+      <c r="I147">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s">
+        <v>36</v>
+      </c>
+      <c r="B148" t="s">
+        <v>10</v>
+      </c>
+      <c r="C148" t="s">
+        <v>25</v>
+      </c>
+      <c r="D148">
+        <v>66560</v>
+      </c>
+      <c r="E148">
+        <v>10567925.4</v>
+      </c>
+      <c r="F148">
+        <v>89496.40358830069</v>
+      </c>
+      <c r="G148">
+        <v>10450303</v>
+      </c>
+      <c r="H148">
+        <v>10720428</v>
+      </c>
+      <c r="I148">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s">
+        <v>36</v>
+      </c>
+      <c r="B149" t="s">
+        <v>10</v>
+      </c>
+      <c r="C149" t="s">
+        <v>26</v>
+      </c>
+      <c r="D149">
+        <v>71680</v>
+      </c>
+      <c r="E149">
+        <v>11444969.8</v>
+      </c>
+      <c r="F149">
+        <v>83970.67658510321</v>
+      </c>
+      <c r="G149">
+        <v>11299989</v>
+      </c>
+      <c r="H149">
+        <v>11619485</v>
+      </c>
+      <c r="I149">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s">
+        <v>36</v>
+      </c>
+      <c r="B150" t="s">
+        <v>10</v>
+      </c>
+      <c r="C150" t="s">
+        <v>27</v>
+      </c>
+      <c r="D150">
+        <v>76800</v>
+      </c>
+      <c r="E150">
+        <v>12222383.2</v>
+      </c>
+      <c r="F150">
+        <v>85743.85168022252</v>
+      </c>
+      <c r="G150">
+        <v>12073174</v>
+      </c>
+      <c r="H150">
+        <v>12371999</v>
+      </c>
+      <c r="I150">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s">
+        <v>36</v>
+      </c>
+      <c r="B151" t="s">
+        <v>10</v>
+      </c>
+      <c r="C151" t="s">
+        <v>28</v>
+      </c>
+      <c r="D151">
+        <v>81920</v>
+      </c>
+      <c r="E151">
+        <v>12978764.1</v>
+      </c>
+      <c r="F151">
+        <v>76727.50033390896</v>
+      </c>
+      <c r="G151">
+        <v>12851847</v>
+      </c>
+      <c r="H151">
+        <v>13125263</v>
+      </c>
+      <c r="I151">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s">
+        <v>36</v>
+      </c>
+      <c r="B152" t="s">
+        <v>10</v>
+      </c>
+      <c r="C152" t="s">
+        <v>29</v>
+      </c>
+      <c r="D152">
+        <v>87040</v>
+      </c>
+      <c r="E152">
+        <v>13897361.3</v>
+      </c>
+      <c r="F152">
+        <v>138497.1894321686</v>
+      </c>
+      <c r="G152">
+        <v>13771945</v>
+      </c>
+      <c r="H152">
+        <v>14208323</v>
+      </c>
+      <c r="I152">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s">
+        <v>36</v>
+      </c>
+      <c r="B153" t="s">
+        <v>10</v>
+      </c>
+      <c r="C153" t="s">
+        <v>30</v>
+      </c>
+      <c r="D153">
+        <v>92160</v>
+      </c>
+      <c r="E153">
+        <v>14789982.7</v>
+      </c>
+      <c r="F153">
+        <v>33147.399427556906</v>
+      </c>
+      <c r="G153">
+        <v>14754313</v>
+      </c>
+      <c r="H153">
+        <v>14865205</v>
+      </c>
+      <c r="I153">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s">
+        <v>36</v>
+      </c>
+      <c r="B154" t="s">
+        <v>10</v>
+      </c>
+      <c r="C154" t="s">
+        <v>31</v>
+      </c>
+      <c r="D154">
+        <v>97280</v>
+      </c>
+      <c r="E154">
+        <v>15417517.6</v>
+      </c>
+      <c r="F154">
+        <v>68052.89279112242</v>
+      </c>
+      <c r="G154">
+        <v>15331293</v>
+      </c>
+      <c r="H154">
+        <v>15564928</v>
+      </c>
+      <c r="I154">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s">
+        <v>36</v>
+      </c>
+      <c r="B155" t="s">
+        <v>10</v>
+      </c>
+      <c r="C155" t="s">
+        <v>32</v>
+      </c>
+      <c r="D155">
+        <v>102400</v>
+      </c>
+      <c r="E155">
+        <v>16565274.4</v>
+      </c>
+      <c r="F155">
+        <v>248431.13569486418</v>
+      </c>
+      <c r="G155">
+        <v>16403863</v>
+      </c>
+      <c r="H155">
+        <v>17287749</v>
+      </c>
+      <c r="I155">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s">
+        <v>36</v>
+      </c>
+      <c r="B156" t="s">
+        <v>33</v>
+      </c>
+      <c r="C156" t="s">
+        <v>11</v>
+      </c>
+      <c r="D156">
+        <v>100</v>
+      </c>
+      <c r="E156">
+        <v>4534.7</v>
+      </c>
+      <c r="F156">
+        <v>939.31337156457</v>
+      </c>
+      <c r="G156">
+        <v>4001</v>
+      </c>
+      <c r="H156">
+        <v>7049</v>
+      </c>
+      <c r="I156">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s">
+        <v>36</v>
+      </c>
+      <c r="B157" t="s">
+        <v>33</v>
+      </c>
+      <c r="C157" t="s">
+        <v>12</v>
+      </c>
+      <c r="D157">
+        <v>1024</v>
+      </c>
+      <c r="E157">
+        <v>71213.6</v>
+      </c>
+      <c r="F157">
+        <v>3165.8121927871844</v>
+      </c>
+      <c r="G157">
+        <v>67369</v>
+      </c>
+      <c r="H157">
+        <v>77745</v>
+      </c>
+      <c r="I157">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s">
+        <v>36</v>
+      </c>
+      <c r="B158" t="s">
+        <v>33</v>
+      </c>
+      <c r="C158" t="s">
+        <v>13</v>
+      </c>
+      <c r="D158">
+        <v>5120</v>
+      </c>
+      <c r="E158">
+        <v>383914.5</v>
+      </c>
+      <c r="F158">
+        <v>16404.526382983448</v>
+      </c>
+      <c r="G158">
+        <v>369094</v>
+      </c>
+      <c r="H158">
+        <v>430934</v>
+      </c>
+      <c r="I158">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s">
+        <v>36</v>
+      </c>
+      <c r="B159" t="s">
+        <v>33</v>
+      </c>
+      <c r="C159" t="s">
+        <v>14</v>
+      </c>
+      <c r="D159">
+        <v>10240</v>
+      </c>
+      <c r="E159">
+        <v>780722.2</v>
+      </c>
+      <c r="F159">
+        <v>15861.735817999237</v>
+      </c>
+      <c r="G159">
+        <v>766377</v>
+      </c>
+      <c r="H159">
+        <v>819666</v>
+      </c>
+      <c r="I159">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s">
+        <v>36</v>
+      </c>
+      <c r="B160" t="s">
+        <v>33</v>
+      </c>
+      <c r="C160" t="s">
+        <v>15</v>
+      </c>
+      <c r="D160">
+        <v>15360</v>
+      </c>
+      <c r="E160">
+        <v>1197383.1</v>
+      </c>
+      <c r="F160">
+        <v>28647.41145182231</v>
+      </c>
+      <c r="G160">
+        <v>1163265</v>
+      </c>
+      <c r="H160">
+        <v>1266258</v>
+      </c>
+      <c r="I160">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s">
+        <v>36</v>
+      </c>
+      <c r="B161" t="s">
+        <v>33</v>
+      </c>
+      <c r="C161" t="s">
+        <v>16</v>
+      </c>
+      <c r="D161">
+        <v>20480</v>
+      </c>
+      <c r="E161">
+        <v>1617710.5</v>
+      </c>
+      <c r="F161">
+        <v>32210.236249521673</v>
+      </c>
+      <c r="G161">
+        <v>1577250</v>
+      </c>
+      <c r="H161">
+        <v>1689270</v>
+      </c>
+      <c r="I161">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s">
+        <v>36</v>
+      </c>
+      <c r="B162" t="s">
+        <v>33</v>
+      </c>
+      <c r="C162" t="s">
+        <v>17</v>
+      </c>
+      <c r="D162">
+        <v>25600</v>
+      </c>
+      <c r="E162">
+        <v>2003608</v>
+      </c>
+      <c r="F162">
+        <v>29623.824091430193</v>
+      </c>
+      <c r="G162">
+        <v>1973822</v>
+      </c>
+      <c r="H162">
+        <v>2076675</v>
+      </c>
+      <c r="I162">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s">
+        <v>36</v>
+      </c>
+      <c r="B163" t="s">
+        <v>33</v>
+      </c>
+      <c r="C163" t="s">
+        <v>18</v>
+      </c>
+      <c r="D163">
+        <v>30720</v>
+      </c>
+      <c r="E163">
+        <v>2446195.5</v>
+      </c>
+      <c r="F163">
+        <v>32816.35155909322</v>
+      </c>
+      <c r="G163">
+        <v>2412819</v>
+      </c>
+      <c r="H163">
+        <v>2513114</v>
+      </c>
+      <c r="I163">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s">
+        <v>36</v>
+      </c>
+      <c r="B164" t="s">
+        <v>33</v>
+      </c>
+      <c r="C164" t="s">
+        <v>19</v>
+      </c>
+      <c r="D164">
+        <v>35840</v>
+      </c>
+      <c r="E164">
+        <v>2859693.4</v>
+      </c>
+      <c r="F164">
+        <v>26447.14919306049</v>
+      </c>
+      <c r="G164">
+        <v>2811834</v>
+      </c>
+      <c r="H164">
+        <v>2899011</v>
+      </c>
+      <c r="I164">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s">
+        <v>36</v>
+      </c>
+      <c r="B165" t="s">
+        <v>33</v>
+      </c>
+      <c r="C165" t="s">
+        <v>20</v>
+      </c>
+      <c r="D165">
+        <v>40960</v>
+      </c>
+      <c r="E165">
+        <v>3316331.1</v>
+      </c>
+      <c r="F165">
+        <v>41823.75758214463</v>
+      </c>
+      <c r="G165">
+        <v>3241486</v>
+      </c>
+      <c r="H165">
+        <v>3375923</v>
+      </c>
+      <c r="I165">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s">
+        <v>36</v>
+      </c>
+      <c r="B166" t="s">
+        <v>33</v>
+      </c>
+      <c r="C166" t="s">
+        <v>21</v>
+      </c>
+      <c r="D166">
+        <v>46080</v>
+      </c>
+      <c r="E166">
+        <v>3721145.5</v>
+      </c>
+      <c r="F166">
+        <v>39265.9371930685</v>
+      </c>
+      <c r="G166">
+        <v>3664271</v>
+      </c>
+      <c r="H166">
+        <v>3796694</v>
+      </c>
+      <c r="I166">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s">
+        <v>36</v>
+      </c>
+      <c r="B167" t="s">
+        <v>33</v>
+      </c>
+      <c r="C167" t="s">
+        <v>22</v>
+      </c>
+      <c r="D167">
+        <v>51200</v>
+      </c>
+      <c r="E167">
+        <v>4190075.6</v>
+      </c>
+      <c r="F167">
+        <v>81707.70218186289</v>
+      </c>
+      <c r="G167">
+        <v>4073204</v>
+      </c>
+      <c r="H167">
+        <v>4334729</v>
+      </c>
+      <c r="I167">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s">
+        <v>36</v>
+      </c>
+      <c r="B168" t="s">
+        <v>33</v>
+      </c>
+      <c r="C168" t="s">
+        <v>23</v>
+      </c>
+      <c r="D168">
+        <v>56320</v>
+      </c>
+      <c r="E168">
+        <v>4569048</v>
+      </c>
+      <c r="F168">
+        <v>37896.64476441153</v>
+      </c>
+      <c r="G168">
+        <v>4519449</v>
+      </c>
+      <c r="H168">
+        <v>4635083</v>
+      </c>
+      <c r="I168">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s">
+        <v>36</v>
+      </c>
+      <c r="B169" t="s">
+        <v>33</v>
+      </c>
+      <c r="C169" t="s">
+        <v>24</v>
+      </c>
+      <c r="D169">
+        <v>61440</v>
+      </c>
+      <c r="E169">
+        <v>5005579.9</v>
+      </c>
+      <c r="F169">
+        <v>42001.91094569389</v>
+      </c>
+      <c r="G169">
+        <v>4951043</v>
+      </c>
+      <c r="H169">
+        <v>5088751</v>
+      </c>
+      <c r="I169">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="s">
+        <v>36</v>
+      </c>
+      <c r="B170" t="s">
+        <v>33</v>
+      </c>
+      <c r="C170" t="s">
+        <v>25</v>
+      </c>
+      <c r="D170">
+        <v>66560</v>
+      </c>
+      <c r="E170">
+        <v>5410891.7</v>
+      </c>
+      <c r="F170">
+        <v>25549.463920207796</v>
+      </c>
+      <c r="G170">
+        <v>5363804</v>
+      </c>
+      <c r="H170">
+        <v>5441963</v>
+      </c>
+      <c r="I170">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="s">
+        <v>36</v>
+      </c>
+      <c r="B171" t="s">
+        <v>33</v>
+      </c>
+      <c r="C171" t="s">
+        <v>26</v>
+      </c>
+      <c r="D171">
+        <v>71680</v>
+      </c>
+      <c r="E171">
+        <v>5874645.8</v>
+      </c>
+      <c r="F171">
+        <v>31047.71521320047</v>
+      </c>
+      <c r="G171">
+        <v>5825408</v>
+      </c>
+      <c r="H171">
+        <v>5913905</v>
+      </c>
+      <c r="I171">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="s">
+        <v>36</v>
+      </c>
+      <c r="B172" t="s">
+        <v>33</v>
+      </c>
+      <c r="C172" t="s">
+        <v>27</v>
+      </c>
+      <c r="D172">
+        <v>76800</v>
+      </c>
+      <c r="E172">
+        <v>6301448.9</v>
+      </c>
+      <c r="F172">
+        <v>64832.65532808294</v>
+      </c>
+      <c r="G172">
+        <v>6195366</v>
+      </c>
+      <c r="H172">
+        <v>6403857</v>
+      </c>
+      <c r="I172">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="s">
+        <v>36</v>
+      </c>
+      <c r="B173" t="s">
+        <v>33</v>
+      </c>
+      <c r="C173" t="s">
+        <v>28</v>
+      </c>
+      <c r="D173">
+        <v>81920</v>
+      </c>
+      <c r="E173">
+        <v>6677578.1</v>
+      </c>
+      <c r="F173">
+        <v>66910.3650467549</v>
+      </c>
+      <c r="G173">
+        <v>6579023</v>
+      </c>
+      <c r="H173">
+        <v>6812683</v>
+      </c>
+      <c r="I173">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="s">
+        <v>36</v>
+      </c>
+      <c r="B174" t="s">
+        <v>33</v>
+      </c>
+      <c r="C174" t="s">
+        <v>29</v>
+      </c>
+      <c r="D174">
+        <v>87040</v>
+      </c>
+      <c r="E174">
+        <v>7194367</v>
+      </c>
+      <c r="F174">
+        <v>80967.88520765501</v>
+      </c>
+      <c r="G174">
+        <v>7081896</v>
+      </c>
+      <c r="H174">
+        <v>7329831</v>
+      </c>
+      <c r="I174">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s">
+        <v>36</v>
+      </c>
+      <c r="B175" t="s">
+        <v>33</v>
+      </c>
+      <c r="C175" t="s">
+        <v>30</v>
+      </c>
+      <c r="D175">
+        <v>92160</v>
+      </c>
+      <c r="E175">
+        <v>7653507.4</v>
+      </c>
+      <c r="F175">
+        <v>120579.58204704478</v>
+      </c>
+      <c r="G175">
+        <v>7563230</v>
+      </c>
+      <c r="H175">
+        <v>7997624</v>
+      </c>
+      <c r="I175">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s">
+        <v>36</v>
+      </c>
+      <c r="B176" t="s">
+        <v>33</v>
+      </c>
+      <c r="C176" t="s">
+        <v>31</v>
+      </c>
+      <c r="D176">
+        <v>97280</v>
+      </c>
+      <c r="E176">
+        <v>8008970.7</v>
+      </c>
+      <c r="F176">
+        <v>71971.43140864992</v>
+      </c>
+      <c r="G176">
+        <v>7887500</v>
+      </c>
+      <c r="H176">
+        <v>8117298</v>
+      </c>
+      <c r="I176">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="s">
+        <v>36</v>
+      </c>
+      <c r="B177" t="s">
+        <v>33</v>
+      </c>
+      <c r="C177" t="s">
+        <v>32</v>
+      </c>
+      <c r="D177">
+        <v>102400</v>
+      </c>
+      <c r="E177">
         <v>8492545.1</v>
       </c>
-      <c r="F67">
+      <c r="F177">
         <v>102272.17173156147</v>
       </c>
-      <c r="G67">
+      <c r="G177">
         <v>8385884</v>
       </c>
-      <c r="H67">
+      <c r="H177">
         <v>8732149</v>
       </c>
-      <c r="I67">
+      <c r="I177">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="s">
+        <v>36</v>
+      </c>
+      <c r="B178" t="s">
+        <v>34</v>
+      </c>
+      <c r="C178" t="s">
+        <v>11</v>
+      </c>
+      <c r="D178">
+        <v>100</v>
+      </c>
+      <c r="E178">
+        <v>50780.4</v>
+      </c>
+      <c r="F178">
+        <v>1624.2490695703045</v>
+      </c>
+      <c r="G178">
+        <v>49999</v>
+      </c>
+      <c r="H178">
+        <v>55624</v>
+      </c>
+      <c r="I178">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="s">
+        <v>36</v>
+      </c>
+      <c r="B179" t="s">
+        <v>34</v>
+      </c>
+      <c r="C179" t="s">
+        <v>12</v>
+      </c>
+      <c r="D179">
+        <v>1024</v>
+      </c>
+      <c r="E179">
+        <v>677621.2</v>
+      </c>
+      <c r="F179">
+        <v>19572.654402507596</v>
+      </c>
+      <c r="G179">
+        <v>663168</v>
+      </c>
+      <c r="H179">
+        <v>728167</v>
+      </c>
+      <c r="I179">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="s">
+        <v>36</v>
+      </c>
+      <c r="B180" t="s">
+        <v>34</v>
+      </c>
+      <c r="C180" t="s">
+        <v>13</v>
+      </c>
+      <c r="D180">
+        <v>5120</v>
+      </c>
+      <c r="E180">
+        <v>3831677.7</v>
+      </c>
+      <c r="F180">
+        <v>60961.17273158383</v>
+      </c>
+      <c r="G180">
+        <v>3770730</v>
+      </c>
+      <c r="H180">
+        <v>3958489</v>
+      </c>
+      <c r="I180">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="s">
+        <v>36</v>
+      </c>
+      <c r="B181" t="s">
+        <v>34</v>
+      </c>
+      <c r="C181" t="s">
+        <v>14</v>
+      </c>
+      <c r="D181">
+        <v>10240</v>
+      </c>
+      <c r="E181">
+        <v>8135072.9</v>
+      </c>
+      <c r="F181">
+        <v>48695.2342071583</v>
+      </c>
+      <c r="G181">
+        <v>8071245</v>
+      </c>
+      <c r="H181">
+        <v>8235514</v>
+      </c>
+      <c r="I181">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="s">
+        <v>36</v>
+      </c>
+      <c r="B182" t="s">
+        <v>34</v>
+      </c>
+      <c r="C182" t="s">
+        <v>15</v>
+      </c>
+      <c r="D182">
+        <v>15360</v>
+      </c>
+      <c r="E182">
+        <v>12598700.2</v>
+      </c>
+      <c r="F182">
+        <v>80572.34058260937</v>
+      </c>
+      <c r="G182">
+        <v>12505717</v>
+      </c>
+      <c r="H182">
+        <v>12774307</v>
+      </c>
+      <c r="I182">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="s">
+        <v>36</v>
+      </c>
+      <c r="B183" t="s">
+        <v>34</v>
+      </c>
+      <c r="C183" t="s">
+        <v>16</v>
+      </c>
+      <c r="D183">
+        <v>20480</v>
+      </c>
+      <c r="E183">
+        <v>17229481.4</v>
+      </c>
+      <c r="F183">
+        <v>112428.50080313266</v>
+      </c>
+      <c r="G183">
+        <v>17105030</v>
+      </c>
+      <c r="H183">
+        <v>17471796</v>
+      </c>
+      <c r="I183">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="s">
+        <v>36</v>
+      </c>
+      <c r="B184" t="s">
+        <v>34</v>
+      </c>
+      <c r="C184" t="s">
+        <v>17</v>
+      </c>
+      <c r="D184">
+        <v>25600</v>
+      </c>
+      <c r="E184">
+        <v>22061593.2</v>
+      </c>
+      <c r="F184">
+        <v>80443.961517071</v>
+      </c>
+      <c r="G184">
+        <v>21969027</v>
+      </c>
+      <c r="H184">
+        <v>22228242</v>
+      </c>
+      <c r="I184">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="s">
+        <v>36</v>
+      </c>
+      <c r="B185" t="s">
+        <v>34</v>
+      </c>
+      <c r="C185" t="s">
+        <v>18</v>
+      </c>
+      <c r="D185">
+        <v>30720</v>
+      </c>
+      <c r="E185">
+        <v>27100394.5</v>
+      </c>
+      <c r="F185">
+        <v>89290.2840181954</v>
+      </c>
+      <c r="G185">
+        <v>26957084</v>
+      </c>
+      <c r="H185">
+        <v>27239268</v>
+      </c>
+      <c r="I185">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="s">
+        <v>36</v>
+      </c>
+      <c r="B186" t="s">
+        <v>34</v>
+      </c>
+      <c r="C186" t="s">
+        <v>19</v>
+      </c>
+      <c r="D186">
+        <v>35840</v>
+      </c>
+      <c r="E186">
+        <v>31610119.5</v>
+      </c>
+      <c r="F186">
+        <v>96856.80151156138</v>
+      </c>
+      <c r="G186">
+        <v>31494991</v>
+      </c>
+      <c r="H186">
+        <v>31795768</v>
+      </c>
+      <c r="I186">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="s">
+        <v>36</v>
+      </c>
+      <c r="B187" t="s">
+        <v>34</v>
+      </c>
+      <c r="C187" t="s">
+        <v>20</v>
+      </c>
+      <c r="D187">
+        <v>40960</v>
+      </c>
+      <c r="E187">
+        <v>37769774.8</v>
+      </c>
+      <c r="F187">
+        <v>70400.77688463387</v>
+      </c>
+      <c r="G187">
+        <v>37641782</v>
+      </c>
+      <c r="H187">
+        <v>37857665</v>
+      </c>
+      <c r="I187">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="s">
+        <v>36</v>
+      </c>
+      <c r="B188" t="s">
+        <v>34</v>
+      </c>
+      <c r="C188" t="s">
+        <v>21</v>
+      </c>
+      <c r="D188">
+        <v>46080</v>
+      </c>
+      <c r="E188">
+        <v>41976279.4</v>
+      </c>
+      <c r="F188">
+        <v>112100.24713817539</v>
+      </c>
+      <c r="G188">
+        <v>41808182</v>
+      </c>
+      <c r="H188">
+        <v>42128804</v>
+      </c>
+      <c r="I188">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="s">
+        <v>36</v>
+      </c>
+      <c r="B189" t="s">
+        <v>34</v>
+      </c>
+      <c r="C189" t="s">
+        <v>22</v>
+      </c>
+      <c r="D189">
+        <v>51200</v>
+      </c>
+      <c r="E189">
+        <v>46097149.5</v>
+      </c>
+      <c r="F189">
+        <v>107481.84285194406</v>
+      </c>
+      <c r="G189">
+        <v>45946042</v>
+      </c>
+      <c r="H189">
+        <v>46322548</v>
+      </c>
+      <c r="I189">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="s">
+        <v>36</v>
+      </c>
+      <c r="B190" t="s">
+        <v>34</v>
+      </c>
+      <c r="C190" t="s">
+        <v>23</v>
+      </c>
+      <c r="D190">
+        <v>56320</v>
+      </c>
+      <c r="E190">
+        <v>51871653.3</v>
+      </c>
+      <c r="F190">
+        <v>117561.19792350706</v>
+      </c>
+      <c r="G190">
+        <v>51722108</v>
+      </c>
+      <c r="H190">
+        <v>52087364</v>
+      </c>
+      <c r="I190">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="s">
+        <v>36</v>
+      </c>
+      <c r="B191" t="s">
+        <v>34</v>
+      </c>
+      <c r="C191" t="s">
+        <v>24</v>
+      </c>
+      <c r="D191">
+        <v>61440</v>
+      </c>
+      <c r="E191">
+        <v>57466128.2</v>
+      </c>
+      <c r="F191">
+        <v>101698.22547596393</v>
+      </c>
+      <c r="G191">
+        <v>57317188</v>
+      </c>
+      <c r="H191">
+        <v>57621246</v>
+      </c>
+      <c r="I191">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="s">
+        <v>36</v>
+      </c>
+      <c r="B192" t="s">
+        <v>34</v>
+      </c>
+      <c r="C192" t="s">
+        <v>25</v>
+      </c>
+      <c r="D192">
+        <v>66560</v>
+      </c>
+      <c r="E192">
+        <v>61991377.5</v>
+      </c>
+      <c r="F192">
+        <v>110781.76766079335</v>
+      </c>
+      <c r="G192">
+        <v>61814052</v>
+      </c>
+      <c r="H192">
+        <v>62113527</v>
+      </c>
+      <c r="I192">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="s">
+        <v>36</v>
+      </c>
+      <c r="B193" t="s">
+        <v>34</v>
+      </c>
+      <c r="C193" t="s">
+        <v>26</v>
+      </c>
+      <c r="D193">
+        <v>71680</v>
+      </c>
+      <c r="E193">
+        <v>67354625.4</v>
+      </c>
+      <c r="F193">
+        <v>84723.87484080269</v>
+      </c>
+      <c r="G193">
+        <v>67215487</v>
+      </c>
+      <c r="H193">
+        <v>67526681</v>
+      </c>
+      <c r="I193">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="s">
+        <v>36</v>
+      </c>
+      <c r="B194" t="s">
+        <v>34</v>
+      </c>
+      <c r="C194" t="s">
+        <v>27</v>
+      </c>
+      <c r="D194">
+        <v>76800</v>
+      </c>
+      <c r="E194">
+        <v>72080043.6</v>
+      </c>
+      <c r="F194">
+        <v>132440.03728042365</v>
+      </c>
+      <c r="G194">
+        <v>71911618</v>
+      </c>
+      <c r="H194">
+        <v>72302708</v>
+      </c>
+      <c r="I194">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="s">
+        <v>36</v>
+      </c>
+      <c r="B195" t="s">
+        <v>34</v>
+      </c>
+      <c r="C195" t="s">
+        <v>28</v>
+      </c>
+      <c r="D195">
+        <v>81920</v>
+      </c>
+      <c r="E195">
+        <v>78243779.9</v>
+      </c>
+      <c r="F195">
+        <v>97534.7874098775</v>
+      </c>
+      <c r="G195">
+        <v>78137364</v>
+      </c>
+      <c r="H195">
+        <v>78406215</v>
+      </c>
+      <c r="I195">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="s">
+        <v>36</v>
+      </c>
+      <c r="B196" t="s">
+        <v>34</v>
+      </c>
+      <c r="C196" t="s">
+        <v>29</v>
+      </c>
+      <c r="D196">
+        <v>87040</v>
+      </c>
+      <c r="E196">
+        <v>83677849.2</v>
+      </c>
+      <c r="F196">
+        <v>81338.28983301776</v>
+      </c>
+      <c r="G196">
+        <v>83569372</v>
+      </c>
+      <c r="H196">
+        <v>83853118</v>
+      </c>
+      <c r="I196">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="s">
+        <v>36</v>
+      </c>
+      <c r="B197" t="s">
+        <v>34</v>
+      </c>
+      <c r="C197" t="s">
+        <v>30</v>
+      </c>
+      <c r="D197">
+        <v>92160</v>
+      </c>
+      <c r="E197">
+        <v>89536990</v>
+      </c>
+      <c r="F197">
+        <v>123401.89692059033</v>
+      </c>
+      <c r="G197">
+        <v>89388977</v>
+      </c>
+      <c r="H197">
+        <v>89838345</v>
+      </c>
+      <c r="I197">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="s">
+        <v>36</v>
+      </c>
+      <c r="B198" t="s">
+        <v>34</v>
+      </c>
+      <c r="C198" t="s">
+        <v>31</v>
+      </c>
+      <c r="D198">
+        <v>97280</v>
+      </c>
+      <c r="E198">
+        <v>93289289.7</v>
+      </c>
+      <c r="F198">
+        <v>115960.08485944635</v>
+      </c>
+      <c r="G198">
+        <v>93180953</v>
+      </c>
+      <c r="H198">
+        <v>93577094</v>
+      </c>
+      <c r="I198">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="s">
+        <v>36</v>
+      </c>
+      <c r="B199" t="s">
+        <v>34</v>
+      </c>
+      <c r="C199" t="s">
+        <v>32</v>
+      </c>
+      <c r="D199">
+        <v>102400</v>
+      </c>
+      <c r="E199">
+        <v>99630069.3</v>
+      </c>
+      <c r="F199">
+        <v>217303.83453130777</v>
+      </c>
+      <c r="G199">
+        <v>99468311</v>
+      </c>
+      <c r="H199">
+        <v>100235072</v>
+      </c>
+      <c r="I199">
         <v>10</v>
       </c>
     </row>
@@ -2417,7 +6263,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2">
@@ -2428,10 +6274,10 @@
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3">
@@ -2439,13 +6285,13 @@
         <v>100</v>
       </c>
       <c r="B3">
-        <v>29812.7</v>
+        <v>82963.4</v>
       </c>
       <c r="C3">
-        <v>228556.6</v>
+        <v>928269.2</v>
       </c>
       <c r="D3">
-        <v>4534.7</v>
+        <v>10055.1</v>
       </c>
     </row>
     <row r="4">
@@ -2453,13 +6299,13 @@
         <v>1024</v>
       </c>
       <c r="B4">
-        <v>2779192.4</v>
+        <v>9827302</v>
       </c>
       <c r="C4">
-        <v>2433976.4</v>
+        <v>10278739.1</v>
       </c>
       <c r="D4">
-        <v>71213.6</v>
+        <v>123599.4</v>
       </c>
     </row>
     <row r="5">
@@ -2467,13 +6313,13 @@
         <v>5120</v>
       </c>
       <c r="B5">
-        <v>71031572.7</v>
+        <v>179148840.3</v>
       </c>
       <c r="C5">
-        <v>12705733.4</v>
+        <v>51183088.8</v>
       </c>
       <c r="D5">
-        <v>383914.5</v>
+        <v>685812.9</v>
       </c>
     </row>
     <row r="6">
@@ -2481,13 +6327,13 @@
         <v>10240</v>
       </c>
       <c r="B6">
-        <v>285652901.5</v>
+        <v>713713868.4</v>
       </c>
       <c r="C6">
-        <v>25389107.5</v>
+        <v>101877702.7</v>
       </c>
       <c r="D6">
-        <v>780722.2</v>
+        <v>1437986.3</v>
       </c>
     </row>
     <row r="7">
@@ -2495,13 +6341,13 @@
         <v>15360</v>
       </c>
       <c r="B7">
-        <v>633566838</v>
+        <v>1610808023.7</v>
       </c>
       <c r="C7">
-        <v>36383113.1</v>
+        <v>152962324.1</v>
       </c>
       <c r="D7">
-        <v>1197383.1</v>
+        <v>2230143.3</v>
       </c>
     </row>
     <row r="8">
@@ -2509,13 +6355,13 @@
         <v>20480</v>
       </c>
       <c r="B8">
-        <v>1115376821.8</v>
+        <v>2846276388.7</v>
       </c>
       <c r="C8">
-        <v>48623879.4</v>
+        <v>204053053.6</v>
       </c>
       <c r="D8">
-        <v>1617710.5</v>
+        <v>2994569.5</v>
       </c>
     </row>
     <row r="9">
@@ -2523,13 +6369,13 @@
         <v>25600</v>
       </c>
       <c r="B9">
-        <v>1760931144</v>
+        <v>4433773216.4</v>
       </c>
       <c r="C9">
-        <v>60985352.4</v>
+        <v>254840481.7</v>
       </c>
       <c r="D9">
-        <v>2003608</v>
+        <v>3790005.1</v>
       </c>
     </row>
     <row r="10">
@@ -2537,13 +6383,13 @@
         <v>30720</v>
       </c>
       <c r="B10">
-        <v>2595987199</v>
+        <v>6518896175</v>
       </c>
       <c r="C10">
-        <v>72569335</v>
+        <v>306111723.1</v>
       </c>
       <c r="D10">
-        <v>2446195.5</v>
+        <v>4622930.7</v>
       </c>
     </row>
     <row r="11">
@@ -2551,13 +6397,13 @@
         <v>35840</v>
       </c>
       <c r="B11">
-        <v>3461565794.5</v>
+        <v>8815969638.3</v>
       </c>
       <c r="C11">
-        <v>85059505.7</v>
+        <v>357054966</v>
       </c>
       <c r="D11">
-        <v>2859693.4</v>
+        <v>5436622.9</v>
       </c>
     </row>
     <row r="12">
@@ -2565,13 +6411,13 @@
         <v>40960</v>
       </c>
       <c r="B12">
-        <v>4695119000.9</v>
+        <v>11585239740.2</v>
       </c>
       <c r="C12">
-        <v>96687521.5</v>
+        <v>407498526.5</v>
       </c>
       <c r="D12">
-        <v>3316331.1</v>
+        <v>6394459.4</v>
       </c>
     </row>
     <row r="13">
@@ -2579,13 +6425,13 @@
         <v>46080</v>
       </c>
       <c r="B13">
-        <v>5725006478.3</v>
+        <v>14567175307.8</v>
       </c>
       <c r="C13">
-        <v>114396494.4</v>
+        <v>461330246.7</v>
       </c>
       <c r="D13">
-        <v>3721145.5</v>
+        <v>7079063</v>
       </c>
     </row>
     <row r="14">
@@ -2593,13 +6439,13 @@
         <v>51200</v>
       </c>
       <c r="B14">
-        <v>7114505067.9</v>
+        <v>18091568600.6</v>
       </c>
       <c r="C14">
-        <v>128073697.4</v>
+        <v>506856371.5</v>
       </c>
       <c r="D14">
-        <v>4190075.6</v>
+        <v>7912422.3</v>
       </c>
     </row>
     <row r="15">
@@ -2607,13 +6453,13 @@
         <v>56320</v>
       </c>
       <c r="B15">
-        <v>8592723655.9</v>
+        <v>21710078733.8</v>
       </c>
       <c r="C15">
-        <v>133712954.7</v>
+        <v>563467551.2</v>
       </c>
       <c r="D15">
-        <v>4569048</v>
+        <v>8786584.6</v>
       </c>
     </row>
     <row r="16">
@@ -2621,13 +6467,13 @@
         <v>61440</v>
       </c>
       <c r="B16">
-        <v>10218618516.7</v>
+        <v>26149479114.6</v>
       </c>
       <c r="C16">
-        <v>146554587.8</v>
+        <v>613243337.9</v>
       </c>
       <c r="D16">
-        <v>5005579.9</v>
+        <v>9717019</v>
       </c>
     </row>
     <row r="17">
@@ -2635,13 +6481,13 @@
         <v>66560</v>
       </c>
       <c r="B17">
-        <v>11958599692.9</v>
+        <v>30474127218.4</v>
       </c>
       <c r="C17">
-        <v>158203280.2</v>
+        <v>661409185.9</v>
       </c>
       <c r="D17">
-        <v>5410891.7</v>
+        <v>10567925.4</v>
       </c>
     </row>
     <row r="18">
@@ -2649,13 +6495,13 @@
         <v>71680</v>
       </c>
       <c r="B18">
-        <v>13956227440.6</v>
+        <v>35765170742.2</v>
       </c>
       <c r="C18">
-        <v>170926709.3</v>
+        <v>713264838.8</v>
       </c>
       <c r="D18">
-        <v>5874645.8</v>
+        <v>11444969.8</v>
       </c>
     </row>
     <row r="19">
@@ -2663,13 +6509,13 @@
         <v>76800</v>
       </c>
       <c r="B19">
-        <v>15974329050.1</v>
+        <v>40081367236.2</v>
       </c>
       <c r="C19">
-        <v>180511694.5</v>
+        <v>762123602</v>
       </c>
       <c r="D19">
-        <v>6301448.9</v>
+        <v>12222383.2</v>
       </c>
     </row>
     <row r="20">
@@ -2677,13 +6523,13 @@
         <v>81920</v>
       </c>
       <c r="B20">
-        <v>18222895840.3</v>
+        <v>46179802809.9</v>
       </c>
       <c r="C20">
-        <v>193626605.6</v>
+        <v>819105618.2</v>
       </c>
       <c r="D20">
-        <v>6677578.1</v>
+        <v>12978764.1</v>
       </c>
     </row>
     <row r="21">
@@ -2691,13 +6537,13 @@
         <v>87040</v>
       </c>
       <c r="B21">
-        <v>20559390221.8</v>
+        <v>51951214409</v>
       </c>
       <c r="C21">
-        <v>208244752.5</v>
+        <v>864279368.6</v>
       </c>
       <c r="D21">
-        <v>7194367</v>
+        <v>13897361.3</v>
       </c>
     </row>
     <row r="22">
@@ -2705,13 +6551,13 @@
         <v>92160</v>
       </c>
       <c r="B22">
-        <v>22971938112.2</v>
+        <v>58742794034.3</v>
       </c>
       <c r="C22">
-        <v>213587381.4</v>
+        <v>918100522.6</v>
       </c>
       <c r="D22">
-        <v>7653507.4</v>
+        <v>14789982.7</v>
       </c>
     </row>
     <row r="23">
@@ -2719,13 +6565,13 @@
         <v>97280</v>
       </c>
       <c r="B23">
-        <v>25709704095.3</v>
+        <v>65638213779.5</v>
       </c>
       <c r="C23">
-        <v>230312851.5</v>
+        <v>971643274.9</v>
       </c>
       <c r="D23">
-        <v>8008970.7</v>
+        <v>15417517.6</v>
       </c>
     </row>
     <row r="24">
@@ -2733,13 +6579,667 @@
         <v>102400</v>
       </c>
       <c r="B24">
+        <v>71617023099.5</v>
+      </c>
+      <c r="C24">
+        <v>1025923888.2</v>
+      </c>
+      <c r="D24">
+        <v>16565274.4</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>3</v>
+      </c>
+      <c r="B29" t="s">
+        <v>9</v>
+      </c>
+      <c r="C29" t="s">
+        <v>35</v>
+      </c>
+      <c r="D29" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>100</v>
+      </c>
+      <c r="B30">
+        <v>29812.7</v>
+      </c>
+      <c r="C30">
+        <v>228556.6</v>
+      </c>
+      <c r="D30">
+        <v>4534.7</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>1024</v>
+      </c>
+      <c r="B31">
+        <v>2779192.4</v>
+      </c>
+      <c r="C31">
+        <v>2433976.4</v>
+      </c>
+      <c r="D31">
+        <v>71213.6</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>5120</v>
+      </c>
+      <c r="B32">
+        <v>71031572.7</v>
+      </c>
+      <c r="C32">
+        <v>12705733.4</v>
+      </c>
+      <c r="D32">
+        <v>383914.5</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>10240</v>
+      </c>
+      <c r="B33">
+        <v>285652901.5</v>
+      </c>
+      <c r="C33">
+        <v>25389107.5</v>
+      </c>
+      <c r="D33">
+        <v>780722.2</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>15360</v>
+      </c>
+      <c r="B34">
+        <v>633566838</v>
+      </c>
+      <c r="C34">
+        <v>36383113.1</v>
+      </c>
+      <c r="D34">
+        <v>1197383.1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>20480</v>
+      </c>
+      <c r="B35">
+        <v>1115376821.8</v>
+      </c>
+      <c r="C35">
+        <v>48623879.4</v>
+      </c>
+      <c r="D35">
+        <v>1617710.5</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>25600</v>
+      </c>
+      <c r="B36">
+        <v>1760931144</v>
+      </c>
+      <c r="C36">
+        <v>60985352.4</v>
+      </c>
+      <c r="D36">
+        <v>2003608</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>30720</v>
+      </c>
+      <c r="B37">
+        <v>2595987199</v>
+      </c>
+      <c r="C37">
+        <v>72569335</v>
+      </c>
+      <c r="D37">
+        <v>2446195.5</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>35840</v>
+      </c>
+      <c r="B38">
+        <v>3461565794.5</v>
+      </c>
+      <c r="C38">
+        <v>85059505.7</v>
+      </c>
+      <c r="D38">
+        <v>2859693.4</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>40960</v>
+      </c>
+      <c r="B39">
+        <v>4695119000.9</v>
+      </c>
+      <c r="C39">
+        <v>96687521.5</v>
+      </c>
+      <c r="D39">
+        <v>3316331.1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>46080</v>
+      </c>
+      <c r="B40">
+        <v>5725006478.3</v>
+      </c>
+      <c r="C40">
+        <v>114396494.4</v>
+      </c>
+      <c r="D40">
+        <v>3721145.5</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>51200</v>
+      </c>
+      <c r="B41">
+        <v>7114505067.9</v>
+      </c>
+      <c r="C41">
+        <v>128073697.4</v>
+      </c>
+      <c r="D41">
+        <v>4190075.6</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>56320</v>
+      </c>
+      <c r="B42">
+        <v>8592723655.9</v>
+      </c>
+      <c r="C42">
+        <v>133712954.7</v>
+      </c>
+      <c r="D42">
+        <v>4569048</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>61440</v>
+      </c>
+      <c r="B43">
+        <v>10218618516.7</v>
+      </c>
+      <c r="C43">
+        <v>146554587.8</v>
+      </c>
+      <c r="D43">
+        <v>5005579.9</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>66560</v>
+      </c>
+      <c r="B44">
+        <v>11958599692.9</v>
+      </c>
+      <c r="C44">
+        <v>158203280.2</v>
+      </c>
+      <c r="D44">
+        <v>5410891.7</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>71680</v>
+      </c>
+      <c r="B45">
+        <v>13956227440.6</v>
+      </c>
+      <c r="C45">
+        <v>170926709.3</v>
+      </c>
+      <c r="D45">
+        <v>5874645.8</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>76800</v>
+      </c>
+      <c r="B46">
+        <v>15974329050.1</v>
+      </c>
+      <c r="C46">
+        <v>180511694.5</v>
+      </c>
+      <c r="D46">
+        <v>6301448.9</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>81920</v>
+      </c>
+      <c r="B47">
+        <v>18222895840.3</v>
+      </c>
+      <c r="C47">
+        <v>193626605.6</v>
+      </c>
+      <c r="D47">
+        <v>6677578.1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>87040</v>
+      </c>
+      <c r="B48">
+        <v>20559390221.8</v>
+      </c>
+      <c r="C48">
+        <v>208244752.5</v>
+      </c>
+      <c r="D48">
+        <v>7194367</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>92160</v>
+      </c>
+      <c r="B49">
+        <v>22971938112.2</v>
+      </c>
+      <c r="C49">
+        <v>213587381.4</v>
+      </c>
+      <c r="D49">
+        <v>7653507.4</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>97280</v>
+      </c>
+      <c r="B50">
+        <v>25709704095.3</v>
+      </c>
+      <c r="C50">
+        <v>230312851.5</v>
+      </c>
+      <c r="D50">
+        <v>8008970.7</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>102400</v>
+      </c>
+      <c r="B51">
         <v>28444096006</v>
       </c>
-      <c r="C24">
+      <c r="C51">
         <v>243367823.3</v>
       </c>
-      <c r="D24">
+      <c r="D51">
         <v>8492545.1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>3</v>
+      </c>
+      <c r="B56" t="s">
+        <v>9</v>
+      </c>
+      <c r="C56" t="s">
+        <v>35</v>
+      </c>
+      <c r="D56" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>100</v>
+      </c>
+      <c r="B57">
+        <v>557762.8</v>
+      </c>
+      <c r="C57">
+        <v>3288990.9</v>
+      </c>
+      <c r="D57">
+        <v>50780.4</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>1024</v>
+      </c>
+      <c r="B58">
+        <v>56498903.5</v>
+      </c>
+      <c r="C58">
+        <v>33342812.4</v>
+      </c>
+      <c r="D58">
+        <v>677621.2</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>5120</v>
+      </c>
+      <c r="B59">
+        <v>1406698940.4</v>
+      </c>
+      <c r="C59">
+        <v>165331042.4</v>
+      </c>
+      <c r="D59">
+        <v>3831677.7</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>10240</v>
+      </c>
+      <c r="B60">
+        <v>5578436295.1</v>
+      </c>
+      <c r="C60">
+        <v>330034105.4</v>
+      </c>
+      <c r="D60">
+        <v>8135072.9</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>15360</v>
+      </c>
+      <c r="B61">
+        <v>12684706235</v>
+      </c>
+      <c r="C61">
+        <v>490022168.3</v>
+      </c>
+      <c r="D61">
+        <v>12598700.2</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>20480</v>
+      </c>
+      <c r="B62">
+        <v>22322146682.4</v>
+      </c>
+      <c r="C62">
+        <v>661321424.9</v>
+      </c>
+      <c r="D62">
+        <v>17229481.4</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>25600</v>
+      </c>
+      <c r="B63">
+        <v>35129432253.3</v>
+      </c>
+      <c r="C63">
+        <v>830303817</v>
+      </c>
+      <c r="D63">
+        <v>22061593.2</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>30720</v>
+      </c>
+      <c r="B64">
+        <v>50811537498.2</v>
+      </c>
+      <c r="C64">
+        <v>992089360.5</v>
+      </c>
+      <c r="D64">
+        <v>27100394.5</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>35840</v>
+      </c>
+      <c r="B65">
+        <v>69105582394.1</v>
+      </c>
+      <c r="C65">
+        <v>1166714536.8</v>
+      </c>
+      <c r="D65">
+        <v>31610119.5</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>40960</v>
+      </c>
+      <c r="B66">
+        <v>90692851024.3</v>
+      </c>
+      <c r="C66">
+        <v>1333042823.5</v>
+      </c>
+      <c r="D66">
+        <v>37769774.8</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>46080</v>
+      </c>
+      <c r="B67">
+        <v>114442607094.5</v>
+      </c>
+      <c r="C67">
+        <v>1490738197.6</v>
+      </c>
+      <c r="D67">
+        <v>41976279.4</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>51200</v>
+      </c>
+      <c r="B68">
+        <v>141530964374.9</v>
+      </c>
+      <c r="C68">
+        <v>1684184290.5</v>
+      </c>
+      <c r="D68">
+        <v>46097149.5</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>56320</v>
+      </c>
+      <c r="B69">
+        <v>170701367450.8</v>
+      </c>
+      <c r="C69">
+        <v>1823900667</v>
+      </c>
+      <c r="D69">
+        <v>51871653.3</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>61440</v>
+      </c>
+      <c r="B70">
+        <v>203820136377.7</v>
+      </c>
+      <c r="C70">
+        <v>1985824590.8</v>
+      </c>
+      <c r="D70">
+        <v>57466128.2</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>66560</v>
+      </c>
+      <c r="B71">
+        <v>239084713971.6</v>
+      </c>
+      <c r="C71">
+        <v>2201072592.7</v>
+      </c>
+      <c r="D71">
+        <v>61991377.5</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>71680</v>
+      </c>
+      <c r="B72">
+        <v>277618517241</v>
+      </c>
+      <c r="C72">
+        <v>2360389873.2</v>
+      </c>
+      <c r="D72">
+        <v>67354625.4</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>76800</v>
+      </c>
+      <c r="B73">
+        <v>317605707827.7</v>
+      </c>
+      <c r="C73">
+        <v>2518559857.4</v>
+      </c>
+      <c r="D73">
+        <v>72080043.6</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>81920</v>
+      </c>
+      <c r="B74">
+        <v>361211297263.7</v>
+      </c>
+      <c r="C74">
+        <v>2676024061.2</v>
+      </c>
+      <c r="D74">
+        <v>78243779.9</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>87040</v>
+      </c>
+      <c r="B75">
+        <v>408896660387.3</v>
+      </c>
+      <c r="C75">
+        <v>2842473626</v>
+      </c>
+      <c r="D75">
+        <v>83677849.2</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>92160</v>
+      </c>
+      <c r="B76">
+        <v>457546233055.2</v>
+      </c>
+      <c r="C76">
+        <v>3008711128.9</v>
+      </c>
+      <c r="D76">
+        <v>89536990</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>97280</v>
+      </c>
+      <c r="B77">
+        <v>511226726172.7</v>
+      </c>
+      <c r="C77">
+        <v>3163661340.3</v>
+      </c>
+      <c r="D77">
+        <v>93289289.7</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>102400</v>
+      </c>
+      <c r="B78">
+        <v>566110304268.6</v>
+      </c>
+      <c r="C78">
+        <v>3336970656.1</v>
+      </c>
+      <c r="D78">
+        <v>99630069.3</v>
       </c>
     </row>
   </sheetData>
@@ -2767,24 +7267,24 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F1" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G1" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H1" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="I1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B2" t="s">
         <v>10</v>
@@ -2813,7 +7313,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B3" t="s">
         <v>10</v>
@@ -2842,7 +7342,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B4" t="s">
         <v>10</v>
@@ -2871,7 +7371,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B5" t="s">
         <v>10</v>
@@ -2900,7 +7400,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B6" t="s">
         <v>10</v>
@@ -2929,7 +7429,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B7" t="s">
         <v>10</v>
@@ -2958,7 +7458,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B8" t="s">
         <v>10</v>
@@ -2987,7 +7487,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B9" t="s">
         <v>10</v>
@@ -3016,7 +7516,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B10" t="s">
         <v>10</v>
@@ -3045,7 +7545,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B11" t="s">
         <v>10</v>
@@ -3074,7 +7574,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B12" t="s">
         <v>10</v>
@@ -3103,7 +7603,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B13" t="s">
         <v>10</v>
@@ -3132,7 +7632,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B14" t="s">
         <v>10</v>
@@ -3161,7 +7661,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B15" t="s">
         <v>10</v>
@@ -3190,7 +7690,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B16" t="s">
         <v>10</v>
@@ -3219,7 +7719,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B17" t="s">
         <v>10</v>
@@ -3248,7 +7748,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B18" t="s">
         <v>10</v>
@@ -3277,7 +7777,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B19" t="s">
         <v>10</v>
@@ -3306,7 +7806,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B20" t="s">
         <v>10</v>
@@ -3335,7 +7835,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B21" t="s">
         <v>10</v>
@@ -3364,7 +7864,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B22" t="s">
         <v>10</v>
@@ -3393,7 +7893,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B23" t="s">
         <v>10</v>
@@ -3417,6 +7917,1282 @@
         <v>102399</v>
       </c>
       <c r="I23">
+        <v>102399</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>35</v>
+      </c>
+      <c r="B24" t="s">
+        <v>33</v>
+      </c>
+      <c r="C24" t="s">
+        <v>11</v>
+      </c>
+      <c r="D24">
+        <v>100</v>
+      </c>
+      <c r="E24">
+        <v>672</v>
+      </c>
+      <c r="F24">
+        <v>672</v>
+      </c>
+      <c r="G24">
+        <v>3.393939393939394</v>
+      </c>
+      <c r="H24">
+        <v>99</v>
+      </c>
+      <c r="I24">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>35</v>
+      </c>
+      <c r="B25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C25" t="s">
+        <v>12</v>
+      </c>
+      <c r="D25">
+        <v>1024</v>
+      </c>
+      <c r="E25">
+        <v>10240</v>
+      </c>
+      <c r="F25">
+        <v>10240</v>
+      </c>
+      <c r="G25">
+        <v>5.004887585532747</v>
+      </c>
+      <c r="H25">
+        <v>1023</v>
+      </c>
+      <c r="I25">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>35</v>
+      </c>
+      <c r="B26" t="s">
+        <v>33</v>
+      </c>
+      <c r="C26" t="s">
+        <v>13</v>
+      </c>
+      <c r="D26">
+        <v>5120</v>
+      </c>
+      <c r="E26">
+        <v>63488</v>
+      </c>
+      <c r="F26">
+        <v>63488</v>
+      </c>
+      <c r="G26">
+        <v>6.201211174057433</v>
+      </c>
+      <c r="H26">
+        <v>5119</v>
+      </c>
+      <c r="I26">
+        <v>5119</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>35</v>
+      </c>
+      <c r="B27" t="s">
+        <v>33</v>
+      </c>
+      <c r="C27" t="s">
+        <v>14</v>
+      </c>
+      <c r="D27">
+        <v>10240</v>
+      </c>
+      <c r="E27">
+        <v>137216</v>
+      </c>
+      <c r="F27">
+        <v>137216</v>
+      </c>
+      <c r="G27">
+        <v>6.70065436077742</v>
+      </c>
+      <c r="H27">
+        <v>10239</v>
+      </c>
+      <c r="I27">
+        <v>10239</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28" t="s">
+        <v>33</v>
+      </c>
+      <c r="C28" t="s">
+        <v>15</v>
+      </c>
+      <c r="D28">
+        <v>15360</v>
+      </c>
+      <c r="E28">
+        <v>214016</v>
+      </c>
+      <c r="F28">
+        <v>214016</v>
+      </c>
+      <c r="G28">
+        <v>6.967120255224949</v>
+      </c>
+      <c r="H28">
+        <v>15359</v>
+      </c>
+      <c r="I28">
+        <v>15359</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>35</v>
+      </c>
+      <c r="B29" t="s">
+        <v>33</v>
+      </c>
+      <c r="C29" t="s">
+        <v>16</v>
+      </c>
+      <c r="D29">
+        <v>20480</v>
+      </c>
+      <c r="E29">
+        <v>294912</v>
+      </c>
+      <c r="F29">
+        <v>294912</v>
+      </c>
+      <c r="G29">
+        <v>7.200351579666976</v>
+      </c>
+      <c r="H29">
+        <v>20479</v>
+      </c>
+      <c r="I29">
+        <v>20479</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>35</v>
+      </c>
+      <c r="B30" t="s">
+        <v>33</v>
+      </c>
+      <c r="C30" t="s">
+        <v>17</v>
+      </c>
+      <c r="D30">
+        <v>25600</v>
+      </c>
+      <c r="E30">
+        <v>376832</v>
+      </c>
+      <c r="F30">
+        <v>376832</v>
+      </c>
+      <c r="G30">
+        <v>7.360287511230908</v>
+      </c>
+      <c r="H30">
+        <v>25599</v>
+      </c>
+      <c r="I30">
+        <v>25599</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>35</v>
+      </c>
+      <c r="B31" t="s">
+        <v>33</v>
+      </c>
+      <c r="C31" t="s">
+        <v>18</v>
+      </c>
+      <c r="D31">
+        <v>30720</v>
+      </c>
+      <c r="E31">
+        <v>458752</v>
+      </c>
+      <c r="F31">
+        <v>458752</v>
+      </c>
+      <c r="G31">
+        <v>7.466909730134445</v>
+      </c>
+      <c r="H31">
+        <v>30719</v>
+      </c>
+      <c r="I31">
+        <v>30719</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>35</v>
+      </c>
+      <c r="B32" t="s">
+        <v>33</v>
+      </c>
+      <c r="C32" t="s">
+        <v>19</v>
+      </c>
+      <c r="D32">
+        <v>35840</v>
+      </c>
+      <c r="E32">
+        <v>543744</v>
+      </c>
+      <c r="F32">
+        <v>543744</v>
+      </c>
+      <c r="G32">
+        <v>7.585925946594492</v>
+      </c>
+      <c r="H32">
+        <v>35839</v>
+      </c>
+      <c r="I32">
+        <v>35839</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>35</v>
+      </c>
+      <c r="B33" t="s">
+        <v>33</v>
+      </c>
+      <c r="C33" t="s">
+        <v>20</v>
+      </c>
+      <c r="D33">
+        <v>40960</v>
+      </c>
+      <c r="E33">
+        <v>630784</v>
+      </c>
+      <c r="F33">
+        <v>630784</v>
+      </c>
+      <c r="G33">
+        <v>7.700187992870919</v>
+      </c>
+      <c r="H33">
+        <v>40959</v>
+      </c>
+      <c r="I33">
+        <v>40959</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>35</v>
+      </c>
+      <c r="B34" t="s">
+        <v>33</v>
+      </c>
+      <c r="C34" t="s">
+        <v>21</v>
+      </c>
+      <c r="D34">
+        <v>46080</v>
+      </c>
+      <c r="E34">
+        <v>717824</v>
+      </c>
+      <c r="F34">
+        <v>717824</v>
+      </c>
+      <c r="G34">
+        <v>7.789057922263938</v>
+      </c>
+      <c r="H34">
+        <v>46079</v>
+      </c>
+      <c r="I34">
+        <v>46079</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>35</v>
+      </c>
+      <c r="B35" t="s">
+        <v>33</v>
+      </c>
+      <c r="C35" t="s">
+        <v>22</v>
+      </c>
+      <c r="D35">
+        <v>51200</v>
+      </c>
+      <c r="E35">
+        <v>804864</v>
+      </c>
+      <c r="F35">
+        <v>804864</v>
+      </c>
+      <c r="G35">
+        <v>7.86015351862341</v>
+      </c>
+      <c r="H35">
+        <v>51199</v>
+      </c>
+      <c r="I35">
+        <v>51199</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
+        <v>33</v>
+      </c>
+      <c r="C36" t="s">
+        <v>23</v>
+      </c>
+      <c r="D36">
+        <v>56320</v>
+      </c>
+      <c r="E36">
+        <v>891904</v>
+      </c>
+      <c r="F36">
+        <v>891904</v>
+      </c>
+      <c r="G36">
+        <v>7.918322413395124</v>
+      </c>
+      <c r="H36">
+        <v>56319</v>
+      </c>
+      <c r="I36">
+        <v>56319</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>35</v>
+      </c>
+      <c r="B37" t="s">
+        <v>33</v>
+      </c>
+      <c r="C37" t="s">
+        <v>24</v>
+      </c>
+      <c r="D37">
+        <v>61440</v>
+      </c>
+      <c r="E37">
+        <v>978944</v>
+      </c>
+      <c r="F37">
+        <v>978944</v>
+      </c>
+      <c r="G37">
+        <v>7.966796334575758</v>
+      </c>
+      <c r="H37">
+        <v>61439</v>
+      </c>
+      <c r="I37">
+        <v>61439</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>35</v>
+      </c>
+      <c r="B38" t="s">
+        <v>33</v>
+      </c>
+      <c r="C38" t="s">
+        <v>25</v>
+      </c>
+      <c r="D38">
+        <v>66560</v>
+      </c>
+      <c r="E38">
+        <v>1067008</v>
+      </c>
+      <c r="F38">
+        <v>1067008</v>
+      </c>
+      <c r="G38">
+        <v>8.015505040640635</v>
+      </c>
+      <c r="H38">
+        <v>66559</v>
+      </c>
+      <c r="I38">
+        <v>66559</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>35</v>
+      </c>
+      <c r="B39" t="s">
+        <v>33</v>
+      </c>
+      <c r="C39" t="s">
+        <v>26</v>
+      </c>
+      <c r="D39">
+        <v>71680</v>
+      </c>
+      <c r="E39">
+        <v>1159168</v>
+      </c>
+      <c r="F39">
+        <v>1159168</v>
+      </c>
+      <c r="G39">
+        <v>8.085827090221683</v>
+      </c>
+      <c r="H39">
+        <v>71679</v>
+      </c>
+      <c r="I39">
+        <v>71679</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>35</v>
+      </c>
+      <c r="B40" t="s">
+        <v>33</v>
+      </c>
+      <c r="C40" t="s">
+        <v>27</v>
+      </c>
+      <c r="D40">
+        <v>76800</v>
+      </c>
+      <c r="E40">
+        <v>1251328</v>
+      </c>
+      <c r="F40">
+        <v>1251328</v>
+      </c>
+      <c r="G40">
+        <v>8.146772744436776</v>
+      </c>
+      <c r="H40">
+        <v>76799</v>
+      </c>
+      <c r="I40">
+        <v>76799</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>35</v>
+      </c>
+      <c r="B41" t="s">
+        <v>33</v>
+      </c>
+      <c r="C41" t="s">
+        <v>28</v>
+      </c>
+      <c r="D41">
+        <v>81920</v>
+      </c>
+      <c r="E41">
+        <v>1343488</v>
+      </c>
+      <c r="F41">
+        <v>1343488</v>
+      </c>
+      <c r="G41">
+        <v>8.20010009887816</v>
+      </c>
+      <c r="H41">
+        <v>81919</v>
+      </c>
+      <c r="I41">
+        <v>81919</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>35</v>
+      </c>
+      <c r="B42" t="s">
+        <v>33</v>
+      </c>
+      <c r="C42" t="s">
+        <v>29</v>
+      </c>
+      <c r="D42">
+        <v>87040</v>
+      </c>
+      <c r="E42">
+        <v>1435648</v>
+      </c>
+      <c r="F42">
+        <v>1435648</v>
+      </c>
+      <c r="G42">
+        <v>8.24715357483427</v>
+      </c>
+      <c r="H42">
+        <v>87039</v>
+      </c>
+      <c r="I42">
+        <v>87039</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>35</v>
+      </c>
+      <c r="B43" t="s">
+        <v>33</v>
+      </c>
+      <c r="C43" t="s">
+        <v>30</v>
+      </c>
+      <c r="D43">
+        <v>92160</v>
+      </c>
+      <c r="E43">
+        <v>1527808</v>
+      </c>
+      <c r="F43">
+        <v>1527808</v>
+      </c>
+      <c r="G43">
+        <v>8.28897883006543</v>
+      </c>
+      <c r="H43">
+        <v>92159</v>
+      </c>
+      <c r="I43">
+        <v>92159</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>35</v>
+      </c>
+      <c r="B44" t="s">
+        <v>33</v>
+      </c>
+      <c r="C44" t="s">
+        <v>31</v>
+      </c>
+      <c r="D44">
+        <v>97280</v>
+      </c>
+      <c r="E44">
+        <v>1619968</v>
+      </c>
+      <c r="F44">
+        <v>1619968</v>
+      </c>
+      <c r="G44">
+        <v>8.326401381593149</v>
+      </c>
+      <c r="H44">
+        <v>97279</v>
+      </c>
+      <c r="I44">
+        <v>97279</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>35</v>
+      </c>
+      <c r="B45" t="s">
+        <v>33</v>
+      </c>
+      <c r="C45" t="s">
+        <v>32</v>
+      </c>
+      <c r="D45">
+        <v>102400</v>
+      </c>
+      <c r="E45">
+        <v>1712128</v>
+      </c>
+      <c r="F45">
+        <v>1712128</v>
+      </c>
+      <c r="G45">
+        <v>8.36008164142228</v>
+      </c>
+      <c r="H45">
+        <v>102399</v>
+      </c>
+      <c r="I45">
+        <v>102399</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>35</v>
+      </c>
+      <c r="B46" t="s">
+        <v>34</v>
+      </c>
+      <c r="C46" t="s">
+        <v>11</v>
+      </c>
+      <c r="D46">
+        <v>100</v>
+      </c>
+      <c r="E46">
+        <v>672</v>
+      </c>
+      <c r="F46">
+        <v>672</v>
+      </c>
+      <c r="G46">
+        <v>3.393939393939394</v>
+      </c>
+      <c r="H46">
+        <v>99</v>
+      </c>
+      <c r="I46">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>35</v>
+      </c>
+      <c r="B47" t="s">
+        <v>34</v>
+      </c>
+      <c r="C47" t="s">
+        <v>12</v>
+      </c>
+      <c r="D47">
+        <v>1024</v>
+      </c>
+      <c r="E47">
+        <v>10240</v>
+      </c>
+      <c r="F47">
+        <v>10240</v>
+      </c>
+      <c r="G47">
+        <v>5.004887585532747</v>
+      </c>
+      <c r="H47">
+        <v>1023</v>
+      </c>
+      <c r="I47">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>35</v>
+      </c>
+      <c r="B48" t="s">
+        <v>34</v>
+      </c>
+      <c r="C48" t="s">
+        <v>13</v>
+      </c>
+      <c r="D48">
+        <v>5120</v>
+      </c>
+      <c r="E48">
+        <v>63488</v>
+      </c>
+      <c r="F48">
+        <v>63488</v>
+      </c>
+      <c r="G48">
+        <v>6.201211174057433</v>
+      </c>
+      <c r="H48">
+        <v>5119</v>
+      </c>
+      <c r="I48">
+        <v>5119</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>35</v>
+      </c>
+      <c r="B49" t="s">
+        <v>34</v>
+      </c>
+      <c r="C49" t="s">
+        <v>14</v>
+      </c>
+      <c r="D49">
+        <v>10240</v>
+      </c>
+      <c r="E49">
+        <v>137216</v>
+      </c>
+      <c r="F49">
+        <v>137216</v>
+      </c>
+      <c r="G49">
+        <v>6.70065436077742</v>
+      </c>
+      <c r="H49">
+        <v>10239</v>
+      </c>
+      <c r="I49">
+        <v>10239</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>35</v>
+      </c>
+      <c r="B50" t="s">
+        <v>34</v>
+      </c>
+      <c r="C50" t="s">
+        <v>15</v>
+      </c>
+      <c r="D50">
+        <v>15360</v>
+      </c>
+      <c r="E50">
+        <v>214016</v>
+      </c>
+      <c r="F50">
+        <v>214016</v>
+      </c>
+      <c r="G50">
+        <v>6.967120255224949</v>
+      </c>
+      <c r="H50">
+        <v>15359</v>
+      </c>
+      <c r="I50">
+        <v>15359</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>35</v>
+      </c>
+      <c r="B51" t="s">
+        <v>34</v>
+      </c>
+      <c r="C51" t="s">
+        <v>16</v>
+      </c>
+      <c r="D51">
+        <v>20480</v>
+      </c>
+      <c r="E51">
+        <v>294912</v>
+      </c>
+      <c r="F51">
+        <v>294912</v>
+      </c>
+      <c r="G51">
+        <v>7.200351579666976</v>
+      </c>
+      <c r="H51">
+        <v>20479</v>
+      </c>
+      <c r="I51">
+        <v>20479</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>35</v>
+      </c>
+      <c r="B52" t="s">
+        <v>34</v>
+      </c>
+      <c r="C52" t="s">
+        <v>17</v>
+      </c>
+      <c r="D52">
+        <v>25600</v>
+      </c>
+      <c r="E52">
+        <v>376832</v>
+      </c>
+      <c r="F52">
+        <v>376832</v>
+      </c>
+      <c r="G52">
+        <v>7.360287511230908</v>
+      </c>
+      <c r="H52">
+        <v>25599</v>
+      </c>
+      <c r="I52">
+        <v>25599</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>35</v>
+      </c>
+      <c r="B53" t="s">
+        <v>34</v>
+      </c>
+      <c r="C53" t="s">
+        <v>18</v>
+      </c>
+      <c r="D53">
+        <v>30720</v>
+      </c>
+      <c r="E53">
+        <v>458752</v>
+      </c>
+      <c r="F53">
+        <v>458752</v>
+      </c>
+      <c r="G53">
+        <v>7.466909730134445</v>
+      </c>
+      <c r="H53">
+        <v>30719</v>
+      </c>
+      <c r="I53">
+        <v>30719</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>35</v>
+      </c>
+      <c r="B54" t="s">
+        <v>34</v>
+      </c>
+      <c r="C54" t="s">
+        <v>19</v>
+      </c>
+      <c r="D54">
+        <v>35840</v>
+      </c>
+      <c r="E54">
+        <v>543744</v>
+      </c>
+      <c r="F54">
+        <v>543744</v>
+      </c>
+      <c r="G54">
+        <v>7.585925946594492</v>
+      </c>
+      <c r="H54">
+        <v>35839</v>
+      </c>
+      <c r="I54">
+        <v>35839</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>35</v>
+      </c>
+      <c r="B55" t="s">
+        <v>34</v>
+      </c>
+      <c r="C55" t="s">
+        <v>20</v>
+      </c>
+      <c r="D55">
+        <v>40960</v>
+      </c>
+      <c r="E55">
+        <v>630784</v>
+      </c>
+      <c r="F55">
+        <v>630784</v>
+      </c>
+      <c r="G55">
+        <v>7.700187992870919</v>
+      </c>
+      <c r="H55">
+        <v>40959</v>
+      </c>
+      <c r="I55">
+        <v>40959</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>35</v>
+      </c>
+      <c r="B56" t="s">
+        <v>34</v>
+      </c>
+      <c r="C56" t="s">
+        <v>21</v>
+      </c>
+      <c r="D56">
+        <v>46080</v>
+      </c>
+      <c r="E56">
+        <v>717824</v>
+      </c>
+      <c r="F56">
+        <v>717824</v>
+      </c>
+      <c r="G56">
+        <v>7.789057922263938</v>
+      </c>
+      <c r="H56">
+        <v>46079</v>
+      </c>
+      <c r="I56">
+        <v>46079</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>35</v>
+      </c>
+      <c r="B57" t="s">
+        <v>34</v>
+      </c>
+      <c r="C57" t="s">
+        <v>22</v>
+      </c>
+      <c r="D57">
+        <v>51200</v>
+      </c>
+      <c r="E57">
+        <v>804864</v>
+      </c>
+      <c r="F57">
+        <v>804864</v>
+      </c>
+      <c r="G57">
+        <v>7.86015351862341</v>
+      </c>
+      <c r="H57">
+        <v>51199</v>
+      </c>
+      <c r="I57">
+        <v>51199</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>35</v>
+      </c>
+      <c r="B58" t="s">
+        <v>34</v>
+      </c>
+      <c r="C58" t="s">
+        <v>23</v>
+      </c>
+      <c r="D58">
+        <v>56320</v>
+      </c>
+      <c r="E58">
+        <v>891904</v>
+      </c>
+      <c r="F58">
+        <v>891904</v>
+      </c>
+      <c r="G58">
+        <v>7.918322413395124</v>
+      </c>
+      <c r="H58">
+        <v>56319</v>
+      </c>
+      <c r="I58">
+        <v>56319</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>35</v>
+      </c>
+      <c r="B59" t="s">
+        <v>34</v>
+      </c>
+      <c r="C59" t="s">
+        <v>24</v>
+      </c>
+      <c r="D59">
+        <v>61440</v>
+      </c>
+      <c r="E59">
+        <v>978944</v>
+      </c>
+      <c r="F59">
+        <v>978944</v>
+      </c>
+      <c r="G59">
+        <v>7.966796334575758</v>
+      </c>
+      <c r="H59">
+        <v>61439</v>
+      </c>
+      <c r="I59">
+        <v>61439</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>35</v>
+      </c>
+      <c r="B60" t="s">
+        <v>34</v>
+      </c>
+      <c r="C60" t="s">
+        <v>25</v>
+      </c>
+      <c r="D60">
+        <v>66560</v>
+      </c>
+      <c r="E60">
+        <v>1067008</v>
+      </c>
+      <c r="F60">
+        <v>1067008</v>
+      </c>
+      <c r="G60">
+        <v>8.015505040640635</v>
+      </c>
+      <c r="H60">
+        <v>66559</v>
+      </c>
+      <c r="I60">
+        <v>66559</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>35</v>
+      </c>
+      <c r="B61" t="s">
+        <v>34</v>
+      </c>
+      <c r="C61" t="s">
+        <v>26</v>
+      </c>
+      <c r="D61">
+        <v>71680</v>
+      </c>
+      <c r="E61">
+        <v>1159168</v>
+      </c>
+      <c r="F61">
+        <v>1159168</v>
+      </c>
+      <c r="G61">
+        <v>8.085827090221683</v>
+      </c>
+      <c r="H61">
+        <v>71679</v>
+      </c>
+      <c r="I61">
+        <v>71679</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>35</v>
+      </c>
+      <c r="B62" t="s">
+        <v>34</v>
+      </c>
+      <c r="C62" t="s">
+        <v>27</v>
+      </c>
+      <c r="D62">
+        <v>76800</v>
+      </c>
+      <c r="E62">
+        <v>1251328</v>
+      </c>
+      <c r="F62">
+        <v>1251328</v>
+      </c>
+      <c r="G62">
+        <v>8.146772744436776</v>
+      </c>
+      <c r="H62">
+        <v>76799</v>
+      </c>
+      <c r="I62">
+        <v>76799</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>35</v>
+      </c>
+      <c r="B63" t="s">
+        <v>34</v>
+      </c>
+      <c r="C63" t="s">
+        <v>28</v>
+      </c>
+      <c r="D63">
+        <v>81920</v>
+      </c>
+      <c r="E63">
+        <v>1343488</v>
+      </c>
+      <c r="F63">
+        <v>1343488</v>
+      </c>
+      <c r="G63">
+        <v>8.20010009887816</v>
+      </c>
+      <c r="H63">
+        <v>81919</v>
+      </c>
+      <c r="I63">
+        <v>81919</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>35</v>
+      </c>
+      <c r="B64" t="s">
+        <v>34</v>
+      </c>
+      <c r="C64" t="s">
+        <v>29</v>
+      </c>
+      <c r="D64">
+        <v>87040</v>
+      </c>
+      <c r="E64">
+        <v>1435648</v>
+      </c>
+      <c r="F64">
+        <v>1435648</v>
+      </c>
+      <c r="G64">
+        <v>8.24715357483427</v>
+      </c>
+      <c r="H64">
+        <v>87039</v>
+      </c>
+      <c r="I64">
+        <v>87039</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>35</v>
+      </c>
+      <c r="B65" t="s">
+        <v>34</v>
+      </c>
+      <c r="C65" t="s">
+        <v>30</v>
+      </c>
+      <c r="D65">
+        <v>92160</v>
+      </c>
+      <c r="E65">
+        <v>1527808</v>
+      </c>
+      <c r="F65">
+        <v>1527808</v>
+      </c>
+      <c r="G65">
+        <v>8.28897883006543</v>
+      </c>
+      <c r="H65">
+        <v>92159</v>
+      </c>
+      <c r="I65">
+        <v>92159</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>35</v>
+      </c>
+      <c r="B66" t="s">
+        <v>34</v>
+      </c>
+      <c r="C66" t="s">
+        <v>31</v>
+      </c>
+      <c r="D66">
+        <v>97280</v>
+      </c>
+      <c r="E66">
+        <v>1619968</v>
+      </c>
+      <c r="F66">
+        <v>1619968</v>
+      </c>
+      <c r="G66">
+        <v>8.326401381593149</v>
+      </c>
+      <c r="H66">
+        <v>97279</v>
+      </c>
+      <c r="I66">
+        <v>97279</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>35</v>
+      </c>
+      <c r="B67" t="s">
+        <v>34</v>
+      </c>
+      <c r="C67" t="s">
+        <v>32</v>
+      </c>
+      <c r="D67">
+        <v>102400</v>
+      </c>
+      <c r="E67">
+        <v>1712128</v>
+      </c>
+      <c r="F67">
+        <v>1712128</v>
+      </c>
+      <c r="G67">
+        <v>8.36008164142228</v>
+      </c>
+      <c r="H67">
+        <v>102399</v>
+      </c>
+      <c r="I67">
         <v>102399</v>
       </c>
     </row>
@@ -3434,7 +9210,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2">
@@ -3442,7 +9218,7 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3">
@@ -3621,6 +9397,384 @@
         <v>102400</v>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>3</v>
+      </c>
+      <c r="B29" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>100</v>
+      </c>
+      <c r="B30">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>1024</v>
+      </c>
+      <c r="B31">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>5120</v>
+      </c>
+      <c r="B32">
+        <v>5120</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>10240</v>
+      </c>
+      <c r="B33">
+        <v>10240</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>15360</v>
+      </c>
+      <c r="B34">
+        <v>15360</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>20480</v>
+      </c>
+      <c r="B35">
+        <v>20480</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>25600</v>
+      </c>
+      <c r="B36">
+        <v>25600</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>30720</v>
+      </c>
+      <c r="B37">
+        <v>30720</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>35840</v>
+      </c>
+      <c r="B38">
+        <v>35840</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>40960</v>
+      </c>
+      <c r="B39">
+        <v>40960</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>46080</v>
+      </c>
+      <c r="B40">
+        <v>46080</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>51200</v>
+      </c>
+      <c r="B41">
+        <v>51200</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>56320</v>
+      </c>
+      <c r="B42">
+        <v>56320</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>61440</v>
+      </c>
+      <c r="B43">
+        <v>61440</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>66560</v>
+      </c>
+      <c r="B44">
+        <v>66560</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>71680</v>
+      </c>
+      <c r="B45">
+        <v>71680</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>76800</v>
+      </c>
+      <c r="B46">
+        <v>76800</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>81920</v>
+      </c>
+      <c r="B47">
+        <v>81920</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>87040</v>
+      </c>
+      <c r="B48">
+        <v>87040</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>92160</v>
+      </c>
+      <c r="B49">
+        <v>92160</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>97280</v>
+      </c>
+      <c r="B50">
+        <v>97280</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>102400</v>
+      </c>
+      <c r="B51">
+        <v>102400</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>3</v>
+      </c>
+      <c r="B56" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>100</v>
+      </c>
+      <c r="B57">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>1024</v>
+      </c>
+      <c r="B58">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>5120</v>
+      </c>
+      <c r="B59">
+        <v>5120</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>10240</v>
+      </c>
+      <c r="B60">
+        <v>10240</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>15360</v>
+      </c>
+      <c r="B61">
+        <v>15360</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>20480</v>
+      </c>
+      <c r="B62">
+        <v>20480</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>25600</v>
+      </c>
+      <c r="B63">
+        <v>25600</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>30720</v>
+      </c>
+      <c r="B64">
+        <v>30720</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>35840</v>
+      </c>
+      <c r="B65">
+        <v>35840</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>40960</v>
+      </c>
+      <c r="B66">
+        <v>40960</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>46080</v>
+      </c>
+      <c r="B67">
+        <v>46080</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>51200</v>
+      </c>
+      <c r="B68">
+        <v>51200</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>56320</v>
+      </c>
+      <c r="B69">
+        <v>56320</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>61440</v>
+      </c>
+      <c r="B70">
+        <v>61440</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>66560</v>
+      </c>
+      <c r="B71">
+        <v>66560</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>71680</v>
+      </c>
+      <c r="B72">
+        <v>71680</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>76800</v>
+      </c>
+      <c r="B73">
+        <v>76800</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>81920</v>
+      </c>
+      <c r="B74">
+        <v>81920</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>87040</v>
+      </c>
+      <c r="B75">
+        <v>87040</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>92160</v>
+      </c>
+      <c r="B76">
+        <v>92160</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>97280</v>
+      </c>
+      <c r="B77">
+        <v>97280</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>102400</v>
+      </c>
+      <c r="B78">
+        <v>102400</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/aggregate_data.xlsx
+++ b/aggregate_data.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F402C45B-330C-41D7-A93D-91764C2D8516}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B1DA2F8-776B-41B5-A08D-2D5F518E220C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="26010" windowHeight="20985" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -14,12 +14,25 @@
     <sheet name="Memory_Statistics" sheetId="4" r:id="rId4"/>
     <sheet name="Memory_Charts" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="122211" iterateDelta="1E-4"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1405" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1407" uniqueCount="65">
   <si>
     <t>Algorithm</t>
   </si>
@@ -212,6 +225,9 @@
   <si>
     <t>ryzen 5</t>
   </si>
+  <si>
+    <t>x</t>
+  </si>
 </sst>
 </file>
 
@@ -1236,7 +1252,9 @@
                 </a:solidFill>
               </a:ln>
             </c:spPr>
-            <c:trendlineType val="power"/>
+            <c:trendlineType val="poly"/>
+            <c:order val="2"/>
+            <c:intercept val="0"/>
             <c:dispRSqr val="1"/>
             <c:dispEq val="1"/>
             <c:trendlineLbl>
@@ -4762,34 +4780,31 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>CPU_Charts!$M$12:$M$16</c:f>
+              <c:f>CPU_Charts!$M$12:$M$15</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>2.5</c:v>
+                  <c:v>3.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4.2</c:v>
+                  <c:v>4.1900000000000004</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.7</c:v>
+                  <c:v>5.3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.8</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>3.6</c:v>
+                  <c:v>2.95</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>CPU_Charts!$N$12:$N$16</c:f>
+              <c:f>CPU_Charts!$N$12:$N$15</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>9.99</c:v>
                 </c:pt>
@@ -4800,9 +4815,6 @@
                   <c:v>2.94</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>52.8</c:v>
-                </c:pt>
-                <c:pt idx="4">
                   <c:v>8.6999999999999993</c:v>
                 </c:pt>
               </c:numCache>
@@ -5042,34 +5054,31 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>CPU_Charts!$M$20:$M$24</c:f>
+              <c:f>CPU_Charts!$M$20:$M$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>2.5</c:v>
+                  <c:v>3.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4.2</c:v>
+                  <c:v>4.1900000000000004</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.7</c:v>
+                  <c:v>5.3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.8</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>3.6</c:v>
+                  <c:v>2.95</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>CPU_Charts!$N$20:$N$24</c:f>
+              <c:f>CPU_Charts!$N$20:$N$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>9969</c:v>
                 </c:pt>
@@ -5080,9 +5089,6 @@
                   <c:v>2375</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>32638</c:v>
-                </c:pt>
-                <c:pt idx="4">
                   <c:v>9990</c:v>
                 </c:pt>
               </c:numCache>
@@ -5322,34 +5328,31 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>CPU_Charts!$M$28:$M$32</c:f>
+              <c:f>CPU_Charts!$M$28:$M$31</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>2.5</c:v>
+                  <c:v>3.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4.2</c:v>
+                  <c:v>4.1900000000000004</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.7</c:v>
+                  <c:v>5.3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.8</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>3.6</c:v>
+                  <c:v>2.95</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>CPU_Charts!$N$28:$N$32</c:f>
+              <c:f>CPU_Charts!$N$28:$N$31</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>158</c:v>
                 </c:pt>
@@ -5360,9 +5363,6 @@
                   <c:v>82</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>946</c:v>
-                </c:pt>
-                <c:pt idx="4">
                   <c:v>186</c:v>
                 </c:pt>
               </c:numCache>
@@ -5556,16 +5556,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>447675</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>495300</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>901800</xdr:colOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>949425</xdr:colOff>
       <xdr:row>49</xdr:row>
-      <xdr:rowOff>113535</xdr:rowOff>
+      <xdr:rowOff>27810</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -5708,16 +5708,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>962025</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>454125</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>23940</xdr:rowOff>
+      <xdr:colOff>568425</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>42990</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -15889,7 +15889,7 @@
         <v>33</v>
       </c>
       <c r="M12">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="N12">
         <v>9.99</v>
@@ -15915,7 +15915,7 @@
         <v>60</v>
       </c>
       <c r="M13">
-        <v>4.2</v>
+        <v>4.1900000000000004</v>
       </c>
       <c r="N13">
         <v>9.0399999999999991</v>
@@ -15941,7 +15941,7 @@
         <v>35</v>
       </c>
       <c r="M14">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="N14">
         <v>2.94</v>
@@ -15964,16 +15964,13 @@
         <v>10112304.4</v>
       </c>
       <c r="L15" t="s">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="M15">
-        <v>1.8</v>
+        <v>2.95</v>
       </c>
       <c r="N15">
-        <v>52.8</v>
-      </c>
-      <c r="O15">
-        <v>2</v>
+        <v>8.6999999999999993</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
@@ -15990,13 +15987,16 @@
         <v>11328937.800000001</v>
       </c>
       <c r="L16" t="s">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="M16">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="N16">
-        <v>8.6999999999999993</v>
+        <v>52.8</v>
+      </c>
+      <c r="O16">
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
@@ -16067,7 +16067,8 @@
         <v>33</v>
       </c>
       <c r="M20">
-        <v>2.5</v>
+        <f>M12</f>
+        <v>3.5</v>
       </c>
       <c r="N20">
         <v>9969</v>
@@ -16090,7 +16091,8 @@
         <v>60</v>
       </c>
       <c r="M21">
-        <v>4.2</v>
+        <f t="shared" ref="M21:M24" si="0">M13</f>
+        <v>4.1900000000000004</v>
       </c>
       <c r="N21">
         <v>5879</v>
@@ -16113,7 +16115,8 @@
         <v>35</v>
       </c>
       <c r="M22">
-        <v>4.7</v>
+        <f t="shared" si="0"/>
+        <v>5.3</v>
       </c>
       <c r="N22">
         <v>2375</v>
@@ -16133,13 +16136,14 @@
         <v>18167731.899999999</v>
       </c>
       <c r="L23" t="s">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="M23">
-        <v>1.8</v>
+        <f>M15</f>
+        <v>2.95</v>
       </c>
       <c r="N23">
-        <v>32638</v>
+        <v>9990</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
@@ -16156,13 +16160,14 @@
         <v>18962636.800000001</v>
       </c>
       <c r="L24" t="s">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="M24">
-        <v>3.6</v>
+        <f>M16</f>
+        <v>1.8</v>
       </c>
       <c r="N24">
-        <v>9990</v>
+        <v>32638</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
@@ -16186,7 +16191,8 @@
         <v>33</v>
       </c>
       <c r="M28">
-        <v>2.5</v>
+        <f>M20</f>
+        <v>3.5</v>
       </c>
       <c r="N28">
         <v>158</v>
@@ -16205,11 +16211,18 @@
       <c r="D29" t="s">
         <v>38</v>
       </c>
+      <c r="E29" t="s">
+        <v>64</v>
+      </c>
+      <c r="F29" t="s">
+        <v>64</v>
+      </c>
       <c r="L29" t="s">
         <v>60</v>
       </c>
       <c r="M29">
-        <v>4.2</v>
+        <f t="shared" ref="M29:M32" si="1">M21</f>
+        <v>4.1900000000000004</v>
       </c>
       <c r="N29">
         <v>149</v>
@@ -16228,11 +16241,20 @@
       <c r="D30">
         <v>10055.1</v>
       </c>
+      <c r="E30">
+        <f t="shared" ref="E30:E51" si="2">9*A30*A30</f>
+        <v>90000</v>
+      </c>
+      <c r="F30">
+        <f>(E30-D30)/E30</f>
+        <v>0.8882766666666666</v>
+      </c>
       <c r="L30" t="s">
         <v>35</v>
       </c>
       <c r="M30">
-        <v>4.7</v>
+        <f t="shared" si="1"/>
+        <v>5.3</v>
       </c>
       <c r="N30">
         <v>82</v>
@@ -16251,14 +16273,23 @@
       <c r="D31">
         <v>123599.4</v>
       </c>
+      <c r="E31">
+        <f t="shared" si="2"/>
+        <v>9437184</v>
+      </c>
+      <c r="F31">
+        <f>(E31-D31)/E31</f>
+        <v>0.98690293629964188</v>
+      </c>
       <c r="L31" t="s">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="M31">
-        <v>1.8</v>
+        <f>M23</f>
+        <v>2.95</v>
       </c>
       <c r="N31">
-        <v>946</v>
+        <v>186</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
@@ -16274,17 +16305,26 @@
       <c r="D32">
         <v>685812.9</v>
       </c>
+      <c r="E32">
+        <f t="shared" si="2"/>
+        <v>235929600</v>
+      </c>
+      <c r="F32">
+        <f t="shared" ref="F32:F51" si="3">(E32-D32)/E32</f>
+        <v>0.9970931460062662</v>
+      </c>
       <c r="L32" t="s">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="M32">
-        <v>3.6</v>
+        <f>M24</f>
+        <v>1.8</v>
       </c>
       <c r="N32">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>10240</v>
       </c>
@@ -16297,8 +16337,16 @@
       <c r="D33">
         <v>1437986.3</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E33">
+        <f t="shared" si="2"/>
+        <v>943718400</v>
+      </c>
+      <c r="F33">
+        <f t="shared" si="3"/>
+        <v>0.99847625488705105</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>15360</v>
       </c>
@@ -16311,8 +16359,16 @@
       <c r="D34">
         <v>2230143.2999999998</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E34">
+        <f t="shared" si="2"/>
+        <v>2123366400</v>
+      </c>
+      <c r="F34">
+        <f t="shared" si="3"/>
+        <v>0.99894971338907879</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>20480</v>
       </c>
@@ -16325,8 +16381,16 @@
       <c r="D35">
         <v>2994569.5</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E35">
+        <f t="shared" si="2"/>
+        <v>3774873600</v>
+      </c>
+      <c r="F35">
+        <f t="shared" si="3"/>
+        <v>0.99920670999421013</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>25600</v>
       </c>
@@ -16339,8 +16403,16 @@
       <c r="D36">
         <v>3790005.1</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E36">
+        <f t="shared" si="2"/>
+        <v>5898240000</v>
+      </c>
+      <c r="F36">
+        <f t="shared" si="3"/>
+        <v>0.9993574345737033</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>30720</v>
       </c>
@@ -16353,8 +16425,16 @@
       <c r="D37">
         <v>4622930.7</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E37">
+        <f t="shared" si="2"/>
+        <v>8493465600</v>
+      </c>
+      <c r="F37">
+        <f t="shared" si="3"/>
+        <v>0.99945570737344247</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>35840</v>
       </c>
@@ -16367,8 +16447,16 @@
       <c r="D38">
         <v>5436622.9000000004</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E38">
+        <f t="shared" si="2"/>
+        <v>11560550400</v>
+      </c>
+      <c r="F38">
+        <f t="shared" si="3"/>
+        <v>0.99952972629227066</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>40960</v>
       </c>
@@ -16381,8 +16469,16 @@
       <c r="D39">
         <v>6394459.4000000004</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E39">
+        <f t="shared" si="2"/>
+        <v>15099494400</v>
+      </c>
+      <c r="F39">
+        <f t="shared" si="3"/>
+        <v>0.99957651168770267</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>46080</v>
       </c>
@@ -16395,8 +16491,16 @@
       <c r="D40">
         <v>7079063</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E40">
+        <f t="shared" si="2"/>
+        <v>19110297600</v>
+      </c>
+      <c r="F40">
+        <f t="shared" si="3"/>
+        <v>0.99962956814445425</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>51200</v>
       </c>
@@ -16409,8 +16513,16 @@
       <c r="D41">
         <v>7912422.2999999998</v>
       </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E41">
+        <f t="shared" si="2"/>
+        <v>23592960000</v>
+      </c>
+      <c r="F41">
+        <f t="shared" si="3"/>
+        <v>0.99966462782541909</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>56320</v>
       </c>
@@ -16423,8 +16535,16 @@
       <c r="D42">
         <v>8786584.5999999996</v>
       </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E42">
+        <f t="shared" si="2"/>
+        <v>28547481600</v>
+      </c>
+      <c r="F42">
+        <f t="shared" si="3"/>
+        <v>0.9996922115679725</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>61440</v>
       </c>
@@ -16437,8 +16557,16 @@
       <c r="D43">
         <v>9717019</v>
       </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E43">
+        <f t="shared" si="2"/>
+        <v>33973862400</v>
+      </c>
+      <c r="F43">
+        <f t="shared" si="3"/>
+        <v>0.99971398544900214</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>66560</v>
       </c>
@@ -16451,8 +16579,16 @@
       <c r="D44">
         <v>10567925.4</v>
       </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E44">
+        <f t="shared" si="2"/>
+        <v>39872102400</v>
+      </c>
+      <c r="F44">
+        <f t="shared" si="3"/>
+        <v>0.99973495439758897</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>71680</v>
       </c>
@@ -16465,8 +16601,16 @@
       <c r="D45">
         <v>11444969.800000001</v>
       </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E45">
+        <f t="shared" si="2"/>
+        <v>46242201600</v>
+      </c>
+      <c r="F45">
+        <f t="shared" si="3"/>
+        <v>0.99975249946144429</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>76800</v>
       </c>
@@ -16479,8 +16623,16 @@
       <c r="D46">
         <v>12222383.199999999</v>
       </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E46">
+        <f t="shared" si="2"/>
+        <v>53084160000</v>
+      </c>
+      <c r="F46">
+        <f t="shared" si="3"/>
+        <v>0.99976975460853112</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>81920</v>
       </c>
@@ -16493,8 +16645,16 @@
       <c r="D47">
         <v>12978764.1</v>
       </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E47">
+        <f t="shared" si="2"/>
+        <v>60397977600</v>
+      </c>
+      <c r="F47">
+        <f t="shared" si="3"/>
+        <v>0.99978511260449887</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>87040</v>
       </c>
@@ -16507,8 +16667,16 @@
       <c r="D48">
         <v>13897361.300000001</v>
       </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E48">
+        <f t="shared" si="2"/>
+        <v>68183654400</v>
+      </c>
+      <c r="F48">
+        <f t="shared" si="3"/>
+        <v>0.99979617752345051</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>92160</v>
       </c>
@@ -16521,8 +16689,16 @@
       <c r="D49">
         <v>14789982.699999999</v>
       </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E49">
+        <f t="shared" si="2"/>
+        <v>76441190400</v>
+      </c>
+      <c r="F49">
+        <f t="shared" si="3"/>
+        <v>0.99980651815307164</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>97280</v>
       </c>
@@ -16535,8 +16711,16 @@
       <c r="D50">
         <v>15417517.6</v>
       </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E50">
+        <f t="shared" si="2"/>
+        <v>85170585600</v>
+      </c>
+      <c r="F50">
+        <f t="shared" si="3"/>
+        <v>0.99981898072566489</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>102400</v>
       </c>
@@ -16549,13 +16733,21 @@
       <c r="D51">
         <v>16565274.4</v>
       </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E51">
+        <f t="shared" si="2"/>
+        <v>94371840000</v>
+      </c>
+      <c r="F51">
+        <f t="shared" si="3"/>
+        <v>0.99982446803622782</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>3</v>
       </c>
@@ -16569,7 +16761,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>100</v>
       </c>
@@ -16583,7 +16775,7 @@
         <v>37641.5</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>1024</v>
       </c>
@@ -16597,7 +16789,7 @@
         <v>137634.70000000001</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>5120</v>
       </c>
@@ -16611,7 +16803,7 @@
         <v>1301088.5</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>10240</v>
       </c>
@@ -16625,7 +16817,7 @@
         <v>2339185.2000000002</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>15360</v>
       </c>
@@ -16639,7 +16831,7 @@
         <v>3285558.6</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>20480</v>
       </c>
@@ -16653,7 +16845,7 @@
         <v>3808641</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>25600</v>
       </c>
@@ -16667,7 +16859,7 @@
         <v>4484253.5999999996</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>30720</v>
       </c>

--- a/aggregate_data.xlsx
+++ b/aggregate_data.xlsx
@@ -7,11 +7,10 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="CPU_Statistics" sheetId="2" r:id="rId4"/>
-    <sheet name="CPU_Charts" sheetId="3" r:id="rId6"/>
-    <sheet name="Memory_Statistics" sheetId="4" r:id="rId7"/>
-    <sheet name="Memory_Charts" sheetId="5" r:id="rId8"/>
+    <sheet name="sort_cpu_stats" sheetId="2" r:id="rId4"/>
+    <sheet name="sort_cpu_stats_cpu_charts" sheetId="3" r:id="rId6"/>
+    <sheet name="sort_mem_stats" sheetId="4" r:id="rId7"/>
+    <sheet name="sort_mem_stats_mem_charts" sheetId="5" r:id="rId8"/>
   </sheets>
   <calcPr calcId="122211"/>
 </workbook>
@@ -53,1012 +52,1021 @@
     <t>amd-ryzen-5</t>
   </si>
   <si>
-    <t>bubble-sort_amd-ryzen-5_01_100.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_amd-ryzen-5_02_1K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_amd-ryzen-5_03_5K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_amd-ryzen-5_04_10K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_amd-ryzen-5_05_15K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_amd-ryzen-5_06_20K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_amd-ryzen-5_07_25K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_amd-ryzen-5_08_30K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_amd-ryzen-5_09_35K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_amd-ryzen-5_10_40K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_amd-ryzen-5_11_45K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_amd-ryzen-5_12_50K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_amd-ryzen-5_13_55K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_amd-ryzen-5_14_60K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_amd-ryzen-5_15_65K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_amd-ryzen-5_16_70K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_amd-ryzen-5_17_75K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_amd-ryzen-5_18_80K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_amd-ryzen-5_19_85K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_amd-ryzen-5_20_90K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_amd-ryzen-5_21_95K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_amd-ryzen-5_22_100K.bin</t>
+    <t>sort_bubble-sort_amd-ryzen-5_01_100.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_amd-ryzen-5_02_1K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_amd-ryzen-5_03_5K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_amd-ryzen-5_04_10K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_amd-ryzen-5_05_15K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_amd-ryzen-5_06_20K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_amd-ryzen-5_07_25K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_amd-ryzen-5_08_30K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_amd-ryzen-5_09_35K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_amd-ryzen-5_10_40K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_amd-ryzen-5_11_45K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_amd-ryzen-5_12_50K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_amd-ryzen-5_13_55K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_amd-ryzen-5_14_60K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_amd-ryzen-5_15_65K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_amd-ryzen-5_16_70K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_amd-ryzen-5_17_75K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_amd-ryzen-5_18_80K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_amd-ryzen-5_19_85K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_amd-ryzen-5_20_90K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_amd-ryzen-5_21_95K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_amd-ryzen-5_22_100K.bin</t>
   </si>
   <si>
     <t>deck</t>
   </si>
   <si>
-    <t>bubble-sort_deck_01_100.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_deck_02_1K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_deck_03_5K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_deck_04_10K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_deck_05_15K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_deck_06_20K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_deck_07_25K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_deck_08_30K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_deck_09_35K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_deck_10_40K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_deck_11_45K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_deck_12_50K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_deck_13_55K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_deck_14_60K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_deck_15_65K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_deck_16_70K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_deck_17_75K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_deck_18_80K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_deck_19_85K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_deck_20_90K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_deck_21_95K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_deck_22_100K.bin</t>
+    <t>sort_bubble-sort_deck_01_100.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_deck_02_1K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_deck_03_5K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_deck_04_10K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_deck_05_15K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_deck_06_20K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_deck_07_25K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_deck_08_30K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_deck_09_35K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_deck_10_40K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_deck_11_45K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_deck_12_50K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_deck_13_55K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_deck_14_60K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_deck_15_65K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_deck_16_70K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_deck_17_75K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_deck_18_80K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_deck_19_85K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_deck_20_90K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_deck_21_95K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_deck_22_100K.bin</t>
   </si>
   <si>
     <t>i5-8600K</t>
   </si>
   <si>
-    <t>bubble-sort_i5-8600K_01_100.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_i5-8600K_02_1K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_i5-8600K_03_5K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_i5-8600K_04_10K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_i5-8600K_05_15K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_i5-8600K_06_20K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_i5-8600K_07_25K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_i5-8600K_08_30K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_i5-8600K_09_35K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_i5-8600K_10_40K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_i5-8600K_11_45K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_i5-8600K_12_50K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_i5-8600K_13_55K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_i5-8600K_14_60K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_i5-8600K_15_65K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_i5-8600K_16_70K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_i5-8600K_17_75K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_i5-8600K_18_80K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_i5-8600K_19_85K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_i5-8600K_20_90K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_i5-8600K_21_95K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_i5-8600K_22_100K.bin</t>
+    <t>sort_bubble-sort_i5-8600K_01_100.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_i5-8600K_02_1K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_i5-8600K_03_5K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_i5-8600K_04_10K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_i5-8600K_05_15K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_i5-8600K_06_20K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_i5-8600K_07_25K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_i5-8600K_08_30K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_i5-8600K_09_35K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_i5-8600K_10_40K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_i5-8600K_11_45K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_i5-8600K_12_50K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_i5-8600K_13_55K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_i5-8600K_14_60K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_i5-8600K_15_65K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_i5-8600K_16_70K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_i5-8600K_17_75K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_i5-8600K_18_80K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_i5-8600K_19_85K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_i5-8600K_20_90K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_i5-8600K_21_95K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_i5-8600K_22_100K.bin</t>
   </si>
   <si>
     <t>i9</t>
   </si>
   <si>
-    <t>bubble-sort_i9_01_100.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_i9_02_1K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_i9_03_5K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_i9_04_10K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_i9_05_15K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_i9_06_20K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_i9_07_25K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_i9_08_30K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_i9_09_35K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_i9_10_40K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_i9_11_45K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_i9_12_50K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_i9_13_55K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_i9_14_60K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_i9_15_65K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_i9_16_70K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_i9_17_75K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_i9_18_80K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_i9_19_85K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_i9_20_90K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_i9_21_95K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_i9_22_100K.bin</t>
+    <t>sort_bubble-sort_i9_01_100.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_i9_02_1K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_i9_03_5K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_i9_04_10K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_i9_05_15K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_i9_06_20K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_i9_07_25K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_i9_08_30K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_i9_09_35K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_i9_10_40K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_i9_11_45K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_i9_12_50K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_i9_13_55K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_i9_14_60K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_i9_15_65K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_i9_16_70K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_i9_17_75K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_i9_18_80K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_i9_19_85K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_i9_20_90K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_i9_21_95K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_i9_22_100K.bin</t>
   </si>
   <si>
     <t>rpi3</t>
   </si>
   <si>
-    <t>bubble-sort_rpi3_01_100.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_rpi3_02_1K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_rpi3_03_5K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_rpi3_04_10K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_rpi3_05_15K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_rpi3_06_20K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_rpi3_07_25K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_rpi3_08_30K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_rpi3_09_35K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_rpi3_10_40K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_rpi3_11_45K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_rpi3_12_50K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_rpi3_13_55K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_rpi3_14_60K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_rpi3_15_65K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_rpi3_16_70K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_rpi3_17_75K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_rpi3_18_80K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_rpi3_19_85K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_rpi3_20_90K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_rpi3_21_95K.bin</t>
-  </si>
-  <si>
-    <t>bubble-sort_rpi3_22_100K.bin</t>
+    <t>sort_bubble-sort_rpi3_01_100.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_rpi3_02_1K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_rpi3_03_5K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_rpi3_04_10K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_rpi3_05_15K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_rpi3_06_20K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_rpi3_07_25K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_rpi3_08_30K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_rpi3_09_35K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_rpi3_10_40K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_rpi3_11_45K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_rpi3_12_50K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_rpi3_13_55K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_rpi3_14_60K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_rpi3_15_65K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_rpi3_16_70K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_rpi3_17_75K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_rpi3_18_80K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_rpi3_19_85K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_rpi3_20_90K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_rpi3_21_95K.bin</t>
+  </si>
+  <si>
+    <t>sort_bubble-sort_rpi3_22_100K.bin</t>
   </si>
   <si>
     <t>merge-sort</t>
   </si>
   <si>
-    <t>merge-sort_amd-ryzen-5_01_100.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_amd-ryzen-5_02_1K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_amd-ryzen-5_03_5K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_amd-ryzen-5_04_10K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_amd-ryzen-5_05_15K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_amd-ryzen-5_06_20K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_amd-ryzen-5_07_25K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_amd-ryzen-5_08_30K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_amd-ryzen-5_09_35K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_amd-ryzen-5_10_40K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_amd-ryzen-5_11_45K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_amd-ryzen-5_12_50K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_amd-ryzen-5_13_55K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_amd-ryzen-5_14_60K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_amd-ryzen-5_15_65K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_amd-ryzen-5_16_70K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_amd-ryzen-5_17_75K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_amd-ryzen-5_18_80K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_amd-ryzen-5_19_85K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_amd-ryzen-5_20_90K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_amd-ryzen-5_21_95K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_amd-ryzen-5_22_100K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_deck_01_100.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_deck_02_1K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_deck_03_5K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_deck_04_10K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_deck_05_15K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_deck_06_20K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_deck_07_25K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_deck_08_30K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_deck_09_35K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_deck_10_40K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_deck_11_45K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_deck_12_50K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_deck_13_55K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_deck_14_60K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_deck_15_65K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_deck_16_70K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_deck_17_75K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_deck_18_80K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_deck_19_85K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_deck_20_90K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_deck_21_95K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_deck_22_100K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_i5-8600K_01_100.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_i5-8600K_02_1K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_i5-8600K_03_5K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_i5-8600K_04_10K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_i5-8600K_05_15K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_i5-8600K_06_20K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_i5-8600K_07_25K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_i5-8600K_08_30K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_i5-8600K_09_35K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_i5-8600K_10_40K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_i5-8600K_11_45K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_i5-8600K_12_50K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_i5-8600K_13_55K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_i5-8600K_14_60K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_i5-8600K_15_65K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_i5-8600K_16_70K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_i5-8600K_17_75K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_i5-8600K_18_80K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_i5-8600K_19_85K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_i5-8600K_20_90K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_i5-8600K_21_95K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_i5-8600K_22_100K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_i9_01_100.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_i9_02_1K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_i9_03_5K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_i9_04_10K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_i9_05_15K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_i9_06_20K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_i9_07_25K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_i9_08_30K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_i9_09_35K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_i9_10_40K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_i9_11_45K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_i9_12_50K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_i9_13_55K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_i9_14_60K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_i9_15_65K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_i9_16_70K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_i9_17_75K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_i9_18_80K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_i9_19_85K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_i9_20_90K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_i9_21_95K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_i9_22_100K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_rpi3_01_100.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_rpi3_02_1K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_rpi3_03_5K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_rpi3_04_10K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_rpi3_05_15K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_rpi3_06_20K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_rpi3_07_25K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_rpi3_08_30K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_rpi3_09_35K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_rpi3_10_40K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_rpi3_11_45K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_rpi3_12_50K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_rpi3_13_55K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_rpi3_14_60K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_rpi3_15_65K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_rpi3_16_70K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_rpi3_17_75K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_rpi3_18_80K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_rpi3_19_85K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_rpi3_20_90K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_rpi3_21_95K.bin</t>
-  </si>
-  <si>
-    <t>merge-sort_rpi3_22_100K.bin</t>
+    <t>sort_merge-sort_amd-ryzen-5_01_100.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_amd-ryzen-5_02_1K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_amd-ryzen-5_03_5K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_amd-ryzen-5_04_10K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_amd-ryzen-5_05_15K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_amd-ryzen-5_06_20K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_amd-ryzen-5_07_25K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_amd-ryzen-5_08_30K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_amd-ryzen-5_09_35K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_amd-ryzen-5_10_40K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_amd-ryzen-5_11_45K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_amd-ryzen-5_12_50K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_amd-ryzen-5_13_55K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_amd-ryzen-5_14_60K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_amd-ryzen-5_15_65K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_amd-ryzen-5_16_70K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_amd-ryzen-5_17_75K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_amd-ryzen-5_18_80K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_amd-ryzen-5_19_85K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_amd-ryzen-5_20_90K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_amd-ryzen-5_21_95K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_amd-ryzen-5_22_100K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_deck_01_100.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_deck_02_1K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_deck_03_5K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_deck_04_10K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_deck_05_15K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_deck_06_20K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_deck_07_25K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_deck_08_30K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_deck_09_35K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_deck_10_40K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_deck_11_45K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_deck_12_50K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_deck_13_55K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_deck_14_60K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_deck_15_65K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_deck_16_70K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_deck_17_75K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_deck_18_80K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_deck_19_85K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_deck_20_90K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_deck_21_95K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_deck_22_100K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_i5-8600K_01_100.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_i5-8600K_02_1K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_i5-8600K_03_5K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_i5-8600K_04_10K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_i5-8600K_05_15K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_i5-8600K_06_20K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_i5-8600K_07_25K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_i5-8600K_08_30K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_i5-8600K_09_35K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_i5-8600K_10_40K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_i5-8600K_11_45K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_i5-8600K_12_50K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_i5-8600K_13_55K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_i5-8600K_14_60K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_i5-8600K_15_65K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_i5-8600K_16_70K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_i5-8600K_17_75K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_i5-8600K_18_80K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_i5-8600K_19_85K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_i5-8600K_20_90K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_i5-8600K_21_95K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_i5-8600K_22_100K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_i9_01_100.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_i9_02_1K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_i9_03_5K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_i9_04_10K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_i9_05_15K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_i9_06_20K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_i9_07_25K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_i9_08_30K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_i9_09_35K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_i9_10_40K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_i9_11_45K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_i9_12_50K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_i9_13_55K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_i9_14_60K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_i9_15_65K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_i9_16_70K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_i9_17_75K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_i9_18_80K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_i9_19_85K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_i9_20_90K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_i9_21_95K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_i9_22_100K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_rpi3_01_100.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_rpi3_02_1K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_rpi3_03_5K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_rpi3_04_10K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_rpi3_05_15K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_rpi3_06_20K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_rpi3_07_25K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_rpi3_08_30K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_rpi3_09_35K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_rpi3_10_40K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_rpi3_11_45K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_rpi3_12_50K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_rpi3_13_55K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_rpi3_14_60K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_rpi3_15_65K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_rpi3_16_70K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_rpi3_17_75K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_rpi3_18_80K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_rpi3_19_85K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_rpi3_20_90K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_rpi3_21_95K.bin</t>
+  </si>
+  <si>
+    <t>sort_merge-sort_rpi3_22_100K.bin</t>
   </si>
   <si>
     <t>quick-sort</t>
   </si>
   <si>
-    <t>quick-sort_amd-ryzen-5_01_100.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_amd-ryzen-5_02_1K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_amd-ryzen-5_03_5K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_amd-ryzen-5_04_10K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_amd-ryzen-5_05_15K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_amd-ryzen-5_06_20K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_amd-ryzen-5_07_25K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_amd-ryzen-5_08_30K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_amd-ryzen-5_09_35K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_amd-ryzen-5_10_40K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_amd-ryzen-5_11_45K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_amd-ryzen-5_12_50K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_amd-ryzen-5_13_55K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_amd-ryzen-5_14_60K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_amd-ryzen-5_15_65K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_amd-ryzen-5_16_70K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_amd-ryzen-5_17_75K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_amd-ryzen-5_18_80K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_amd-ryzen-5_19_85K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_amd-ryzen-5_20_90K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_amd-ryzen-5_21_95K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_amd-ryzen-5_22_100K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_deck_01_100.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_deck_02_1K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_deck_03_5K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_deck_04_10K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_deck_05_15K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_deck_06_20K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_deck_07_25K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_deck_08_30K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_deck_09_35K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_deck_10_40K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_deck_11_45K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_deck_12_50K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_deck_13_55K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_deck_14_60K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_deck_15_65K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_deck_16_70K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_deck_17_75K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_deck_18_80K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_deck_19_85K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_deck_20_90K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_deck_21_95K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_deck_22_100K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_i5-8600K_01_100.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_i5-8600K_02_1K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_i5-8600K_03_5K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_i5-8600K_04_10K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_i5-8600K_05_15K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_i5-8600K_06_20K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_i5-8600K_07_25K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_i5-8600K_08_30K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_i5-8600K_09_35K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_i5-8600K_10_40K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_i5-8600K_11_45K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_i5-8600K_12_50K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_i5-8600K_13_55K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_i5-8600K_14_60K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_i5-8600K_15_65K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_i5-8600K_16_70K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_i5-8600K_17_75K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_i5-8600K_18_80K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_i5-8600K_19_85K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_i5-8600K_20_90K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_i5-8600K_21_95K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_i5-8600K_22_100K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_i9_01_100.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_i9_02_1K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_i9_03_5K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_i9_04_10K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_i9_05_15K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_i9_06_20K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_i9_07_25K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_i9_08_30K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_i9_09_35K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_i9_10_40K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_i9_11_45K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_i9_12_50K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_i9_13_55K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_i9_14_60K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_i9_15_65K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_i9_16_70K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_i9_17_75K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_i9_18_80K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_i9_19_85K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_i9_20_90K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_i9_21_95K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_i9_22_100K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_rpi3_01_100.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_rpi3_02_1K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_rpi3_03_5K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_rpi3_04_10K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_rpi3_05_15K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_rpi3_06_20K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_rpi3_07_25K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_rpi3_08_30K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_rpi3_09_35K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_rpi3_10_40K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_rpi3_11_45K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_rpi3_12_50K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_rpi3_13_55K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_rpi3_14_60K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_rpi3_15_65K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_rpi3_16_70K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_rpi3_17_75K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_rpi3_18_80K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_rpi3_19_85K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_rpi3_20_90K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_rpi3_21_95K.bin</t>
-  </si>
-  <si>
-    <t>quick-sort_rpi3_22_100K.bin</t>
+    <t>sort_quick-sort_amd-ryzen-5_01_100.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_amd-ryzen-5_02_1K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_amd-ryzen-5_03_5K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_amd-ryzen-5_04_10K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_amd-ryzen-5_05_15K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_amd-ryzen-5_06_20K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_amd-ryzen-5_07_25K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_amd-ryzen-5_08_30K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_amd-ryzen-5_09_35K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_amd-ryzen-5_10_40K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_amd-ryzen-5_11_45K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_amd-ryzen-5_12_50K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_amd-ryzen-5_13_55K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_amd-ryzen-5_14_60K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_amd-ryzen-5_15_65K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_amd-ryzen-5_16_70K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_amd-ryzen-5_17_75K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_amd-ryzen-5_18_80K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_amd-ryzen-5_19_85K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_amd-ryzen-5_20_90K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_amd-ryzen-5_21_95K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_amd-ryzen-5_22_100K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_deck_01_100.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_deck_02_1K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_deck_03_5K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_deck_04_10K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_deck_05_15K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_deck_06_20K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_deck_07_25K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_deck_08_30K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_deck_09_35K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_deck_10_40K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_deck_11_45K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_deck_12_50K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_deck_13_55K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_deck_14_60K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_deck_15_65K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_deck_16_70K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_deck_17_75K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_deck_18_80K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_deck_19_85K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_deck_20_90K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_deck_21_95K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_deck_22_100K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_i5-8600K_01_100.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_i5-8600K_02_1K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_i5-8600K_03_5K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_i5-8600K_04_10K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_i5-8600K_05_15K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_i5-8600K_06_20K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_i5-8600K_07_25K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_i5-8600K_08_30K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_i5-8600K_09_35K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_i5-8600K_10_40K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_i5-8600K_11_45K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_i5-8600K_12_50K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_i5-8600K_13_55K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_i5-8600K_14_60K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_i5-8600K_15_65K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_i5-8600K_16_70K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_i5-8600K_17_75K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_i5-8600K_18_80K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_i5-8600K_19_85K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_i5-8600K_20_90K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_i5-8600K_21_95K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_i5-8600K_22_100K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_i9_01_100.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_i9_02_1K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_i9_03_5K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_i9_04_10K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_i9_05_15K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_i9_06_20K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_i9_07_25K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_i9_08_30K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_i9_09_35K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_i9_10_40K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_i9_11_45K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_i9_12_50K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_i9_13_55K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_i9_14_60K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_i9_15_65K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_i9_16_70K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_i9_17_75K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_i9_18_80K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_i9_19_85K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_i9_20_90K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_i9_21_95K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_i9_22_100K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_rpi3_01_100.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_rpi3_02_1K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_rpi3_03_5K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_rpi3_04_10K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_rpi3_05_15K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_rpi3_06_20K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_rpi3_07_25K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_rpi3_08_30K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_rpi3_09_35K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_rpi3_10_40K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_rpi3_11_45K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_rpi3_12_50K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_rpi3_13_55K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_rpi3_14_60K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_rpi3_15_65K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_rpi3_16_70K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_rpi3_17_75K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_rpi3_18_80K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_rpi3_19_85K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_rpi3_20_90K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_rpi3_21_95K.bin</t>
+  </si>
+  <si>
+    <t>sort_quick-sort_rpi3_22_100K.bin</t>
+  </si>
+  <si>
+    <t>CPU Performance - i5-8600K</t>
+  </si>
+  <si>
+    <t>CPU Performance - i9</t>
+  </si>
+  <si>
+    <t>CPU Performance - rpi3</t>
   </si>
   <si>
     <t>CPU Performance - amd-ryzen-5</t>
@@ -1067,15 +1075,6 @@
     <t>CPU Performance - deck</t>
   </si>
   <si>
-    <t>CPU Performance - i5-8600K</t>
-  </si>
-  <si>
-    <t>CPU Performance - i9</t>
-  </si>
-  <si>
-    <t>CPU Performance - rpi3</t>
-  </si>
-  <si>
     <t>Total Allocated (bytes)</t>
   </si>
   <si>
@@ -1091,19 +1090,19 @@
     <t>Free Count</t>
   </si>
   <si>
+    <t>Memory Usage - i5-8600K</t>
+  </si>
+  <si>
+    <t>Memory Usage - i9</t>
+  </si>
+  <si>
+    <t>Memory Usage - rpi3</t>
+  </si>
+  <si>
     <t>Memory Usage - amd-ryzen-5</t>
   </si>
   <si>
     <t>Memory Usage - deck</t>
-  </si>
-  <si>
-    <t>Memory Usage - i5-8600K</t>
-  </si>
-  <si>
-    <t>Memory Usage - i9</t>
-  </si>
-  <si>
-    <t>Memory Usage - rpi3</t>
   </si>
 </sst>
 </file>
@@ -1405,14 +1404,6 @@
 </theme>
 </file>
 
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
@@ -11055,13 +11046,13 @@
         <v>100</v>
       </c>
       <c r="B3">
-        <v>89452.9</v>
+        <v>87712.9</v>
       </c>
       <c r="C3">
-        <v>941095.8</v>
+        <v>604761.6</v>
       </c>
       <c r="D3">
-        <v>39446.4</v>
+        <v>37641.5</v>
       </c>
     </row>
     <row r="4">
@@ -11069,13 +11060,13 @@
         <v>1024</v>
       </c>
       <c r="B4">
-        <v>8673015.9</v>
+        <v>7306501.7</v>
       </c>
       <c r="C4">
-        <v>10641478.5</v>
+        <v>6456141.4</v>
       </c>
       <c r="D4">
-        <v>207205</v>
+        <v>137634.7</v>
       </c>
     </row>
     <row r="5">
@@ -11083,13 +11074,13 @@
         <v>5120</v>
       </c>
       <c r="B5">
-        <v>215855984</v>
+        <v>175004186.8</v>
       </c>
       <c r="C5">
-        <v>51522013.1</v>
+        <v>31119339.2</v>
       </c>
       <c r="D5">
-        <v>932798.6</v>
+        <v>1301088.5</v>
       </c>
     </row>
     <row r="6">
@@ -11097,13 +11088,13 @@
         <v>10240</v>
       </c>
       <c r="B6">
-        <v>858544015.2</v>
+        <v>692206853</v>
       </c>
       <c r="C6">
-        <v>102634954.9</v>
+        <v>62097116.9</v>
       </c>
       <c r="D6">
-        <v>1722534.8</v>
+        <v>2339185.2</v>
       </c>
     </row>
     <row r="7">
@@ -11111,13 +11102,13 @@
         <v>15360</v>
       </c>
       <c r="B7">
-        <v>1953099635.9</v>
+        <v>1571365150.7</v>
       </c>
       <c r="C7">
-        <v>154174631.1</v>
+        <v>92226994.4</v>
       </c>
       <c r="D7">
-        <v>2623485.9</v>
+        <v>3285558.6</v>
       </c>
     </row>
     <row r="8">
@@ -11125,13 +11116,13 @@
         <v>20480</v>
       </c>
       <c r="B8">
-        <v>3433528456.4</v>
+        <v>2781892304</v>
       </c>
       <c r="C8">
-        <v>205524792.4</v>
+        <v>121092255.6</v>
       </c>
       <c r="D8">
-        <v>3655599.1</v>
+        <v>3808641</v>
       </c>
     </row>
     <row r="9">
@@ -11139,13 +11130,13 @@
         <v>25600</v>
       </c>
       <c r="B9">
-        <v>5401253159.4</v>
+        <v>4338337460.6</v>
       </c>
       <c r="C9">
-        <v>256159479.9</v>
+        <v>152818990</v>
       </c>
       <c r="D9">
-        <v>4307328.8</v>
+        <v>4484253.6</v>
       </c>
     </row>
     <row r="10">
@@ -11153,13 +11144,13 @@
         <v>30720</v>
       </c>
       <c r="B10">
-        <v>7820954640.5</v>
+        <v>6279970744.3</v>
       </c>
       <c r="C10">
-        <v>308156888.3</v>
+        <v>181529052.5</v>
       </c>
       <c r="D10">
-        <v>5529409.9</v>
+        <v>5446161</v>
       </c>
     </row>
     <row r="11">
@@ -11167,13 +11158,13 @@
         <v>35840</v>
       </c>
       <c r="B11">
-        <v>10630072784.8</v>
+        <v>8538052337.4</v>
       </c>
       <c r="C11">
-        <v>358817878</v>
+        <v>214028041.2</v>
       </c>
       <c r="D11">
-        <v>6575239.7</v>
+        <v>6106381.6</v>
       </c>
     </row>
     <row r="12">
@@ -11181,13 +11172,13 @@
         <v>40960</v>
       </c>
       <c r="B12">
-        <v>13928839418.8</v>
+        <v>11212164187.8</v>
       </c>
       <c r="C12">
-        <v>409841265.7</v>
+        <v>241991136.4</v>
       </c>
       <c r="D12">
-        <v>7389001.2</v>
+        <v>6769567.5</v>
       </c>
     </row>
     <row r="13">
@@ -11195,13 +11186,13 @@
         <v>46080</v>
       </c>
       <c r="B13">
-        <v>17558931813.1</v>
+        <v>14117560892.3</v>
       </c>
       <c r="C13">
-        <v>462516625.9</v>
+        <v>268016892.8</v>
       </c>
       <c r="D13">
-        <v>8247768.3</v>
+        <v>7489102.8</v>
       </c>
     </row>
     <row r="14">
@@ -11209,13 +11200,13 @@
         <v>51200</v>
       </c>
       <c r="B14">
-        <v>21734468197.5</v>
+        <v>17486221346.3</v>
       </c>
       <c r="C14">
-        <v>511187265.2</v>
+        <v>301571247.2</v>
       </c>
       <c r="D14">
-        <v>9066810.2</v>
+        <v>8219346</v>
       </c>
     </row>
     <row r="15">
@@ -11223,13 +11214,13 @@
         <v>56320</v>
       </c>
       <c r="B15">
-        <v>26239442069.3</v>
+        <v>21098876885.7</v>
       </c>
       <c r="C15">
-        <v>564640102.9</v>
+        <v>328156144.5</v>
       </c>
       <c r="D15">
-        <v>10112304.4</v>
+        <v>8956698</v>
       </c>
     </row>
     <row r="16">
@@ -11237,13 +11228,13 @@
         <v>61440</v>
       </c>
       <c r="B16">
-        <v>31291654033.9</v>
+        <v>25162952466</v>
       </c>
       <c r="C16">
-        <v>614037176.5</v>
+        <v>360783618.9</v>
       </c>
       <c r="D16">
-        <v>11328937.8</v>
+        <v>9765886.9</v>
       </c>
     </row>
     <row r="17">
@@ -11251,13 +11242,13 @@
         <v>66560</v>
       </c>
       <c r="B17">
-        <v>36682712680.8</v>
+        <v>29496528298.4</v>
       </c>
       <c r="C17">
-        <v>667235027.9</v>
+        <v>391002385.6</v>
       </c>
       <c r="D17">
-        <v>12058555.2</v>
+        <v>10166746.6</v>
       </c>
     </row>
     <row r="18">
@@ -11265,13 +11256,13 @@
         <v>71680</v>
       </c>
       <c r="B18">
-        <v>42621988840.4</v>
+        <v>34285335375.5</v>
       </c>
       <c r="C18">
-        <v>717975603.1</v>
+        <v>422921747.4</v>
       </c>
       <c r="D18">
-        <v>13105474.4</v>
+        <v>9893848.1</v>
       </c>
     </row>
     <row r="19">
@@ -11279,13 +11270,13 @@
         <v>76800</v>
       </c>
       <c r="B19">
-        <v>48839209437.4</v>
+        <v>39216374986.3</v>
       </c>
       <c r="C19">
-        <v>767957804.3</v>
+        <v>455854237.1</v>
       </c>
       <c r="D19">
-        <v>14270733</v>
+        <v>12114077.6</v>
       </c>
     </row>
     <row r="20">
@@ -11293,13 +11284,13 @@
         <v>81920</v>
       </c>
       <c r="B20">
-        <v>55587646018.6</v>
+        <v>44619467243.2</v>
       </c>
       <c r="C20">
-        <v>818475216.9</v>
+        <v>473085876.4</v>
       </c>
       <c r="D20">
-        <v>16275007.6</v>
+        <v>12642150.4</v>
       </c>
     </row>
     <row r="21">
@@ -11307,13 +11298,13 @@
         <v>87040</v>
       </c>
       <c r="B21">
-        <v>63436063197.6</v>
+        <v>51049435564.7</v>
       </c>
       <c r="C21">
-        <v>871442012.3</v>
+        <v>519246877.2</v>
       </c>
       <c r="D21">
-        <v>17328072.9</v>
+        <v>12227992.2</v>
       </c>
     </row>
     <row r="22">
@@ -11321,13 +11312,13 @@
         <v>92160</v>
       </c>
       <c r="B22">
-        <v>72342763670.3</v>
+        <v>56479524530.1</v>
       </c>
       <c r="C22">
-        <v>907252602.4</v>
+        <v>533442170.4</v>
       </c>
       <c r="D22">
-        <v>17365871.5</v>
+        <v>13096093.4</v>
       </c>
     </row>
     <row r="23">
@@ -11335,13 +11326,13 @@
         <v>97280</v>
       </c>
       <c r="B23">
-        <v>80858923500.6</v>
+        <v>63133498743</v>
       </c>
       <c r="C23">
-        <v>974526797.3</v>
+        <v>572680741.5</v>
       </c>
       <c r="D23">
-        <v>18167731.9</v>
+        <v>13649812.2</v>
       </c>
     </row>
     <row r="24">
@@ -11349,13 +11340,13 @@
         <v>102400</v>
       </c>
       <c r="B24">
-        <v>89488301072.8</v>
+        <v>69878666113</v>
       </c>
       <c r="C24">
-        <v>1024637142.2</v>
+        <v>605127322</v>
       </c>
       <c r="D24">
-        <v>18962636.8</v>
+        <v>14540352.3</v>
       </c>
     </row>
     <row r="28">
@@ -11382,13 +11373,13 @@
         <v>100</v>
       </c>
       <c r="B30">
-        <v>82963.4</v>
+        <v>29812.7</v>
       </c>
       <c r="C30">
-        <v>928269.2</v>
+        <v>228556.6</v>
       </c>
       <c r="D30">
-        <v>10055.1</v>
+        <v>4534.7</v>
       </c>
     </row>
     <row r="31">
@@ -11396,13 +11387,13 @@
         <v>1024</v>
       </c>
       <c r="B31">
-        <v>9827302</v>
+        <v>2779192.4</v>
       </c>
       <c r="C31">
-        <v>10278739.1</v>
+        <v>2433976.4</v>
       </c>
       <c r="D31">
-        <v>123599.4</v>
+        <v>71213.6</v>
       </c>
     </row>
     <row r="32">
@@ -11410,13 +11401,13 @@
         <v>5120</v>
       </c>
       <c r="B32">
-        <v>179148840.3</v>
+        <v>71031572.7</v>
       </c>
       <c r="C32">
-        <v>51183088.8</v>
+        <v>12705733.4</v>
       </c>
       <c r="D32">
-        <v>685812.9</v>
+        <v>383914.5</v>
       </c>
     </row>
     <row r="33">
@@ -11424,13 +11415,13 @@
         <v>10240</v>
       </c>
       <c r="B33">
-        <v>713713868.4</v>
+        <v>285652901.5</v>
       </c>
       <c r="C33">
-        <v>101877702.7</v>
+        <v>25389107.5</v>
       </c>
       <c r="D33">
-        <v>1437986.3</v>
+        <v>780722.2</v>
       </c>
     </row>
     <row r="34">
@@ -11438,13 +11429,13 @@
         <v>15360</v>
       </c>
       <c r="B34">
-        <v>1610808023.7</v>
+        <v>633566838</v>
       </c>
       <c r="C34">
-        <v>152962324.1</v>
+        <v>36383113.1</v>
       </c>
       <c r="D34">
-        <v>2230143.3</v>
+        <v>1197383.1</v>
       </c>
     </row>
     <row r="35">
@@ -11452,13 +11443,13 @@
         <v>20480</v>
       </c>
       <c r="B35">
-        <v>2846276388.7</v>
+        <v>1115376821.8</v>
       </c>
       <c r="C35">
-        <v>204053053.6</v>
+        <v>48623879.4</v>
       </c>
       <c r="D35">
-        <v>2994569.5</v>
+        <v>1617710.5</v>
       </c>
     </row>
     <row r="36">
@@ -11466,13 +11457,13 @@
         <v>25600</v>
       </c>
       <c r="B36">
-        <v>4433773216.4</v>
+        <v>1760931144</v>
       </c>
       <c r="C36">
-        <v>254840481.7</v>
+        <v>60985352.4</v>
       </c>
       <c r="D36">
-        <v>3790005.1</v>
+        <v>2003608</v>
       </c>
     </row>
     <row r="37">
@@ -11480,13 +11471,13 @@
         <v>30720</v>
       </c>
       <c r="B37">
-        <v>6518896175</v>
+        <v>2595987199</v>
       </c>
       <c r="C37">
-        <v>306111723.1</v>
+        <v>72569335</v>
       </c>
       <c r="D37">
-        <v>4622930.7</v>
+        <v>2446195.5</v>
       </c>
     </row>
     <row r="38">
@@ -11494,13 +11485,13 @@
         <v>35840</v>
       </c>
       <c r="B38">
-        <v>8815969638.3</v>
+        <v>3461565794.5</v>
       </c>
       <c r="C38">
-        <v>357054966</v>
+        <v>85059505.7</v>
       </c>
       <c r="D38">
-        <v>5436622.9</v>
+        <v>2859693.4</v>
       </c>
     </row>
     <row r="39">
@@ -11508,13 +11499,13 @@
         <v>40960</v>
       </c>
       <c r="B39">
-        <v>11585239740.2</v>
+        <v>4695119000.9</v>
       </c>
       <c r="C39">
-        <v>407498526.5</v>
+        <v>96687521.5</v>
       </c>
       <c r="D39">
-        <v>6394459.4</v>
+        <v>3316331.1</v>
       </c>
     </row>
     <row r="40">
@@ -11522,13 +11513,13 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>14567175307.8</v>
+        <v>5725006478.3</v>
       </c>
       <c r="C40">
-        <v>461330246.7</v>
+        <v>114396494.4</v>
       </c>
       <c r="D40">
-        <v>7079063</v>
+        <v>3721145.5</v>
       </c>
     </row>
     <row r="41">
@@ -11536,13 +11527,13 @@
         <v>51200</v>
       </c>
       <c r="B41">
-        <v>18091568600.6</v>
+        <v>7114505067.9</v>
       </c>
       <c r="C41">
-        <v>506856371.5</v>
+        <v>128073697.4</v>
       </c>
       <c r="D41">
-        <v>7912422.3</v>
+        <v>4190075.6</v>
       </c>
     </row>
     <row r="42">
@@ -11550,13 +11541,13 @@
         <v>56320</v>
       </c>
       <c r="B42">
-        <v>21710078733.8</v>
+        <v>8592723655.9</v>
       </c>
       <c r="C42">
-        <v>563467551.2</v>
+        <v>133712954.7</v>
       </c>
       <c r="D42">
-        <v>8786584.6</v>
+        <v>4569048</v>
       </c>
     </row>
     <row r="43">
@@ -11564,13 +11555,13 @@
         <v>61440</v>
       </c>
       <c r="B43">
-        <v>26149479114.6</v>
+        <v>10218618516.7</v>
       </c>
       <c r="C43">
-        <v>613243337.9</v>
+        <v>146554587.8</v>
       </c>
       <c r="D43">
-        <v>9717019</v>
+        <v>5005579.9</v>
       </c>
     </row>
     <row r="44">
@@ -11578,13 +11569,13 @@
         <v>66560</v>
       </c>
       <c r="B44">
-        <v>30474127218.4</v>
+        <v>11958599692.9</v>
       </c>
       <c r="C44">
-        <v>661409185.9</v>
+        <v>158203280.2</v>
       </c>
       <c r="D44">
-        <v>10567925.4</v>
+        <v>5410891.7</v>
       </c>
     </row>
     <row r="45">
@@ -11592,13 +11583,13 @@
         <v>71680</v>
       </c>
       <c r="B45">
-        <v>35765170742.2</v>
+        <v>13956227440.6</v>
       </c>
       <c r="C45">
-        <v>713264838.8</v>
+        <v>170926709.3</v>
       </c>
       <c r="D45">
-        <v>11444969.8</v>
+        <v>5874645.8</v>
       </c>
     </row>
     <row r="46">
@@ -11606,13 +11597,13 @@
         <v>76800</v>
       </c>
       <c r="B46">
-        <v>40081367236.2</v>
+        <v>15974329050.1</v>
       </c>
       <c r="C46">
-        <v>762123602</v>
+        <v>180511694.5</v>
       </c>
       <c r="D46">
-        <v>12222383.2</v>
+        <v>6301448.9</v>
       </c>
     </row>
     <row r="47">
@@ -11620,13 +11611,13 @@
         <v>81920</v>
       </c>
       <c r="B47">
-        <v>46179802809.9</v>
+        <v>18222895840.3</v>
       </c>
       <c r="C47">
-        <v>819105618.2</v>
+        <v>193626605.6</v>
       </c>
       <c r="D47">
-        <v>12978764.1</v>
+        <v>6677578.1</v>
       </c>
     </row>
     <row r="48">
@@ -11634,13 +11625,13 @@
         <v>87040</v>
       </c>
       <c r="B48">
-        <v>51951214409</v>
+        <v>20559390221.8</v>
       </c>
       <c r="C48">
-        <v>864279368.6</v>
+        <v>208244752.5</v>
       </c>
       <c r="D48">
-        <v>13897361.3</v>
+        <v>7194367</v>
       </c>
     </row>
     <row r="49">
@@ -11648,13 +11639,13 @@
         <v>92160</v>
       </c>
       <c r="B49">
-        <v>58742794034.3</v>
+        <v>22971938112.2</v>
       </c>
       <c r="C49">
-        <v>918100522.6</v>
+        <v>213587381.4</v>
       </c>
       <c r="D49">
-        <v>14789982.7</v>
+        <v>7653507.4</v>
       </c>
     </row>
     <row r="50">
@@ -11662,13 +11653,13 @@
         <v>97280</v>
       </c>
       <c r="B50">
-        <v>65638213779.5</v>
+        <v>25709704095.3</v>
       </c>
       <c r="C50">
-        <v>971643274.9</v>
+        <v>230312851.5</v>
       </c>
       <c r="D50">
-        <v>15417517.6</v>
+        <v>8008970.7</v>
       </c>
     </row>
     <row r="51">
@@ -11676,13 +11667,13 @@
         <v>102400</v>
       </c>
       <c r="B51">
-        <v>71617023099.5</v>
+        <v>28444096006</v>
       </c>
       <c r="C51">
-        <v>1025923888.2</v>
+        <v>243367823.3</v>
       </c>
       <c r="D51">
-        <v>16565274.4</v>
+        <v>8492545.1</v>
       </c>
     </row>
     <row r="55">
@@ -11709,13 +11700,13 @@
         <v>100</v>
       </c>
       <c r="B57">
-        <v>87712.9</v>
+        <v>557762.8</v>
       </c>
       <c r="C57">
-        <v>604761.6</v>
+        <v>3288990.9</v>
       </c>
       <c r="D57">
-        <v>37641.5</v>
+        <v>50780.4</v>
       </c>
     </row>
     <row r="58">
@@ -11723,13 +11714,13 @@
         <v>1024</v>
       </c>
       <c r="B58">
-        <v>7306501.7</v>
+        <v>56498903.5</v>
       </c>
       <c r="C58">
-        <v>6456141.4</v>
+        <v>33342812.4</v>
       </c>
       <c r="D58">
-        <v>137634.7</v>
+        <v>677621.2</v>
       </c>
     </row>
     <row r="59">
@@ -11737,13 +11728,13 @@
         <v>5120</v>
       </c>
       <c r="B59">
-        <v>175004186.8</v>
+        <v>1406698940.4</v>
       </c>
       <c r="C59">
-        <v>31119339.2</v>
+        <v>165331042.4</v>
       </c>
       <c r="D59">
-        <v>1301088.5</v>
+        <v>3831677.7</v>
       </c>
     </row>
     <row r="60">
@@ -11751,13 +11742,13 @@
         <v>10240</v>
       </c>
       <c r="B60">
-        <v>692206853</v>
+        <v>5578436295.1</v>
       </c>
       <c r="C60">
-        <v>62097116.9</v>
+        <v>330034105.4</v>
       </c>
       <c r="D60">
-        <v>2339185.2</v>
+        <v>8135072.9</v>
       </c>
     </row>
     <row r="61">
@@ -11765,13 +11756,13 @@
         <v>15360</v>
       </c>
       <c r="B61">
-        <v>1571365150.7</v>
+        <v>12684706235</v>
       </c>
       <c r="C61">
-        <v>92226994.4</v>
+        <v>490022168.3</v>
       </c>
       <c r="D61">
-        <v>3285558.6</v>
+        <v>12598700.2</v>
       </c>
     </row>
     <row r="62">
@@ -11779,13 +11770,13 @@
         <v>20480</v>
       </c>
       <c r="B62">
-        <v>2781892304</v>
+        <v>22322146682.4</v>
       </c>
       <c r="C62">
-        <v>121092255.6</v>
+        <v>661321424.9</v>
       </c>
       <c r="D62">
-        <v>3808641</v>
+        <v>17229481.4</v>
       </c>
     </row>
     <row r="63">
@@ -11793,13 +11784,13 @@
         <v>25600</v>
       </c>
       <c r="B63">
-        <v>4338337460.6</v>
+        <v>35129432253.3</v>
       </c>
       <c r="C63">
-        <v>152818990</v>
+        <v>830303817</v>
       </c>
       <c r="D63">
-        <v>4484253.6</v>
+        <v>22061593.2</v>
       </c>
     </row>
     <row r="64">
@@ -11807,13 +11798,13 @@
         <v>30720</v>
       </c>
       <c r="B64">
-        <v>6279970744.3</v>
+        <v>50811537498.2</v>
       </c>
       <c r="C64">
-        <v>181529052.5</v>
+        <v>992089360.5</v>
       </c>
       <c r="D64">
-        <v>5446161</v>
+        <v>27100394.5</v>
       </c>
     </row>
     <row r="65">
@@ -11821,13 +11812,13 @@
         <v>35840</v>
       </c>
       <c r="B65">
-        <v>8538052337.4</v>
+        <v>69105582394.1</v>
       </c>
       <c r="C65">
-        <v>214028041.2</v>
+        <v>1166714536.8</v>
       </c>
       <c r="D65">
-        <v>6106381.6</v>
+        <v>31610119.5</v>
       </c>
     </row>
     <row r="66">
@@ -11835,13 +11826,13 @@
         <v>40960</v>
       </c>
       <c r="B66">
-        <v>11212164187.8</v>
+        <v>90692851024.3</v>
       </c>
       <c r="C66">
-        <v>241991136.4</v>
+        <v>1333042823.5</v>
       </c>
       <c r="D66">
-        <v>6769567.5</v>
+        <v>37769774.8</v>
       </c>
     </row>
     <row r="67">
@@ -11849,13 +11840,13 @@
         <v>46080</v>
       </c>
       <c r="B67">
-        <v>14117560892.3</v>
+        <v>114442607094.5</v>
       </c>
       <c r="C67">
-        <v>268016892.8</v>
+        <v>1490738197.6</v>
       </c>
       <c r="D67">
-        <v>7489102.8</v>
+        <v>41976279.4</v>
       </c>
     </row>
     <row r="68">
@@ -11863,13 +11854,13 @@
         <v>51200</v>
       </c>
       <c r="B68">
-        <v>17486221346.3</v>
+        <v>141530964374.9</v>
       </c>
       <c r="C68">
-        <v>301571247.2</v>
+        <v>1684184290.5</v>
       </c>
       <c r="D68">
-        <v>8219346</v>
+        <v>46097149.5</v>
       </c>
     </row>
     <row r="69">
@@ -11877,13 +11868,13 @@
         <v>56320</v>
       </c>
       <c r="B69">
-        <v>21098876885.7</v>
+        <v>170701367450.8</v>
       </c>
       <c r="C69">
-        <v>328156144.5</v>
+        <v>1823900667</v>
       </c>
       <c r="D69">
-        <v>8956698</v>
+        <v>51871653.3</v>
       </c>
     </row>
     <row r="70">
@@ -11891,13 +11882,13 @@
         <v>61440</v>
       </c>
       <c r="B70">
-        <v>25162952466</v>
+        <v>203820136377.7</v>
       </c>
       <c r="C70">
-        <v>360783618.9</v>
+        <v>1985824590.8</v>
       </c>
       <c r="D70">
-        <v>9765886.9</v>
+        <v>57466128.2</v>
       </c>
     </row>
     <row r="71">
@@ -11905,13 +11896,13 @@
         <v>66560</v>
       </c>
       <c r="B71">
-        <v>29496528298.4</v>
+        <v>239084713971.6</v>
       </c>
       <c r="C71">
-        <v>391002385.6</v>
+        <v>2201072592.7</v>
       </c>
       <c r="D71">
-        <v>10166746.6</v>
+        <v>61991377.5</v>
       </c>
     </row>
     <row r="72">
@@ -11919,13 +11910,13 @@
         <v>71680</v>
       </c>
       <c r="B72">
-        <v>34285335375.5</v>
+        <v>277618517241</v>
       </c>
       <c r="C72">
-        <v>422921747.4</v>
+        <v>2360389873.2</v>
       </c>
       <c r="D72">
-        <v>9893848.1</v>
+        <v>67354625.4</v>
       </c>
     </row>
     <row r="73">
@@ -11933,13 +11924,13 @@
         <v>76800</v>
       </c>
       <c r="B73">
-        <v>39216374986.3</v>
+        <v>317605707827.7</v>
       </c>
       <c r="C73">
-        <v>455854237.1</v>
+        <v>2518559857.4</v>
       </c>
       <c r="D73">
-        <v>12114077.6</v>
+        <v>72080043.6</v>
       </c>
     </row>
     <row r="74">
@@ -11947,13 +11938,13 @@
         <v>81920</v>
       </c>
       <c r="B74">
-        <v>44619467243.2</v>
+        <v>361211297263.7</v>
       </c>
       <c r="C74">
-        <v>473085876.4</v>
+        <v>2676024061.2</v>
       </c>
       <c r="D74">
-        <v>12642150.4</v>
+        <v>78243779.9</v>
       </c>
     </row>
     <row r="75">
@@ -11961,13 +11952,13 @@
         <v>87040</v>
       </c>
       <c r="B75">
-        <v>51049435564.7</v>
+        <v>408896660387.3</v>
       </c>
       <c r="C75">
-        <v>519246877.2</v>
+        <v>2842473626</v>
       </c>
       <c r="D75">
-        <v>12227992.2</v>
+        <v>83677849.2</v>
       </c>
     </row>
     <row r="76">
@@ -11975,13 +11966,13 @@
         <v>92160</v>
       </c>
       <c r="B76">
-        <v>56479524530.1</v>
+        <v>457546233055.2</v>
       </c>
       <c r="C76">
-        <v>533442170.4</v>
+        <v>3008711128.9</v>
       </c>
       <c r="D76">
-        <v>13096093.4</v>
+        <v>89536990</v>
       </c>
     </row>
     <row r="77">
@@ -11989,13 +11980,13 @@
         <v>97280</v>
       </c>
       <c r="B77">
-        <v>63133498743</v>
+        <v>511226726172.7</v>
       </c>
       <c r="C77">
-        <v>572680741.5</v>
+        <v>3163661340.3</v>
       </c>
       <c r="D77">
-        <v>13649812.2</v>
+        <v>93289289.7</v>
       </c>
     </row>
     <row r="78">
@@ -12003,13 +11994,13 @@
         <v>102400</v>
       </c>
       <c r="B78">
-        <v>69878666113</v>
+        <v>566110304268.6</v>
       </c>
       <c r="C78">
-        <v>605127322</v>
+        <v>3336970656.1</v>
       </c>
       <c r="D78">
-        <v>14540352.3</v>
+        <v>99630069.3</v>
       </c>
     </row>
     <row r="82">
@@ -12036,13 +12027,13 @@
         <v>100</v>
       </c>
       <c r="B84">
-        <v>29812.7</v>
+        <v>89452.9</v>
       </c>
       <c r="C84">
-        <v>228556.6</v>
+        <v>941095.8</v>
       </c>
       <c r="D84">
-        <v>4534.7</v>
+        <v>39446.4</v>
       </c>
     </row>
     <row r="85">
@@ -12050,13 +12041,13 @@
         <v>1024</v>
       </c>
       <c r="B85">
-        <v>2779192.4</v>
+        <v>8673015.9</v>
       </c>
       <c r="C85">
-        <v>2433976.4</v>
+        <v>10641478.5</v>
       </c>
       <c r="D85">
-        <v>71213.6</v>
+        <v>207205</v>
       </c>
     </row>
     <row r="86">
@@ -12064,13 +12055,13 @@
         <v>5120</v>
       </c>
       <c r="B86">
-        <v>71031572.7</v>
+        <v>215855984</v>
       </c>
       <c r="C86">
-        <v>12705733.4</v>
+        <v>51522013.1</v>
       </c>
       <c r="D86">
-        <v>383914.5</v>
+        <v>932798.6</v>
       </c>
     </row>
     <row r="87">
@@ -12078,13 +12069,13 @@
         <v>10240</v>
       </c>
       <c r="B87">
-        <v>285652901.5</v>
+        <v>858544015.2</v>
       </c>
       <c r="C87">
-        <v>25389107.5</v>
+        <v>102634954.9</v>
       </c>
       <c r="D87">
-        <v>780722.2</v>
+        <v>1722534.8</v>
       </c>
     </row>
     <row r="88">
@@ -12092,13 +12083,13 @@
         <v>15360</v>
       </c>
       <c r="B88">
-        <v>633566838</v>
+        <v>1953099635.9</v>
       </c>
       <c r="C88">
-        <v>36383113.1</v>
+        <v>154174631.1</v>
       </c>
       <c r="D88">
-        <v>1197383.1</v>
+        <v>2623485.9</v>
       </c>
     </row>
     <row r="89">
@@ -12106,13 +12097,13 @@
         <v>20480</v>
       </c>
       <c r="B89">
-        <v>1115376821.8</v>
+        <v>3433528456.4</v>
       </c>
       <c r="C89">
-        <v>48623879.4</v>
+        <v>205524792.4</v>
       </c>
       <c r="D89">
-        <v>1617710.5</v>
+        <v>3655599.1</v>
       </c>
     </row>
     <row r="90">
@@ -12120,13 +12111,13 @@
         <v>25600</v>
       </c>
       <c r="B90">
-        <v>1760931144</v>
+        <v>5401253159.4</v>
       </c>
       <c r="C90">
-        <v>60985352.4</v>
+        <v>256159479.9</v>
       </c>
       <c r="D90">
-        <v>2003608</v>
+        <v>4307328.8</v>
       </c>
     </row>
     <row r="91">
@@ -12134,13 +12125,13 @@
         <v>30720</v>
       </c>
       <c r="B91">
-        <v>2595987199</v>
+        <v>7820954640.5</v>
       </c>
       <c r="C91">
-        <v>72569335</v>
+        <v>308156888.3</v>
       </c>
       <c r="D91">
-        <v>2446195.5</v>
+        <v>5529409.9</v>
       </c>
     </row>
     <row r="92">
@@ -12148,13 +12139,13 @@
         <v>35840</v>
       </c>
       <c r="B92">
-        <v>3461565794.5</v>
+        <v>10630072784.8</v>
       </c>
       <c r="C92">
-        <v>85059505.7</v>
+        <v>358817878</v>
       </c>
       <c r="D92">
-        <v>2859693.4</v>
+        <v>6575239.7</v>
       </c>
     </row>
     <row r="93">
@@ -12162,13 +12153,13 @@
         <v>40960</v>
       </c>
       <c r="B93">
-        <v>4695119000.9</v>
+        <v>13928839418.8</v>
       </c>
       <c r="C93">
-        <v>96687521.5</v>
+        <v>409841265.7</v>
       </c>
       <c r="D93">
-        <v>3316331.1</v>
+        <v>7389001.2</v>
       </c>
     </row>
     <row r="94">
@@ -12176,13 +12167,13 @@
         <v>46080</v>
       </c>
       <c r="B94">
-        <v>5725006478.3</v>
+        <v>17558931813.1</v>
       </c>
       <c r="C94">
-        <v>114396494.4</v>
+        <v>462516625.9</v>
       </c>
       <c r="D94">
-        <v>3721145.5</v>
+        <v>8247768.3</v>
       </c>
     </row>
     <row r="95">
@@ -12190,13 +12181,13 @@
         <v>51200</v>
       </c>
       <c r="B95">
-        <v>7114505067.9</v>
+        <v>21734468197.5</v>
       </c>
       <c r="C95">
-        <v>128073697.4</v>
+        <v>511187265.2</v>
       </c>
       <c r="D95">
-        <v>4190075.6</v>
+        <v>9066810.2</v>
       </c>
     </row>
     <row r="96">
@@ -12204,13 +12195,13 @@
         <v>56320</v>
       </c>
       <c r="B96">
-        <v>8592723655.9</v>
+        <v>26239442069.3</v>
       </c>
       <c r="C96">
-        <v>133712954.7</v>
+        <v>564640102.9</v>
       </c>
       <c r="D96">
-        <v>4569048</v>
+        <v>10112304.4</v>
       </c>
     </row>
     <row r="97">
@@ -12218,13 +12209,13 @@
         <v>61440</v>
       </c>
       <c r="B97">
-        <v>10218618516.7</v>
+        <v>31291654033.9</v>
       </c>
       <c r="C97">
-        <v>146554587.8</v>
+        <v>614037176.5</v>
       </c>
       <c r="D97">
-        <v>5005579.9</v>
+        <v>11328937.8</v>
       </c>
     </row>
     <row r="98">
@@ -12232,13 +12223,13 @@
         <v>66560</v>
       </c>
       <c r="B98">
-        <v>11958599692.9</v>
+        <v>36682712680.8</v>
       </c>
       <c r="C98">
-        <v>158203280.2</v>
+        <v>667235027.9</v>
       </c>
       <c r="D98">
-        <v>5410891.7</v>
+        <v>12058555.2</v>
       </c>
     </row>
     <row r="99">
@@ -12246,13 +12237,13 @@
         <v>71680</v>
       </c>
       <c r="B99">
-        <v>13956227440.6</v>
+        <v>42621988840.4</v>
       </c>
       <c r="C99">
-        <v>170926709.3</v>
+        <v>717975603.1</v>
       </c>
       <c r="D99">
-        <v>5874645.8</v>
+        <v>13105474.4</v>
       </c>
     </row>
     <row r="100">
@@ -12260,13 +12251,13 @@
         <v>76800</v>
       </c>
       <c r="B100">
-        <v>15974329050.1</v>
+        <v>48839209437.4</v>
       </c>
       <c r="C100">
-        <v>180511694.5</v>
+        <v>767957804.3</v>
       </c>
       <c r="D100">
-        <v>6301448.9</v>
+        <v>14270733</v>
       </c>
     </row>
     <row r="101">
@@ -12274,13 +12265,13 @@
         <v>81920</v>
       </c>
       <c r="B101">
-        <v>18222895840.3</v>
+        <v>55587646018.6</v>
       </c>
       <c r="C101">
-        <v>193626605.6</v>
+        <v>818475216.9</v>
       </c>
       <c r="D101">
-        <v>6677578.1</v>
+        <v>16275007.6</v>
       </c>
     </row>
     <row r="102">
@@ -12288,13 +12279,13 @@
         <v>87040</v>
       </c>
       <c r="B102">
-        <v>20559390221.8</v>
+        <v>63436063197.6</v>
       </c>
       <c r="C102">
-        <v>208244752.5</v>
+        <v>871442012.3</v>
       </c>
       <c r="D102">
-        <v>7194367</v>
+        <v>17328072.9</v>
       </c>
     </row>
     <row r="103">
@@ -12302,13 +12293,13 @@
         <v>92160</v>
       </c>
       <c r="B103">
-        <v>22971938112.2</v>
+        <v>72342763670.3</v>
       </c>
       <c r="C103">
-        <v>213587381.4</v>
+        <v>907252602.4</v>
       </c>
       <c r="D103">
-        <v>7653507.4</v>
+        <v>17365871.5</v>
       </c>
     </row>
     <row r="104">
@@ -12316,13 +12307,13 @@
         <v>97280</v>
       </c>
       <c r="B104">
-        <v>25709704095.3</v>
+        <v>80858923500.6</v>
       </c>
       <c r="C104">
-        <v>230312851.5</v>
+        <v>974526797.3</v>
       </c>
       <c r="D104">
-        <v>8008970.7</v>
+        <v>18167731.9</v>
       </c>
     </row>
     <row r="105">
@@ -12330,13 +12321,13 @@
         <v>102400</v>
       </c>
       <c r="B105">
-        <v>28444096006</v>
+        <v>89488301072.8</v>
       </c>
       <c r="C105">
-        <v>243367823.3</v>
+        <v>1024637142.2</v>
       </c>
       <c r="D105">
-        <v>8492545.1</v>
+        <v>18962636.8</v>
       </c>
     </row>
     <row r="109">
@@ -12363,13 +12354,13 @@
         <v>100</v>
       </c>
       <c r="B111">
-        <v>557762.8</v>
+        <v>82963.4</v>
       </c>
       <c r="C111">
-        <v>3288990.9</v>
+        <v>928269.2</v>
       </c>
       <c r="D111">
-        <v>50780.4</v>
+        <v>10055.1</v>
       </c>
     </row>
     <row r="112">
@@ -12377,13 +12368,13 @@
         <v>1024</v>
       </c>
       <c r="B112">
-        <v>56498903.5</v>
+        <v>9827302</v>
       </c>
       <c r="C112">
-        <v>33342812.4</v>
+        <v>10278739.1</v>
       </c>
       <c r="D112">
-        <v>677621.2</v>
+        <v>123599.4</v>
       </c>
     </row>
     <row r="113">
@@ -12391,13 +12382,13 @@
         <v>5120</v>
       </c>
       <c r="B113">
-        <v>1406698940.4</v>
+        <v>179148840.3</v>
       </c>
       <c r="C113">
-        <v>165331042.4</v>
+        <v>51183088.8</v>
       </c>
       <c r="D113">
-        <v>3831677.7</v>
+        <v>685812.9</v>
       </c>
     </row>
     <row r="114">
@@ -12405,13 +12396,13 @@
         <v>10240</v>
       </c>
       <c r="B114">
-        <v>5578436295.1</v>
+        <v>713713868.4</v>
       </c>
       <c r="C114">
-        <v>330034105.4</v>
+        <v>101877702.7</v>
       </c>
       <c r="D114">
-        <v>8135072.9</v>
+        <v>1437986.3</v>
       </c>
     </row>
     <row r="115">
@@ -12419,13 +12410,13 @@
         <v>15360</v>
       </c>
       <c r="B115">
-        <v>12684706235</v>
+        <v>1610808023.7</v>
       </c>
       <c r="C115">
-        <v>490022168.3</v>
+        <v>152962324.1</v>
       </c>
       <c r="D115">
-        <v>12598700.2</v>
+        <v>2230143.3</v>
       </c>
     </row>
     <row r="116">
@@ -12433,13 +12424,13 @@
         <v>20480</v>
       </c>
       <c r="B116">
-        <v>22322146682.4</v>
+        <v>2846276388.7</v>
       </c>
       <c r="C116">
-        <v>661321424.9</v>
+        <v>204053053.6</v>
       </c>
       <c r="D116">
-        <v>17229481.4</v>
+        <v>2994569.5</v>
       </c>
     </row>
     <row r="117">
@@ -12447,13 +12438,13 @@
         <v>25600</v>
       </c>
       <c r="B117">
-        <v>35129432253.3</v>
+        <v>4433773216.4</v>
       </c>
       <c r="C117">
-        <v>830303817</v>
+        <v>254840481.7</v>
       </c>
       <c r="D117">
-        <v>22061593.2</v>
+        <v>3790005.1</v>
       </c>
     </row>
     <row r="118">
@@ -12461,13 +12452,13 @@
         <v>30720</v>
       </c>
       <c r="B118">
-        <v>50811537498.2</v>
+        <v>6518896175</v>
       </c>
       <c r="C118">
-        <v>992089360.5</v>
+        <v>306111723.1</v>
       </c>
       <c r="D118">
-        <v>27100394.5</v>
+        <v>4622930.7</v>
       </c>
     </row>
     <row r="119">
@@ -12475,13 +12466,13 @@
         <v>35840</v>
       </c>
       <c r="B119">
-        <v>69105582394.1</v>
+        <v>8815969638.3</v>
       </c>
       <c r="C119">
-        <v>1166714536.8</v>
+        <v>357054966</v>
       </c>
       <c r="D119">
-        <v>31610119.5</v>
+        <v>5436622.9</v>
       </c>
     </row>
     <row r="120">
@@ -12489,13 +12480,13 @@
         <v>40960</v>
       </c>
       <c r="B120">
-        <v>90692851024.3</v>
+        <v>11585239740.2</v>
       </c>
       <c r="C120">
-        <v>1333042823.5</v>
+        <v>407498526.5</v>
       </c>
       <c r="D120">
-        <v>37769774.8</v>
+        <v>6394459.4</v>
       </c>
     </row>
     <row r="121">
@@ -12503,13 +12494,13 @@
         <v>46080</v>
       </c>
       <c r="B121">
-        <v>114442607094.5</v>
+        <v>14567175307.8</v>
       </c>
       <c r="C121">
-        <v>1490738197.6</v>
+        <v>461330246.7</v>
       </c>
       <c r="D121">
-        <v>41976279.4</v>
+        <v>7079063</v>
       </c>
     </row>
     <row r="122">
@@ -12517,13 +12508,13 @@
         <v>51200</v>
       </c>
       <c r="B122">
-        <v>141530964374.9</v>
+        <v>18091568600.6</v>
       </c>
       <c r="C122">
-        <v>1684184290.5</v>
+        <v>506856371.5</v>
       </c>
       <c r="D122">
-        <v>46097149.5</v>
+        <v>7912422.3</v>
       </c>
     </row>
     <row r="123">
@@ -12531,13 +12522,13 @@
         <v>56320</v>
       </c>
       <c r="B123">
-        <v>170701367450.8</v>
+        <v>21710078733.8</v>
       </c>
       <c r="C123">
-        <v>1823900667</v>
+        <v>563467551.2</v>
       </c>
       <c r="D123">
-        <v>51871653.3</v>
+        <v>8786584.6</v>
       </c>
     </row>
     <row r="124">
@@ -12545,13 +12536,13 @@
         <v>61440</v>
       </c>
       <c r="B124">
-        <v>203820136377.7</v>
+        <v>26149479114.6</v>
       </c>
       <c r="C124">
-        <v>1985824590.8</v>
+        <v>613243337.9</v>
       </c>
       <c r="D124">
-        <v>57466128.2</v>
+        <v>9717019</v>
       </c>
     </row>
     <row r="125">
@@ -12559,13 +12550,13 @@
         <v>66560</v>
       </c>
       <c r="B125">
-        <v>239084713971.6</v>
+        <v>30474127218.4</v>
       </c>
       <c r="C125">
-        <v>2201072592.7</v>
+        <v>661409185.9</v>
       </c>
       <c r="D125">
-        <v>61991377.5</v>
+        <v>10567925.4</v>
       </c>
     </row>
     <row r="126">
@@ -12573,13 +12564,13 @@
         <v>71680</v>
       </c>
       <c r="B126">
-        <v>277618517241</v>
+        <v>35765170742.2</v>
       </c>
       <c r="C126">
-        <v>2360389873.2</v>
+        <v>713264838.8</v>
       </c>
       <c r="D126">
-        <v>67354625.4</v>
+        <v>11444969.8</v>
       </c>
     </row>
     <row r="127">
@@ -12587,13 +12578,13 @@
         <v>76800</v>
       </c>
       <c r="B127">
-        <v>317605707827.7</v>
+        <v>40081367236.2</v>
       </c>
       <c r="C127">
-        <v>2518559857.4</v>
+        <v>762123602</v>
       </c>
       <c r="D127">
-        <v>72080043.6</v>
+        <v>12222383.2</v>
       </c>
     </row>
     <row r="128">
@@ -12601,13 +12592,13 @@
         <v>81920</v>
       </c>
       <c r="B128">
-        <v>361211297263.7</v>
+        <v>46179802809.9</v>
       </c>
       <c r="C128">
-        <v>2676024061.2</v>
+        <v>819105618.2</v>
       </c>
       <c r="D128">
-        <v>78243779.9</v>
+        <v>12978764.1</v>
       </c>
     </row>
     <row r="129">
@@ -12615,13 +12606,13 @@
         <v>87040</v>
       </c>
       <c r="B129">
-        <v>408896660387.3</v>
+        <v>51951214409</v>
       </c>
       <c r="C129">
-        <v>2842473626</v>
+        <v>864279368.6</v>
       </c>
       <c r="D129">
-        <v>83677849.2</v>
+        <v>13897361.3</v>
       </c>
     </row>
     <row r="130">
@@ -12629,13 +12620,13 @@
         <v>92160</v>
       </c>
       <c r="B130">
-        <v>457546233055.2</v>
+        <v>58742794034.3</v>
       </c>
       <c r="C130">
-        <v>3008711128.9</v>
+        <v>918100522.6</v>
       </c>
       <c r="D130">
-        <v>89536990</v>
+        <v>14789982.7</v>
       </c>
     </row>
     <row r="131">
@@ -12643,13 +12634,13 @@
         <v>97280</v>
       </c>
       <c r="B131">
-        <v>511226726172.7</v>
+        <v>65638213779.5</v>
       </c>
       <c r="C131">
-        <v>3163661340.3</v>
+        <v>971643274.9</v>
       </c>
       <c r="D131">
-        <v>93289289.7</v>
+        <v>15417517.6</v>
       </c>
     </row>
     <row r="132">
@@ -12657,13 +12648,13 @@
         <v>102400</v>
       </c>
       <c r="B132">
-        <v>566110304268.6</v>
+        <v>71617023099.5</v>
       </c>
       <c r="C132">
-        <v>3336970656.1</v>
+        <v>1025923888.2</v>
       </c>
       <c r="D132">
-        <v>99630069.3</v>
+        <v>16565274.4</v>
       </c>
     </row>
   </sheetData>
@@ -15926,7 +15917,7 @@
         <v>100</v>
       </c>
       <c r="B3">
-        <v>672</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4">
@@ -15934,7 +15925,7 @@
         <v>1024</v>
       </c>
       <c r="B4">
-        <v>10240</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="5">
@@ -15942,7 +15933,7 @@
         <v>5120</v>
       </c>
       <c r="B5">
-        <v>63488</v>
+        <v>5120</v>
       </c>
     </row>
     <row r="6">
@@ -15950,7 +15941,7 @@
         <v>10240</v>
       </c>
       <c r="B6">
-        <v>137216</v>
+        <v>10240</v>
       </c>
     </row>
     <row r="7">
@@ -15958,7 +15949,7 @@
         <v>15360</v>
       </c>
       <c r="B7">
-        <v>214016</v>
+        <v>15360</v>
       </c>
     </row>
     <row r="8">
@@ -15966,7 +15957,7 @@
         <v>20480</v>
       </c>
       <c r="B8">
-        <v>294912</v>
+        <v>20480</v>
       </c>
     </row>
     <row r="9">
@@ -15974,7 +15965,7 @@
         <v>25600</v>
       </c>
       <c r="B9">
-        <v>376832</v>
+        <v>25600</v>
       </c>
     </row>
     <row r="10">
@@ -15982,7 +15973,7 @@
         <v>30720</v>
       </c>
       <c r="B10">
-        <v>458752</v>
+        <v>30720</v>
       </c>
     </row>
     <row r="11">
@@ -15990,7 +15981,7 @@
         <v>35840</v>
       </c>
       <c r="B11">
-        <v>543744</v>
+        <v>35840</v>
       </c>
     </row>
     <row r="12">
@@ -15998,7 +15989,7 @@
         <v>40960</v>
       </c>
       <c r="B12">
-        <v>630784</v>
+        <v>40960</v>
       </c>
     </row>
     <row r="13">
@@ -16006,7 +15997,7 @@
         <v>46080</v>
       </c>
       <c r="B13">
-        <v>717824</v>
+        <v>46080</v>
       </c>
     </row>
     <row r="14">
@@ -16014,7 +16005,7 @@
         <v>51200</v>
       </c>
       <c r="B14">
-        <v>804864</v>
+        <v>51200</v>
       </c>
     </row>
     <row r="15">
@@ -16022,7 +16013,7 @@
         <v>56320</v>
       </c>
       <c r="B15">
-        <v>891904</v>
+        <v>56320</v>
       </c>
     </row>
     <row r="16">
@@ -16030,7 +16021,7 @@
         <v>61440</v>
       </c>
       <c r="B16">
-        <v>978944</v>
+        <v>61440</v>
       </c>
     </row>
     <row r="17">
@@ -16038,7 +16029,7 @@
         <v>66560</v>
       </c>
       <c r="B17">
-        <v>1067008</v>
+        <v>66560</v>
       </c>
     </row>
     <row r="18">
@@ -16046,7 +16037,7 @@
         <v>71680</v>
       </c>
       <c r="B18">
-        <v>1159168</v>
+        <v>71680</v>
       </c>
     </row>
     <row r="19">
@@ -16054,7 +16045,7 @@
         <v>76800</v>
       </c>
       <c r="B19">
-        <v>1251328</v>
+        <v>76800</v>
       </c>
     </row>
     <row r="20">
@@ -16062,7 +16053,7 @@
         <v>81920</v>
       </c>
       <c r="B20">
-        <v>1343488</v>
+        <v>81920</v>
       </c>
     </row>
     <row r="21">
@@ -16070,7 +16061,7 @@
         <v>87040</v>
       </c>
       <c r="B21">
-        <v>1435648</v>
+        <v>87040</v>
       </c>
     </row>
     <row r="22">
@@ -16078,7 +16069,7 @@
         <v>92160</v>
       </c>
       <c r="B22">
-        <v>1527808</v>
+        <v>92160</v>
       </c>
     </row>
     <row r="23">
@@ -16086,7 +16077,7 @@
         <v>97280</v>
       </c>
       <c r="B23">
-        <v>1619968</v>
+        <v>97280</v>
       </c>
     </row>
     <row r="24">
@@ -16094,7 +16085,7 @@
         <v>102400</v>
       </c>
       <c r="B24">
-        <v>1712128</v>
+        <v>102400</v>
       </c>
     </row>
     <row r="28">
@@ -16115,7 +16106,7 @@
         <v>100</v>
       </c>
       <c r="B30">
-        <v>672</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31">
@@ -16123,7 +16114,7 @@
         <v>1024</v>
       </c>
       <c r="B31">
-        <v>10240</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="32">
@@ -16131,7 +16122,7 @@
         <v>5120</v>
       </c>
       <c r="B32">
-        <v>63488</v>
+        <v>5120</v>
       </c>
     </row>
     <row r="33">
@@ -16139,7 +16130,7 @@
         <v>10240</v>
       </c>
       <c r="B33">
-        <v>137216</v>
+        <v>10240</v>
       </c>
     </row>
     <row r="34">
@@ -16147,7 +16138,7 @@
         <v>15360</v>
       </c>
       <c r="B34">
-        <v>214016</v>
+        <v>15360</v>
       </c>
     </row>
     <row r="35">
@@ -16155,7 +16146,7 @@
         <v>20480</v>
       </c>
       <c r="B35">
-        <v>294912</v>
+        <v>20480</v>
       </c>
     </row>
     <row r="36">
@@ -16163,7 +16154,7 @@
         <v>25600</v>
       </c>
       <c r="B36">
-        <v>376832</v>
+        <v>25600</v>
       </c>
     </row>
     <row r="37">
@@ -16171,7 +16162,7 @@
         <v>30720</v>
       </c>
       <c r="B37">
-        <v>458752</v>
+        <v>30720</v>
       </c>
     </row>
     <row r="38">
@@ -16179,7 +16170,7 @@
         <v>35840</v>
       </c>
       <c r="B38">
-        <v>543744</v>
+        <v>35840</v>
       </c>
     </row>
     <row r="39">
@@ -16187,7 +16178,7 @@
         <v>40960</v>
       </c>
       <c r="B39">
-        <v>630784</v>
+        <v>40960</v>
       </c>
     </row>
     <row r="40">
@@ -16195,7 +16186,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>717824</v>
+        <v>46080</v>
       </c>
     </row>
     <row r="41">
@@ -16203,7 +16194,7 @@
         <v>51200</v>
       </c>
       <c r="B41">
-        <v>804864</v>
+        <v>51200</v>
       </c>
     </row>
     <row r="42">
@@ -16211,7 +16202,7 @@
         <v>56320</v>
       </c>
       <c r="B42">
-        <v>891904</v>
+        <v>56320</v>
       </c>
     </row>
     <row r="43">
@@ -16219,7 +16210,7 @@
         <v>61440</v>
       </c>
       <c r="B43">
-        <v>978944</v>
+        <v>61440</v>
       </c>
     </row>
     <row r="44">
@@ -16227,7 +16218,7 @@
         <v>66560</v>
       </c>
       <c r="B44">
-        <v>1067008</v>
+        <v>66560</v>
       </c>
     </row>
     <row r="45">
@@ -16235,7 +16226,7 @@
         <v>71680</v>
       </c>
       <c r="B45">
-        <v>1159168</v>
+        <v>71680</v>
       </c>
     </row>
     <row r="46">
@@ -16243,7 +16234,7 @@
         <v>76800</v>
       </c>
       <c r="B46">
-        <v>1251328</v>
+        <v>76800</v>
       </c>
     </row>
     <row r="47">
@@ -16251,7 +16242,7 @@
         <v>81920</v>
       </c>
       <c r="B47">
-        <v>1343488</v>
+        <v>81920</v>
       </c>
     </row>
     <row r="48">
@@ -16259,7 +16250,7 @@
         <v>87040</v>
       </c>
       <c r="B48">
-        <v>1435648</v>
+        <v>87040</v>
       </c>
     </row>
     <row r="49">
@@ -16267,7 +16258,7 @@
         <v>92160</v>
       </c>
       <c r="B49">
-        <v>1527808</v>
+        <v>92160</v>
       </c>
     </row>
     <row r="50">
@@ -16275,7 +16266,7 @@
         <v>97280</v>
       </c>
       <c r="B50">
-        <v>1619968</v>
+        <v>97280</v>
       </c>
     </row>
     <row r="51">
@@ -16283,7 +16274,7 @@
         <v>102400</v>
       </c>
       <c r="B51">
-        <v>1712128</v>
+        <v>102400</v>
       </c>
     </row>
     <row r="55">
@@ -16304,7 +16295,7 @@
         <v>100</v>
       </c>
       <c r="B57">
-        <v>672</v>
+        <v>100</v>
       </c>
     </row>
     <row r="58">
@@ -16312,7 +16303,7 @@
         <v>1024</v>
       </c>
       <c r="B58">
-        <v>10240</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="59">
@@ -16320,7 +16311,7 @@
         <v>5120</v>
       </c>
       <c r="B59">
-        <v>63488</v>
+        <v>5120</v>
       </c>
     </row>
     <row r="60">
@@ -16328,7 +16319,7 @@
         <v>10240</v>
       </c>
       <c r="B60">
-        <v>137216</v>
+        <v>10240</v>
       </c>
     </row>
     <row r="61">
@@ -16336,7 +16327,7 @@
         <v>15360</v>
       </c>
       <c r="B61">
-        <v>214016</v>
+        <v>15360</v>
       </c>
     </row>
     <row r="62">
@@ -16344,7 +16335,7 @@
         <v>20480</v>
       </c>
       <c r="B62">
-        <v>294912</v>
+        <v>20480</v>
       </c>
     </row>
     <row r="63">
@@ -16352,7 +16343,7 @@
         <v>25600</v>
       </c>
       <c r="B63">
-        <v>376832</v>
+        <v>25600</v>
       </c>
     </row>
     <row r="64">
@@ -16360,7 +16351,7 @@
         <v>30720</v>
       </c>
       <c r="B64">
-        <v>458752</v>
+        <v>30720</v>
       </c>
     </row>
     <row r="65">
@@ -16368,7 +16359,7 @@
         <v>35840</v>
       </c>
       <c r="B65">
-        <v>543744</v>
+        <v>35840</v>
       </c>
     </row>
     <row r="66">
@@ -16376,7 +16367,7 @@
         <v>40960</v>
       </c>
       <c r="B66">
-        <v>630784</v>
+        <v>40960</v>
       </c>
     </row>
     <row r="67">
@@ -16384,7 +16375,7 @@
         <v>46080</v>
       </c>
       <c r="B67">
-        <v>717824</v>
+        <v>46080</v>
       </c>
     </row>
     <row r="68">
@@ -16392,7 +16383,7 @@
         <v>51200</v>
       </c>
       <c r="B68">
-        <v>804864</v>
+        <v>51200</v>
       </c>
     </row>
     <row r="69">
@@ -16400,7 +16391,7 @@
         <v>56320</v>
       </c>
       <c r="B69">
-        <v>891904</v>
+        <v>56320</v>
       </c>
     </row>
     <row r="70">
@@ -16408,7 +16399,7 @@
         <v>61440</v>
       </c>
       <c r="B70">
-        <v>978944</v>
+        <v>61440</v>
       </c>
     </row>
     <row r="71">
@@ -16416,7 +16407,7 @@
         <v>66560</v>
       </c>
       <c r="B71">
-        <v>1067008</v>
+        <v>66560</v>
       </c>
     </row>
     <row r="72">
@@ -16424,7 +16415,7 @@
         <v>71680</v>
       </c>
       <c r="B72">
-        <v>1159168</v>
+        <v>71680</v>
       </c>
     </row>
     <row r="73">
@@ -16432,7 +16423,7 @@
         <v>76800</v>
       </c>
       <c r="B73">
-        <v>1251328</v>
+        <v>76800</v>
       </c>
     </row>
     <row r="74">
@@ -16440,7 +16431,7 @@
         <v>81920</v>
       </c>
       <c r="B74">
-        <v>1343488</v>
+        <v>81920</v>
       </c>
     </row>
     <row r="75">
@@ -16448,7 +16439,7 @@
         <v>87040</v>
       </c>
       <c r="B75">
-        <v>1435648</v>
+        <v>87040</v>
       </c>
     </row>
     <row r="76">
@@ -16456,7 +16447,7 @@
         <v>92160</v>
       </c>
       <c r="B76">
-        <v>1527808</v>
+        <v>92160</v>
       </c>
     </row>
     <row r="77">
@@ -16464,7 +16455,7 @@
         <v>97280</v>
       </c>
       <c r="B77">
-        <v>1619968</v>
+        <v>97280</v>
       </c>
     </row>
     <row r="78">
@@ -16472,7 +16463,7 @@
         <v>102400</v>
       </c>
       <c r="B78">
-        <v>1712128</v>
+        <v>102400</v>
       </c>
     </row>
     <row r="82">
@@ -16493,7 +16484,7 @@
         <v>100</v>
       </c>
       <c r="B84">
-        <v>672</v>
+        <v>100</v>
       </c>
     </row>
     <row r="85">
@@ -16501,7 +16492,7 @@
         <v>1024</v>
       </c>
       <c r="B85">
-        <v>10240</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="86">
@@ -16509,7 +16500,7 @@
         <v>5120</v>
       </c>
       <c r="B86">
-        <v>63488</v>
+        <v>5120</v>
       </c>
     </row>
     <row r="87">
@@ -16517,7 +16508,7 @@
         <v>10240</v>
       </c>
       <c r="B87">
-        <v>137216</v>
+        <v>10240</v>
       </c>
     </row>
     <row r="88">
@@ -16525,7 +16516,7 @@
         <v>15360</v>
       </c>
       <c r="B88">
-        <v>214016</v>
+        <v>15360</v>
       </c>
     </row>
     <row r="89">
@@ -16533,7 +16524,7 @@
         <v>20480</v>
       </c>
       <c r="B89">
-        <v>294912</v>
+        <v>20480</v>
       </c>
     </row>
     <row r="90">
@@ -16541,7 +16532,7 @@
         <v>25600</v>
       </c>
       <c r="B90">
-        <v>376832</v>
+        <v>25600</v>
       </c>
     </row>
     <row r="91">
@@ -16549,7 +16540,7 @@
         <v>30720</v>
       </c>
       <c r="B91">
-        <v>458752</v>
+        <v>30720</v>
       </c>
     </row>
     <row r="92">
@@ -16557,7 +16548,7 @@
         <v>35840</v>
       </c>
       <c r="B92">
-        <v>543744</v>
+        <v>35840</v>
       </c>
     </row>
     <row r="93">
@@ -16565,7 +16556,7 @@
         <v>40960</v>
       </c>
       <c r="B93">
-        <v>630784</v>
+        <v>40960</v>
       </c>
     </row>
     <row r="94">
@@ -16573,7 +16564,7 @@
         <v>46080</v>
       </c>
       <c r="B94">
-        <v>717824</v>
+        <v>46080</v>
       </c>
     </row>
     <row r="95">
@@ -16581,7 +16572,7 @@
         <v>51200</v>
       </c>
       <c r="B95">
-        <v>804864</v>
+        <v>51200</v>
       </c>
     </row>
     <row r="96">
@@ -16589,7 +16580,7 @@
         <v>56320</v>
       </c>
       <c r="B96">
-        <v>891904</v>
+        <v>56320</v>
       </c>
     </row>
     <row r="97">
@@ -16597,7 +16588,7 @@
         <v>61440</v>
       </c>
       <c r="B97">
-        <v>978944</v>
+        <v>61440</v>
       </c>
     </row>
     <row r="98">
@@ -16605,7 +16596,7 @@
         <v>66560</v>
       </c>
       <c r="B98">
-        <v>1067008</v>
+        <v>66560</v>
       </c>
     </row>
     <row r="99">
@@ -16613,7 +16604,7 @@
         <v>71680</v>
       </c>
       <c r="B99">
-        <v>1159168</v>
+        <v>71680</v>
       </c>
     </row>
     <row r="100">
@@ -16621,7 +16612,7 @@
         <v>76800</v>
       </c>
       <c r="B100">
-        <v>1251328</v>
+        <v>76800</v>
       </c>
     </row>
     <row r="101">
@@ -16629,7 +16620,7 @@
         <v>81920</v>
       </c>
       <c r="B101">
-        <v>1343488</v>
+        <v>81920</v>
       </c>
     </row>
     <row r="102">
@@ -16637,7 +16628,7 @@
         <v>87040</v>
       </c>
       <c r="B102">
-        <v>1435648</v>
+        <v>87040</v>
       </c>
     </row>
     <row r="103">
@@ -16645,7 +16636,7 @@
         <v>92160</v>
       </c>
       <c r="B103">
-        <v>1527808</v>
+        <v>92160</v>
       </c>
     </row>
     <row r="104">
@@ -16653,7 +16644,7 @@
         <v>97280</v>
       </c>
       <c r="B104">
-        <v>1619968</v>
+        <v>97280</v>
       </c>
     </row>
     <row r="105">
@@ -16661,7 +16652,7 @@
         <v>102400</v>
       </c>
       <c r="B105">
-        <v>1712128</v>
+        <v>102400</v>
       </c>
     </row>
     <row r="109">
@@ -16682,7 +16673,7 @@
         <v>100</v>
       </c>
       <c r="B111">
-        <v>672</v>
+        <v>100</v>
       </c>
     </row>
     <row r="112">
@@ -16690,7 +16681,7 @@
         <v>1024</v>
       </c>
       <c r="B112">
-        <v>10240</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="113">
@@ -16698,7 +16689,7 @@
         <v>5120</v>
       </c>
       <c r="B113">
-        <v>63488</v>
+        <v>5120</v>
       </c>
     </row>
     <row r="114">
@@ -16706,7 +16697,7 @@
         <v>10240</v>
       </c>
       <c r="B114">
-        <v>137216</v>
+        <v>10240</v>
       </c>
     </row>
     <row r="115">
@@ -16714,7 +16705,7 @@
         <v>15360</v>
       </c>
       <c r="B115">
-        <v>214016</v>
+        <v>15360</v>
       </c>
     </row>
     <row r="116">
@@ -16722,7 +16713,7 @@
         <v>20480</v>
       </c>
       <c r="B116">
-        <v>294912</v>
+        <v>20480</v>
       </c>
     </row>
     <row r="117">
@@ -16730,7 +16721,7 @@
         <v>25600</v>
       </c>
       <c r="B117">
-        <v>376832</v>
+        <v>25600</v>
       </c>
     </row>
     <row r="118">
@@ -16738,7 +16729,7 @@
         <v>30720</v>
       </c>
       <c r="B118">
-        <v>458752</v>
+        <v>30720</v>
       </c>
     </row>
     <row r="119">
@@ -16746,7 +16737,7 @@
         <v>35840</v>
       </c>
       <c r="B119">
-        <v>543744</v>
+        <v>35840</v>
       </c>
     </row>
     <row r="120">
@@ -16754,7 +16745,7 @@
         <v>40960</v>
       </c>
       <c r="B120">
-        <v>630784</v>
+        <v>40960</v>
       </c>
     </row>
     <row r="121">
@@ -16762,7 +16753,7 @@
         <v>46080</v>
       </c>
       <c r="B121">
-        <v>717824</v>
+        <v>46080</v>
       </c>
     </row>
     <row r="122">
@@ -16770,7 +16761,7 @@
         <v>51200</v>
       </c>
       <c r="B122">
-        <v>804864</v>
+        <v>51200</v>
       </c>
     </row>
     <row r="123">
@@ -16778,7 +16769,7 @@
         <v>56320</v>
       </c>
       <c r="B123">
-        <v>891904</v>
+        <v>56320</v>
       </c>
     </row>
     <row r="124">
@@ -16786,7 +16777,7 @@
         <v>61440</v>
       </c>
       <c r="B124">
-        <v>978944</v>
+        <v>61440</v>
       </c>
     </row>
     <row r="125">
@@ -16794,7 +16785,7 @@
         <v>66560</v>
       </c>
       <c r="B125">
-        <v>1067008</v>
+        <v>66560</v>
       </c>
     </row>
     <row r="126">
@@ -16802,7 +16793,7 @@
         <v>71680</v>
       </c>
       <c r="B126">
-        <v>1159168</v>
+        <v>71680</v>
       </c>
     </row>
     <row r="127">
@@ -16810,7 +16801,7 @@
         <v>76800</v>
       </c>
       <c r="B127">
-        <v>1251328</v>
+        <v>76800</v>
       </c>
     </row>
     <row r="128">
@@ -16818,7 +16809,7 @@
         <v>81920</v>
       </c>
       <c r="B128">
-        <v>1343488</v>
+        <v>81920</v>
       </c>
     </row>
     <row r="129">
@@ -16826,7 +16817,7 @@
         <v>87040</v>
       </c>
       <c r="B129">
-        <v>1435648</v>
+        <v>87040</v>
       </c>
     </row>
     <row r="130">
@@ -16834,7 +16825,7 @@
         <v>92160</v>
       </c>
       <c r="B130">
-        <v>1527808</v>
+        <v>92160</v>
       </c>
     </row>
     <row r="131">
@@ -16842,7 +16833,7 @@
         <v>97280</v>
       </c>
       <c r="B131">
-        <v>1619968</v>
+        <v>97280</v>
       </c>
     </row>
     <row r="132">
@@ -16850,7 +16841,7 @@
         <v>102400</v>
       </c>
       <c r="B132">
-        <v>1712128</v>
+        <v>102400</v>
       </c>
     </row>
   </sheetData>
